--- a/UX検定_基礎.xlsx
+++ b/UX検定_基礎.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\勉強\資格(取得)\UX\基礎\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\UX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15017551-6A43-46F2-B561-701DA397D2A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06F838A-7458-4D3A-ADFD-E05C5829A159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="模擬" sheetId="1" r:id="rId1"/>
@@ -36,15 +36,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="313">
   <si>
     <t>UXインテリジェンスが生み出す価値として重要視するものを、次の中から選びなさい。</t>
     <phoneticPr fontId="1"/>
@@ -813,6 +810,1853 @@
   </si>
   <si>
     <t>ペインポイントとは、ユーザーがストレスや不便を感じるところであり、行動データの分析により、どこで迷いや離脱が起きているかを把握することが出来ます。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーテストにおける「思考発話法」の説明として、適切なものはどれか？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが操作中に発言してしまうのを避ける方法</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが操作中に考えていることをその場で声に出して言ってもらう方法</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの行動だけを記録し、後で行動理由を尋ねる方法</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイナーがユーザーの行動を予測して代弁する方法</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>思考発話法では、ユーザーが操作しながら感じたことを声に出してもらい、リアルタイムで認知や判断を把握する方法です。</t>
+  </si>
+  <si>
+    <t>カスタマージャーニーマップについての説明として、適切なものは次のうちどれか？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロダクトのUI改善後の効果を数値で示すための資料</t>
+    <rPh sb="8" eb="10">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>スウチ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>シメ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>シリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>顧客接点におけるユーザーの体験の流れや感情を可視化し、課題を発見するために活用する</t>
+    <rPh sb="0" eb="2">
+      <t>コキャク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セッテン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カンジョウ</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>カシカ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ハッケン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>カツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ペルソナごとのユーザーインターフェースを設定する</t>
+    <rPh sb="20" eb="22">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用状況の定量データを記録するための表</t>
+    <rPh sb="5" eb="7">
+      <t>テイリョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カスタマージャーニーマップは、ユーザーの行動・感情・接点を時系列で整理して、</t>
+    <rPh sb="20" eb="22">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>カンジョウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>セッテン</t>
+    </rPh>
+    <rPh sb="29" eb="32">
+      <t>ジケイレツ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>セイリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UX上の課題や改善するべき点を発見するためのツールです。</t>
+    <rPh sb="2" eb="3">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ハッケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロトタイピングの目的として、適切なものは次のうちどれか？</t>
+    <rPh sb="9" eb="11">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コーディングを外注するための資料を準備すること</t>
+    <rPh sb="7" eb="9">
+      <t>ガイチュウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジュンビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイン案を簡易的に具現化して、アイデアの検証や改善につなげること</t>
+    <rPh sb="4" eb="5">
+      <t>アン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>グゲンカ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ケンショウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実装の手間を省くための最終成果物に近いアウトプットを作ること</t>
+    <rPh sb="0" eb="2">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>テマ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ハブ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サイシュウ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>セイカブツ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>チカ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ビジュアルを見せるためのコンセプトアートを作ること</t>
+    <rPh sb="6" eb="7">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロトタイプは試作品としてアイデアを可視化して、ユーザーの反応や使いやすさを検証するためのツールです。</t>
+    <rPh sb="7" eb="10">
+      <t>シサクヒン</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>カシカ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ハンノウ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ケンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ペルソナ作成について重視されるべきポイントとして、適切なものはどれか？</t>
+    <rPh sb="4" eb="6">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジュウシ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>テキセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サービス担当者の理想のユーザー像を想像して書くこと</t>
+    <rPh sb="4" eb="7">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>リソウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ゾウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ソウゾウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実在のユーザーのプロフィールをそのまま転記すること</t>
+    <rPh sb="0" eb="2">
+      <t>ジツザイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>テンキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実際の調査データに基づき、行動やニーズを明確にした架空の人物像を作ること</t>
+    <rPh sb="0" eb="2">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>メイカク</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>カクウ</t>
+    </rPh>
+    <rPh sb="28" eb="31">
+      <t>ジンブツゾウ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>市場に合わせてインフルエンサーなど有名人をモデルにすること</t>
+    <rPh sb="0" eb="2">
+      <t>シジョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>ユウメイジン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ペルソナは仮想ユーザーですが、実際の定性・定量調査を元に、行動・ニーズ・価値観を反映した現実的なモデルである必要があります</t>
+    <rPh sb="5" eb="7">
+      <t>カソウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>テイセイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>テイリョウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="36" eb="39">
+      <t>カチカン</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ハンエイ</t>
+    </rPh>
+    <rPh sb="44" eb="47">
+      <t>ゲンジツテキ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アクセシビリティの目的として、適切なものは次のうちどれか？</t>
+    <rPh sb="9" eb="11">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIの美しさを最大限に引き出すこと</t>
+    <rPh sb="3" eb="4">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>サイダイゲン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一般的なユーザーのみに向けて設計を効率化すること</t>
+    <rPh sb="0" eb="3">
+      <t>イッパンテキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>コウリツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アプリの操作速度を最適化すること</t>
+    <rPh sb="4" eb="6">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>サイテキカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すべてのユーザーにとって利用可能な環境を提供すること</t>
+    <rPh sb="12" eb="14">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>テイキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アクセシビリティとは、年齢や使用環境などに関係なく、あらゆる人が等しく使える設計を目指すアプローチのことです。</t>
+    <rPh sb="11" eb="13">
+      <t>ネンレイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>メザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXグロース活動で「ファネル型マーケティング」の限界を補う考え方として、適切なのはどれか？</t>
+    <rPh sb="6" eb="8">
+      <t>カツドウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ゲンカイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>オギナ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>テキセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>離脱ユーザーの分析に集中してコンバージョン率を上げる</t>
+    <rPh sb="0" eb="2">
+      <t>リダツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シュウチュウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーのジャーニー内で価値を提供し続ける体験提供型アプローチ</t>
+    <rPh sb="10" eb="11">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カチ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>テイキョウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>テイキョウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>広告出稿を増やしてファネルを押し広げる</t>
+    <rPh sb="0" eb="2">
+      <t>コウコク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュッコウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ヒロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一度の利用で最大の満足を提供するワンショットUX戦略</t>
+    <rPh sb="0" eb="2">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>マンゾク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>テイキョウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>センリャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーのジャーニー内で価値を提供し続ける体験提供型アプローチ</t>
+    <rPh sb="10" eb="11">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カチ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>テイキョウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>テイキョウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>カタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>体験提供型の考え方においては、UXグロースを一度のコンバージョンで終わらせず、ジャーニーの中で繰り返し価値を提供する設計が重要となります。</t>
+    <rPh sb="0" eb="2">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>テイキョウガタ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>カチ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>テイキョウ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ヒューリスティック評価」に関する説明として、適切なものは次のうちどれか？</t>
+    <rPh sb="10" eb="12">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実ユーザーによる評価に基づく体験分析手法</t>
+    <rPh sb="0" eb="1">
+      <t>ジツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>感情分析アルゴリズムに基づくUX数値化手法</t>
+    <rPh sb="0" eb="2">
+      <t>カンジョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>スウチカ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>専門家が経験則を元にUIの問題を洗い出す手法</t>
+    <rPh sb="0" eb="3">
+      <t>センモンカ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ケイケンソク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>アラ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AIを使って自動的にUXを分析する手法</t>
+    <rPh sb="3" eb="4">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ジドウテキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒューリスティック評価とは、UX専門家が経験と知識を元に問題を洗い出す手法であり、</t>
+    <rPh sb="9" eb="11">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>センモンカ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>チシキ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>アラ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実ユーザーが不要であり、短期間で効果的なレビューが出来ます。</t>
+    <rPh sb="0" eb="1">
+      <t>ジツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>フヨウ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>タンキカン</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>コウカテキ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>デキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXライティングにおける「マイクロコピー」の目的として、適切なものは次のうちどれか？</t>
+    <rPh sb="22" eb="24">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文章全体のトーンやブランドガイドラインの整備</t>
+    <rPh sb="0" eb="2">
+      <t>ブンショウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>セイビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UI上の短い文言で、ユーザーの迷いを減らし、行動を促す</t>
+    <rPh sb="2" eb="3">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ミジカ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>モンゴン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>マヨ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヘ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ウナガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サービスの魅力を広告的に伝える長文コンテンツの作成</t>
+    <rPh sb="5" eb="7">
+      <t>ミリョク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウコク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ツタ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>チョウブン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コードレビュー時のコメント記述を効率化する</t>
+    <rPh sb="7" eb="8">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キジュツ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>コウリツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マイクロコピーとは「ボタン」「エラーメッセージ」等のミクロな文言であり、</t>
+    <rPh sb="24" eb="25">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>モンゴン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの行動をガイドする重要な要素であり、UXにおける心理的ハードルの軽減に役立ちます。</t>
+    <rPh sb="5" eb="7">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="28" eb="31">
+      <t>シンリテキ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ケイゲン</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ヤクダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UX改善における「フィードバックループ」の活用についての説明</t>
+    <rPh sb="2" eb="4">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カツヨウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一度のリリースで完結する体験設計を行う</t>
+    <rPh sb="0" eb="2">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンケツ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>改善施策の実施後、ユーザーの反応やデータに基づいて再度改善を繰り返す</t>
+    <rPh sb="0" eb="2">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シサク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハンノウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>サイド</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>カエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社内レビューのみによってUX施策を評価する</t>
+    <rPh sb="0" eb="2">
+      <t>シャナイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シサク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヒョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザインを毎回一新し、過去の反応を参照しない</t>
+    <rPh sb="5" eb="7">
+      <t>マイカイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イッシン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハンノウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>サンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フィードバックループとは「実装→評価→改善」の循環型プロセスであり、</t>
+    <rPh sb="13" eb="15">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>ジュンカンガタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの反応を取り入れて継続的にUXを進化させるスタンスのことです。</t>
+    <rPh sb="5" eb="7">
+      <t>ハンノウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ケイゾクテキ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サービスデザイン思考における「タッチポイント」の説明として、適切なものは次のうちどれか？</t>
+    <rPh sb="8" eb="10">
+      <t>シコウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サービス提供側が意図する主要KPI</t>
+    <rPh sb="4" eb="6">
+      <t>テイキョウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>イト</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シュヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サービスのROIを評価する財務指標</t>
+    <rPh sb="9" eb="11">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ザイム</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サービス内のクリック可能なリンクの総数</t>
+    <rPh sb="4" eb="5">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ソウスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーがサービスと接するすべての接点</t>
+    <rPh sb="10" eb="11">
+      <t>セッ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>セッテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タッチポイントは、ユーザーがサービスに関与するすべての接点のことであり、</t>
+    <rPh sb="19" eb="21">
+      <t>カンヨ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>セッテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>店舗・サポートなどのオフラインも含まれます。</t>
+    <rPh sb="0" eb="2">
+      <t>テンポ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行動データ活用における「シーケンス分析」の目的についての説明として、適切なものは次のうちどれか？</t>
+    <rPh sb="0" eb="2">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カツヨウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの感情変化を把握する</t>
+    <rPh sb="5" eb="7">
+      <t>カンジョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ハアク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーがサービス内で行った行動の流れを分析する</t>
+    <rPh sb="9" eb="10">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ブンセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが経験した失敗事例を一覧にする</t>
+    <rPh sb="5" eb="7">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジレイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サイト上でのコンテンツの人気度を確認する</t>
+    <rPh sb="3" eb="4">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニンキ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーケンス分析は、ユーザーがたどった行動の流れを分析する手法であり、</t>
+    <rPh sb="5" eb="7">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UX改善では、無駄な導線や離脱ポイントの特定に活用されます。</t>
+    <rPh sb="2" eb="4">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ムダ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ドウセン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>リダツ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>カツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「エスノグラフィー」のUXリサーチ手法の特徴として、適切なものはどれか？</t>
+    <rPh sb="17" eb="19">
+      <t>シュホウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>トクチョウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>テキセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オンラインで大規模に実施するアンケート調査</t>
+    <rPh sb="6" eb="9">
+      <t>ダイキボ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>チョウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの行動を自然な環境で観察して、文化や習慣を理解する調査</t>
+    <rPh sb="8" eb="10">
+      <t>シゼン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カンサツ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ブンカ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シュウカン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>リカイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>チョウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの反応を比較するA/Bテスト手法</t>
+    <rPh sb="5" eb="7">
+      <t>ハンノウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒカク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>短時間で多くの仮設検証を繰り返す実験的手法</t>
+    <rPh sb="0" eb="3">
+      <t>タンジカン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カセツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ケンショウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>ジッケンテキ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エスノグラフィーは文化人類学にルーツを持つリサーチ手法で、ユーザーの日常での行動を観察することにより、</t>
+    <rPh sb="9" eb="11">
+      <t>ブンカ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ジンルイガク</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>シュホウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ニチジョウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>カンサツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本質的なニーズを発見します。</t>
+    <rPh sb="0" eb="3">
+      <t>ホンシツテキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハッケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーインタビューを実施する際、インタビューガイドの設計において、重要だと思われる配慮は次のうちどれか？</t>
+    <rPh sb="11" eb="13">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ハイリョ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの深層心理を引き出せるようにするため、質問の流れを論理的に構成する</t>
+    <rPh sb="5" eb="7">
+      <t>シンソウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シンリ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>シツモン</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="29" eb="32">
+      <t>ロンリテキ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>コウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>質問はランダムに並べ、自然な会話を装う</t>
+    <rPh sb="0" eb="2">
+      <t>シツモン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ナラ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シゼン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カイワ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ヨソオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回答を誘導するように質問を組み立てる</t>
+    <rPh sb="0" eb="2">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ユウドウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シツモン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アンケートの設問をそのまま活用する</t>
+    <rPh sb="6" eb="8">
+      <t>セツモン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インタビューガイドは、ユーザーの本音を引き出すために、段階的に深堀りしていく構成が必要であり、</t>
+    <rPh sb="16" eb="18">
+      <t>ホンネ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="27" eb="30">
+      <t>ダンカイテキ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>フカボリ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>論理的な順序とオープンクエスチョンの活用がキーポイントになります。</t>
+    <rPh sb="0" eb="3">
+      <t>ロンリテキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジュンジョ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MVP（Minimum Viable Product）の考え方の説明として、適切なものは次のうちどれか？</t>
+    <rPh sb="28" eb="29">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初期コストを抑えるため、プロトタイプの品質を最低限にする</t>
+    <rPh sb="0" eb="2">
+      <t>ショキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オサ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヒンシツ</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>サイテイゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーからのフィードバックを獲得するため、最小限の機能で製品を市場投入する</t>
+    <rPh sb="15" eb="17">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>サイショウゲン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>シジョウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>トウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機能をすべて実装した完成形を最初に投入する</t>
+    <rPh sb="0" eb="2">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>トウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一度の開発で全ての要望を満たすように設計する</t>
+    <rPh sb="0" eb="2">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヨウボウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MVPは最小限の機能だけを持った製品であり、ユーザーの反応やニーズを早期に検証するためのアプローチとして、</t>
+    <rPh sb="4" eb="7">
+      <t>サイショウゲン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ハンノウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ソウキ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ケンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXグロースの初期段階に有効です。</t>
+    <rPh sb="7" eb="9">
+      <t>ショキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ダンカイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ユウコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダブルダイヤモンドモデルにおける第1の「ダイヤモンド」が担う役割として、適切なものはどれか？</t>
+    <rPh sb="16" eb="17">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ニナ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヤクワリ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>テキセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンセプトの選定とデザインパターンの展開</t>
+    <rPh sb="6" eb="8">
+      <t>センテイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>テンカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開発手順の整理とタスクの優先度設定</t>
+    <rPh sb="0" eb="2">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>テジュン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セイリ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ユウセンド</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ソリューションの構築とテストの最適化</t>
+    <rPh sb="8" eb="10">
+      <t>コウチク</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>サイテキカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>問題を発見して、正しく定義するためのプロセス</t>
+    <rPh sb="0" eb="2">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハッケン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIとUXの関係の説明について、適切なものは次のうちどれか？</t>
+    <rPh sb="6" eb="8">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIはユーザー体験そのものであり、UXと同義である</t>
+    <rPh sb="7" eb="9">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ドウギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIはUXに含まれる一つの構成要素であり、UX全体の体験を構成する一部である</t>
+    <rPh sb="6" eb="7">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>イチブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXはUIの設計後にのみ考慮される概念である</t>
+    <rPh sb="6" eb="8">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コウリョ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガイネン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIとUXは互いに無関係で、別々に設計されるべきである</t>
+    <rPh sb="6" eb="7">
+      <t>タガ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ムカンケイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ベツベツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXは体験全体であるのに対して、UIはその構成要素の一つになります。</t>
+    <rPh sb="3" eb="5">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ヒト</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -862,10 +2706,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1150,7 +2993,7 @@
   <dimension ref="B2:P46"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="15" max="16" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
@@ -1160,7 +3003,7 @@
       <c r="C2" t="s">
         <v>0</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" s="2" t="s">
         <v>53</v>
       </c>
       <c r="O2" t="s">
@@ -1209,10 +3052,10 @@
       <c r="B7">
         <v>2</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>13</v>
       </c>
-      <c r="N7" s="3" t="s">
+      <c r="N7" s="2" t="s">
         <v>53</v>
       </c>
       <c r="O7" t="s">
@@ -1460,7 +3303,7 @@
       <c r="C32" t="s">
         <v>38</v>
       </c>
-      <c r="N32" s="3" t="s">
+      <c r="N32" s="2" t="s">
         <v>53</v>
       </c>
       <c r="O32" t="s">
@@ -1512,7 +3355,7 @@
       <c r="C37" t="s">
         <v>43</v>
       </c>
-      <c r="N37" s="3" t="s">
+      <c r="N37" s="2" t="s">
         <v>53</v>
       </c>
       <c r="O37" t="s">
@@ -1617,7 +3460,7 @@
   <dimension ref="B2:W23"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="23" max="23" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:23">
@@ -1627,7 +3470,7 @@
       <c r="C2" t="s">
         <v>55</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="U2" s="2" t="s">
         <v>53</v>
       </c>
       <c r="V2" t="s">
@@ -1679,7 +3522,7 @@
       <c r="C7" t="s">
         <v>60</v>
       </c>
-      <c r="U7" s="3" t="s">
+      <c r="U7" s="2" t="s">
         <v>53</v>
       </c>
       <c r="V7" t="s">
@@ -1741,7 +3584,7 @@
       <c r="C14" t="s">
         <v>67</v>
       </c>
-      <c r="U14" s="3" t="s">
+      <c r="U14" s="2" t="s">
         <v>53</v>
       </c>
       <c r="V14" t="s">
@@ -1793,7 +3636,7 @@
       <c r="C19" t="s">
         <v>72</v>
       </c>
-      <c r="U19" s="3" t="s">
+      <c r="U19" s="2" t="s">
         <v>53</v>
       </c>
       <c r="V19" t="s">
@@ -1849,7 +3692,7 @@
   <dimension ref="B2:R27"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="18" max="18" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18">
@@ -1859,7 +3702,7 @@
       <c r="C2" t="s">
         <v>77</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P2" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Q2" t="s">
@@ -2063,7 +3906,7 @@
       <c r="C23" t="s">
         <v>98</v>
       </c>
-      <c r="P23" s="3" t="s">
+      <c r="P23" s="2" t="s">
         <v>53</v>
       </c>
       <c r="Q23" t="s">
@@ -2119,7 +3962,7 @@
   <dimension ref="B2:V23"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="22" max="22" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:22">
@@ -2129,7 +3972,7 @@
       <c r="C2" t="s">
         <v>103</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="T2" s="2" t="s">
         <v>53</v>
       </c>
       <c r="U2" t="s">
@@ -2289,7 +4132,7 @@
       <c r="C19" t="s">
         <v>119</v>
       </c>
-      <c r="T19" s="3" t="s">
+      <c r="T19" s="2" t="s">
         <v>53</v>
       </c>
       <c r="U19" t="s">
@@ -2342,30 +4185,30 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D63812B-C002-4F55-8D6D-817F494D0664}">
-  <dimension ref="B2:P71"/>
+  <dimension ref="B2:Q151"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="16" max="16" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16">
+    <row r="2" spans="2:17">
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>124</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>54</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="1">
+      <c r="Q2" s="1">
         <v>46082</v>
       </c>
     </row>
-    <row r="3" spans="2:16">
+    <row r="3" spans="2:17">
       <c r="C3" t="s">
         <v>5</v>
       </c>
@@ -2373,7 +4216,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="2:16">
+    <row r="4" spans="2:17">
       <c r="C4" t="s">
         <v>7</v>
       </c>
@@ -2381,7 +4224,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="5" spans="2:16">
+    <row r="5" spans="2:17">
       <c r="C5" t="s">
         <v>9</v>
       </c>
@@ -2389,7 +4232,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="6" spans="2:16">
+    <row r="6" spans="2:17">
       <c r="C6" t="s">
         <v>11</v>
       </c>
@@ -2397,24 +4240,24 @@
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="2:16">
+    <row r="7" spans="2:17">
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
         <v>130</v>
       </c>
-      <c r="N7" t="s">
+      <c r="O7" t="s">
         <v>54</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>8</v>
       </c>
-      <c r="P7" s="1">
+      <c r="Q7" s="1">
         <v>46082</v>
       </c>
     </row>
-    <row r="8" spans="2:16">
+    <row r="8" spans="2:17">
       <c r="C8" t="s">
         <v>5</v>
       </c>
@@ -2422,7 +4265,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="9" spans="2:16">
+    <row r="9" spans="2:17">
       <c r="C9" t="s">
         <v>7</v>
       </c>
@@ -2430,7 +4273,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="10" spans="2:16">
+    <row r="10" spans="2:17">
       <c r="C10" t="s">
         <v>9</v>
       </c>
@@ -2438,7 +4281,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="11" spans="2:16">
+    <row r="11" spans="2:17">
       <c r="C11" t="s">
         <v>11</v>
       </c>
@@ -2446,24 +4289,24 @@
         <v>134</v>
       </c>
     </row>
-    <row r="12" spans="2:16">
+    <row r="12" spans="2:17">
       <c r="B12">
         <v>3</v>
       </c>
       <c r="C12" t="s">
         <v>136</v>
       </c>
-      <c r="N12" t="s">
+      <c r="O12" t="s">
         <v>54</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>10</v>
       </c>
-      <c r="P12" s="1">
+      <c r="Q12" s="1">
         <v>46082</v>
       </c>
     </row>
-    <row r="13" spans="2:16">
+    <row r="13" spans="2:17">
       <c r="C13" t="s">
         <v>5</v>
       </c>
@@ -2471,7 +4314,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="14" spans="2:16">
+    <row r="14" spans="2:17">
       <c r="C14" t="s">
         <v>7</v>
       </c>
@@ -2479,7 +4322,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="15" spans="2:16">
+    <row r="15" spans="2:17">
       <c r="C15" t="s">
         <v>9</v>
       </c>
@@ -2487,7 +4330,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="16" spans="2:16">
+    <row r="16" spans="2:17">
       <c r="C16" t="s">
         <v>11</v>
       </c>
@@ -2495,24 +4338,24 @@
         <v>140</v>
       </c>
     </row>
-    <row r="17" spans="2:16">
+    <row r="17" spans="2:17">
       <c r="B17">
         <v>4</v>
       </c>
       <c r="C17" t="s">
         <v>142</v>
       </c>
-      <c r="N17" t="s">
+      <c r="O17" t="s">
         <v>54</v>
       </c>
-      <c r="O17" t="s">
+      <c r="P17" t="s">
         <v>12</v>
       </c>
-      <c r="P17" s="1">
+      <c r="Q17" s="1">
         <v>46082</v>
       </c>
     </row>
-    <row r="18" spans="2:16">
+    <row r="18" spans="2:17">
       <c r="C18" t="s">
         <v>5</v>
       </c>
@@ -2520,7 +4363,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="19" spans="2:16">
+    <row r="19" spans="2:17">
       <c r="C19" t="s">
         <v>7</v>
       </c>
@@ -2528,7 +4371,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="20" spans="2:16">
+    <row r="20" spans="2:17">
       <c r="C20" t="s">
         <v>9</v>
       </c>
@@ -2536,7 +4379,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="21" spans="2:16">
+    <row r="21" spans="2:17">
       <c r="C21" t="s">
         <v>11</v>
       </c>
@@ -2544,35 +4387,35 @@
         <v>145</v>
       </c>
     </row>
-    <row r="22" spans="2:16">
+    <row r="22" spans="2:17">
       <c r="B22">
         <v>5</v>
       </c>
       <c r="C22" t="s">
         <v>148</v>
       </c>
-      <c r="N22" s="3" t="s">
+      <c r="O22" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>6</v>
       </c>
-      <c r="P22" s="1">
+      <c r="Q22" s="1">
         <v>46082</v>
       </c>
     </row>
-    <row r="23" spans="2:16">
+    <row r="23" spans="2:17">
       <c r="C23" t="s">
         <v>5</v>
       </c>
       <c r="D23" t="s">
         <v>149</v>
       </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="2:16">
+    <row r="24" spans="2:17">
       <c r="C24" t="s">
         <v>7</v>
       </c>
@@ -2580,7 +4423,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="25" spans="2:16">
+    <row r="25" spans="2:17">
       <c r="C25" t="s">
         <v>9</v>
       </c>
@@ -2588,7 +4431,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="26" spans="2:16">
+    <row r="26" spans="2:17">
       <c r="C26" t="s">
         <v>11</v>
       </c>
@@ -2596,24 +4439,24 @@
         <v>152</v>
       </c>
     </row>
-    <row r="27" spans="2:16">
+    <row r="27" spans="2:17">
       <c r="B27">
         <v>6</v>
       </c>
       <c r="C27" t="s">
         <v>154</v>
       </c>
-      <c r="N27" t="s">
+      <c r="O27" t="s">
         <v>54</v>
       </c>
-      <c r="O27" t="s">
+      <c r="P27" t="s">
         <v>8</v>
       </c>
-      <c r="P27" s="1">
+      <c r="Q27" s="1">
         <v>46082</v>
       </c>
     </row>
-    <row r="28" spans="2:16">
+    <row r="28" spans="2:17">
       <c r="C28" t="s">
         <v>5</v>
       </c>
@@ -2621,7 +4464,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="29" spans="2:16">
+    <row r="29" spans="2:17">
       <c r="C29" t="s">
         <v>7</v>
       </c>
@@ -2629,7 +4472,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="30" spans="2:16">
+    <row r="30" spans="2:17">
       <c r="C30" t="s">
         <v>9</v>
       </c>
@@ -2637,7 +4480,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="31" spans="2:16">
+    <row r="31" spans="2:17">
       <c r="C31" t="s">
         <v>11</v>
       </c>
@@ -2645,35 +4488,35 @@
         <v>158</v>
       </c>
     </row>
-    <row r="32" spans="2:16">
+    <row r="32" spans="2:17">
       <c r="B32">
         <v>7</v>
       </c>
       <c r="C32" t="s">
         <v>160</v>
       </c>
-      <c r="N32" s="3" t="s">
+      <c r="O32" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="O32" t="s">
+      <c r="P32" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="1">
+      <c r="Q32" s="1">
         <v>46082</v>
       </c>
     </row>
-    <row r="33" spans="2:16">
+    <row r="33" spans="2:17">
       <c r="C33" t="s">
         <v>5</v>
       </c>
       <c r="D33" t="s">
         <v>161</v>
       </c>
-      <c r="O33" t="s">
+      <c r="P33" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="2:16">
+    <row r="34" spans="2:17">
       <c r="C34" t="s">
         <v>7</v>
       </c>
@@ -2681,7 +4524,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="35" spans="2:16">
+    <row r="35" spans="2:17">
       <c r="C35" t="s">
         <v>9</v>
       </c>
@@ -2689,7 +4532,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="36" spans="2:16">
+    <row r="36" spans="2:17">
       <c r="C36" t="s">
         <v>11</v>
       </c>
@@ -2697,24 +4540,24 @@
         <v>164</v>
       </c>
     </row>
-    <row r="37" spans="2:16">
+    <row r="37" spans="2:17">
       <c r="B37">
         <v>8</v>
       </c>
       <c r="C37" t="s">
         <v>166</v>
       </c>
-      <c r="N37" t="s">
+      <c r="O37" t="s">
         <v>54</v>
       </c>
-      <c r="O37" t="s">
+      <c r="P37" t="s">
         <v>10</v>
       </c>
-      <c r="P37" s="1">
+      <c r="Q37" s="1">
         <v>46082</v>
       </c>
     </row>
-    <row r="38" spans="2:16">
+    <row r="38" spans="2:17">
       <c r="C38" t="s">
         <v>5</v>
       </c>
@@ -2722,7 +4565,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="39" spans="2:16">
+    <row r="39" spans="2:17">
       <c r="C39" t="s">
         <v>7</v>
       </c>
@@ -2730,7 +4573,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="40" spans="2:16">
+    <row r="40" spans="2:17">
       <c r="C40" t="s">
         <v>9</v>
       </c>
@@ -2738,7 +4581,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="41" spans="2:16">
+    <row r="41" spans="2:17">
       <c r="C41" t="s">
         <v>11</v>
       </c>
@@ -2746,24 +4589,24 @@
         <v>170</v>
       </c>
     </row>
-    <row r="42" spans="2:16">
+    <row r="42" spans="2:17">
       <c r="B42">
         <v>9</v>
       </c>
       <c r="C42" t="s">
         <v>172</v>
       </c>
-      <c r="N42" t="s">
+      <c r="O42" t="s">
         <v>54</v>
       </c>
-      <c r="O42" t="s">
+      <c r="P42" t="s">
         <v>12</v>
       </c>
-      <c r="P42" s="1">
+      <c r="Q42" s="1">
         <v>46082</v>
       </c>
     </row>
-    <row r="43" spans="2:16">
+    <row r="43" spans="2:17">
       <c r="C43" t="s">
         <v>5</v>
       </c>
@@ -2771,7 +4614,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="44" spans="2:16">
+    <row r="44" spans="2:17">
       <c r="C44" t="s">
         <v>7</v>
       </c>
@@ -2779,7 +4622,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="45" spans="2:16">
+    <row r="45" spans="2:17">
       <c r="C45" t="s">
         <v>9</v>
       </c>
@@ -2787,7 +4630,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="46" spans="2:16">
+    <row r="46" spans="2:17">
       <c r="C46" t="s">
         <v>11</v>
       </c>
@@ -2795,24 +4638,24 @@
         <v>176</v>
       </c>
     </row>
-    <row r="47" spans="2:16">
+    <row r="47" spans="2:17">
       <c r="B47">
         <v>10</v>
       </c>
       <c r="C47" t="s">
         <v>178</v>
       </c>
-      <c r="N47" t="s">
+      <c r="O47" t="s">
         <v>54</v>
       </c>
-      <c r="O47" t="s">
+      <c r="P47" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="1">
+      <c r="Q47" s="1">
         <v>46082</v>
       </c>
     </row>
-    <row r="48" spans="2:16">
+    <row r="48" spans="2:17">
       <c r="C48" t="s">
         <v>5</v>
       </c>
@@ -2820,7 +4663,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="49" spans="2:16">
+    <row r="49" spans="2:17">
       <c r="C49" t="s">
         <v>7</v>
       </c>
@@ -2828,7 +4671,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="50" spans="2:16">
+    <row r="50" spans="2:17">
       <c r="C50" t="s">
         <v>9</v>
       </c>
@@ -2836,7 +4679,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="51" spans="2:16">
+    <row r="51" spans="2:17">
       <c r="C51" t="s">
         <v>11</v>
       </c>
@@ -2844,24 +4687,24 @@
         <v>182</v>
       </c>
     </row>
-    <row r="52" spans="2:16">
+    <row r="52" spans="2:17">
       <c r="B52">
         <v>11</v>
       </c>
       <c r="C52" t="s">
         <v>184</v>
       </c>
-      <c r="N52" t="s">
+      <c r="O52" t="s">
         <v>54</v>
       </c>
-      <c r="O52" t="s">
+      <c r="P52" t="s">
         <v>12</v>
       </c>
-      <c r="P52" s="1">
+      <c r="Q52" s="1">
         <v>46082</v>
       </c>
     </row>
-    <row r="53" spans="2:16">
+    <row r="53" spans="2:17">
       <c r="C53" t="s">
         <v>5</v>
       </c>
@@ -2869,7 +4712,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="54" spans="2:16">
+    <row r="54" spans="2:17">
       <c r="C54" t="s">
         <v>7</v>
       </c>
@@ -2877,7 +4720,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="55" spans="2:16">
+    <row r="55" spans="2:17">
       <c r="C55" t="s">
         <v>9</v>
       </c>
@@ -2885,7 +4728,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="56" spans="2:16">
+    <row r="56" spans="2:17">
       <c r="C56" t="s">
         <v>11</v>
       </c>
@@ -2893,24 +4736,24 @@
         <v>188</v>
       </c>
     </row>
-    <row r="57" spans="2:16">
+    <row r="57" spans="2:17">
       <c r="B57">
         <v>12</v>
       </c>
       <c r="C57" t="s">
         <v>190</v>
       </c>
-      <c r="N57" t="s">
+      <c r="O57" t="s">
         <v>54</v>
       </c>
-      <c r="O57" t="s">
+      <c r="P57" t="s">
         <v>10</v>
       </c>
-      <c r="P57" s="1">
+      <c r="Q57" s="1">
         <v>46082</v>
       </c>
     </row>
-    <row r="58" spans="2:16">
+    <row r="58" spans="2:17">
       <c r="C58" t="s">
         <v>5</v>
       </c>
@@ -2918,7 +4761,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="59" spans="2:16">
+    <row r="59" spans="2:17">
       <c r="C59" t="s">
         <v>7</v>
       </c>
@@ -2926,7 +4769,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="60" spans="2:16">
+    <row r="60" spans="2:17">
       <c r="C60" t="s">
         <v>9</v>
       </c>
@@ -2934,7 +4777,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="61" spans="2:16">
+    <row r="61" spans="2:17">
       <c r="C61" t="s">
         <v>11</v>
       </c>
@@ -2942,35 +4785,35 @@
         <v>194</v>
       </c>
     </row>
-    <row r="62" spans="2:16">
+    <row r="62" spans="2:17">
       <c r="B62">
         <v>13</v>
       </c>
       <c r="C62" t="s">
         <v>196</v>
       </c>
-      <c r="N62" s="3" t="s">
+      <c r="O62" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="O62" t="s">
+      <c r="P62" t="s">
         <v>10</v>
       </c>
-      <c r="P62" s="1">
+      <c r="Q62" s="1">
         <v>46082</v>
       </c>
     </row>
-    <row r="63" spans="2:16">
+    <row r="63" spans="2:17">
       <c r="C63" t="s">
         <v>5</v>
       </c>
       <c r="D63" t="s">
         <v>197</v>
       </c>
-      <c r="O63" t="s">
+      <c r="P63" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="2:16">
+    <row r="64" spans="2:17">
       <c r="C64" t="s">
         <v>7</v>
       </c>
@@ -2978,7 +4821,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="65" spans="2:16">
+    <row r="65" spans="2:17">
       <c r="C65" t="s">
         <v>9</v>
       </c>
@@ -2986,7 +4829,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="66" spans="2:16">
+    <row r="66" spans="2:17">
       <c r="C66" t="s">
         <v>11</v>
       </c>
@@ -2994,24 +4837,24 @@
         <v>200</v>
       </c>
     </row>
-    <row r="67" spans="2:16">
+    <row r="67" spans="2:17">
       <c r="B67">
         <v>14</v>
       </c>
       <c r="C67" t="s">
         <v>202</v>
       </c>
-      <c r="N67" t="s">
+      <c r="O67" t="s">
         <v>54</v>
       </c>
-      <c r="O67" t="s">
+      <c r="P67" t="s">
         <v>8</v>
       </c>
-      <c r="P67" s="1">
+      <c r="Q67" s="1">
         <v>46082</v>
       </c>
     </row>
-    <row r="68" spans="2:16">
+    <row r="68" spans="2:17">
       <c r="C68" t="s">
         <v>5</v>
       </c>
@@ -3019,7 +4862,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="69" spans="2:16">
+    <row r="69" spans="2:17">
       <c r="C69" t="s">
         <v>7</v>
       </c>
@@ -3027,7 +4870,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="70" spans="2:16">
+    <row r="70" spans="2:17">
       <c r="C70" t="s">
         <v>9</v>
       </c>
@@ -3035,12 +4878,805 @@
         <v>205</v>
       </c>
     </row>
-    <row r="71" spans="2:16">
+    <row r="71" spans="2:17">
       <c r="C71" t="s">
         <v>11</v>
       </c>
       <c r="D71" t="s">
         <v>206</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17">
+      <c r="B72">
+        <v>15</v>
+      </c>
+      <c r="C72" t="s">
+        <v>208</v>
+      </c>
+      <c r="O72" t="s">
+        <v>54</v>
+      </c>
+      <c r="P72" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q72" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17">
+      <c r="C73" t="s">
+        <v>5</v>
+      </c>
+      <c r="D73" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17">
+      <c r="C74" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17">
+      <c r="C75" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17">
+      <c r="C76" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17">
+      <c r="B77">
+        <v>16</v>
+      </c>
+      <c r="C77" t="s">
+        <v>214</v>
+      </c>
+      <c r="O77" t="s">
+        <v>54</v>
+      </c>
+      <c r="P77" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q77" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="78" spans="2:17">
+      <c r="C78" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17">
+      <c r="C79" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="80" spans="2:17">
+      <c r="C80" t="s">
+        <v>9</v>
+      </c>
+      <c r="D80" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="81" spans="2:17">
+      <c r="C81" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="82" spans="2:17">
+      <c r="B82">
+        <v>17</v>
+      </c>
+      <c r="C82" t="s">
+        <v>221</v>
+      </c>
+      <c r="O82" t="s">
+        <v>54</v>
+      </c>
+      <c r="P82" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q82" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="83" spans="2:17">
+      <c r="C83" t="s">
+        <v>5</v>
+      </c>
+      <c r="D83" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="84" spans="2:17">
+      <c r="C84" t="s">
+        <v>7</v>
+      </c>
+      <c r="D84" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="85" spans="2:17">
+      <c r="C85" t="s">
+        <v>9</v>
+      </c>
+      <c r="D85" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="86" spans="2:17">
+      <c r="C86" t="s">
+        <v>11</v>
+      </c>
+      <c r="D86" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="87" spans="2:17">
+      <c r="B87">
+        <v>18</v>
+      </c>
+      <c r="C87" t="s">
+        <v>227</v>
+      </c>
+      <c r="O87" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P87" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q87" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="88" spans="2:17">
+      <c r="C88" t="s">
+        <v>5</v>
+      </c>
+      <c r="D88" t="s">
+        <v>228</v>
+      </c>
+      <c r="P88" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" spans="2:17">
+      <c r="C89" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="90" spans="2:17">
+      <c r="C90" t="s">
+        <v>9</v>
+      </c>
+      <c r="D90" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="91" spans="2:17">
+      <c r="C91" t="s">
+        <v>11</v>
+      </c>
+      <c r="D91" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="92" spans="2:17">
+      <c r="B92">
+        <v>19</v>
+      </c>
+      <c r="C92" t="s">
+        <v>233</v>
+      </c>
+      <c r="O92" t="s">
+        <v>54</v>
+      </c>
+      <c r="P92" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q92" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="93" spans="2:17">
+      <c r="C93" t="s">
+        <v>5</v>
+      </c>
+      <c r="D93" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="94" spans="2:17">
+      <c r="C94" t="s">
+        <v>7</v>
+      </c>
+      <c r="D94" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="95" spans="2:17">
+      <c r="C95" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="96" spans="2:17">
+      <c r="C96" t="s">
+        <v>11</v>
+      </c>
+      <c r="D96" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="97" spans="2:17">
+      <c r="B97">
+        <v>20</v>
+      </c>
+      <c r="C97" t="s">
+        <v>239</v>
+      </c>
+      <c r="O97" t="s">
+        <v>54</v>
+      </c>
+      <c r="P97" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q97" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="98" spans="2:17">
+      <c r="C98" t="s">
+        <v>5</v>
+      </c>
+      <c r="D98" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="99" spans="2:17">
+      <c r="C99" t="s">
+        <v>7</v>
+      </c>
+      <c r="D99" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="100" spans="2:17">
+      <c r="C100" t="s">
+        <v>9</v>
+      </c>
+      <c r="D100" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="101" spans="2:17">
+      <c r="C101" t="s">
+        <v>11</v>
+      </c>
+      <c r="D101" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="102" spans="2:17">
+      <c r="B102">
+        <v>21</v>
+      </c>
+      <c r="C102" t="s">
+        <v>246</v>
+      </c>
+      <c r="O102" t="s">
+        <v>54</v>
+      </c>
+      <c r="P102" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q102" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="103" spans="2:17">
+      <c r="C103" t="s">
+        <v>5</v>
+      </c>
+      <c r="D103" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="104" spans="2:17">
+      <c r="C104" t="s">
+        <v>7</v>
+      </c>
+      <c r="D104" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="105" spans="2:17">
+      <c r="C105" t="s">
+        <v>9</v>
+      </c>
+      <c r="D105" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="106" spans="2:17">
+      <c r="C106" t="s">
+        <v>11</v>
+      </c>
+      <c r="D106" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="107" spans="2:17">
+      <c r="B107">
+        <v>22</v>
+      </c>
+      <c r="C107" t="s">
+        <v>253</v>
+      </c>
+      <c r="O107" t="s">
+        <v>54</v>
+      </c>
+      <c r="P107" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q107" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="108" spans="2:17">
+      <c r="C108" t="s">
+        <v>5</v>
+      </c>
+      <c r="D108" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="109" spans="2:17">
+      <c r="C109" t="s">
+        <v>7</v>
+      </c>
+      <c r="D109" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="110" spans="2:17">
+      <c r="C110" t="s">
+        <v>9</v>
+      </c>
+      <c r="D110" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="111" spans="2:17">
+      <c r="C111" t="s">
+        <v>11</v>
+      </c>
+      <c r="D111" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="112" spans="2:17">
+      <c r="B112">
+        <v>23</v>
+      </c>
+      <c r="C112" t="s">
+        <v>260</v>
+      </c>
+      <c r="O112" t="s">
+        <v>54</v>
+      </c>
+      <c r="P112" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q112" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="113" spans="2:17">
+      <c r="C113" t="s">
+        <v>5</v>
+      </c>
+      <c r="D113" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="114" spans="2:17">
+      <c r="C114" t="s">
+        <v>7</v>
+      </c>
+      <c r="D114" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="115" spans="2:17">
+      <c r="C115" t="s">
+        <v>9</v>
+      </c>
+      <c r="D115" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="116" spans="2:17">
+      <c r="C116" t="s">
+        <v>11</v>
+      </c>
+      <c r="D116" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="117" spans="2:17">
+      <c r="B117">
+        <v>24</v>
+      </c>
+      <c r="C117" t="s">
+        <v>267</v>
+      </c>
+      <c r="O117" t="s">
+        <v>54</v>
+      </c>
+      <c r="P117" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q117" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="118" spans="2:17">
+      <c r="C118" t="s">
+        <v>5</v>
+      </c>
+      <c r="D118" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="119" spans="2:17">
+      <c r="C119" t="s">
+        <v>7</v>
+      </c>
+      <c r="D119" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="120" spans="2:17">
+      <c r="C120" t="s">
+        <v>9</v>
+      </c>
+      <c r="D120" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="121" spans="2:17">
+      <c r="C121" t="s">
+        <v>11</v>
+      </c>
+      <c r="D121" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="122" spans="2:17">
+      <c r="B122">
+        <v>25</v>
+      </c>
+      <c r="C122" t="s">
+        <v>274</v>
+      </c>
+      <c r="O122" t="s">
+        <v>54</v>
+      </c>
+      <c r="P122" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q122" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="123" spans="2:17">
+      <c r="C123" t="s">
+        <v>5</v>
+      </c>
+      <c r="D123" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="124" spans="2:17">
+      <c r="C124" t="s">
+        <v>7</v>
+      </c>
+      <c r="D124" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="125" spans="2:17">
+      <c r="C125" t="s">
+        <v>9</v>
+      </c>
+      <c r="D125" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="126" spans="2:17">
+      <c r="C126" t="s">
+        <v>11</v>
+      </c>
+      <c r="D126" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="127" spans="2:17">
+      <c r="B127">
+        <v>26</v>
+      </c>
+      <c r="C127" t="s">
+        <v>281</v>
+      </c>
+      <c r="O127" t="s">
+        <v>54</v>
+      </c>
+      <c r="P127" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q127" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="128" spans="2:17">
+      <c r="C128" t="s">
+        <v>5</v>
+      </c>
+      <c r="D128" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="129" spans="2:17">
+      <c r="C129" t="s">
+        <v>7</v>
+      </c>
+      <c r="D129" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="130" spans="2:17">
+      <c r="C130" t="s">
+        <v>9</v>
+      </c>
+      <c r="D130" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="131" spans="2:17">
+      <c r="C131" t="s">
+        <v>11</v>
+      </c>
+      <c r="D131" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="132" spans="2:17">
+      <c r="B132">
+        <v>27</v>
+      </c>
+      <c r="C132" t="s">
+        <v>288</v>
+      </c>
+      <c r="O132" t="s">
+        <v>54</v>
+      </c>
+      <c r="P132" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q132" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="133" spans="2:17">
+      <c r="C133" t="s">
+        <v>5</v>
+      </c>
+      <c r="D133" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="134" spans="2:17">
+      <c r="C134" t="s">
+        <v>7</v>
+      </c>
+      <c r="D134" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="135" spans="2:17">
+      <c r="C135" t="s">
+        <v>9</v>
+      </c>
+      <c r="D135" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="136" spans="2:17">
+      <c r="C136" t="s">
+        <v>11</v>
+      </c>
+      <c r="D136" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="137" spans="2:17">
+      <c r="B137">
+        <v>28</v>
+      </c>
+      <c r="C137" t="s">
+        <v>295</v>
+      </c>
+      <c r="O137" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P137" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q137" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="138" spans="2:17">
+      <c r="C138" t="s">
+        <v>5</v>
+      </c>
+      <c r="D138" t="s">
+        <v>296</v>
+      </c>
+      <c r="P138" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="139" spans="2:17">
+      <c r="C139" t="s">
+        <v>7</v>
+      </c>
+      <c r="D139" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="140" spans="2:17">
+      <c r="C140" t="s">
+        <v>9</v>
+      </c>
+      <c r="D140" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="141" spans="2:17">
+      <c r="C141" t="s">
+        <v>11</v>
+      </c>
+      <c r="D141" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="142" spans="2:17">
+      <c r="B142">
+        <v>29</v>
+      </c>
+      <c r="C142" t="s">
+        <v>302</v>
+      </c>
+      <c r="O142" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P142" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q142" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="143" spans="2:17">
+      <c r="C143" t="s">
+        <v>5</v>
+      </c>
+      <c r="D143" t="s">
+        <v>303</v>
+      </c>
+      <c r="P143" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="144" spans="2:17">
+      <c r="C144" t="s">
+        <v>7</v>
+      </c>
+      <c r="D144" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="145" spans="2:17">
+      <c r="C145" t="s">
+        <v>9</v>
+      </c>
+      <c r="D145" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="146" spans="2:17">
+      <c r="C146" t="s">
+        <v>11</v>
+      </c>
+      <c r="D146" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="147" spans="2:17">
+      <c r="B147">
+        <v>30</v>
+      </c>
+      <c r="C147" t="s">
+        <v>307</v>
+      </c>
+      <c r="O147" t="s">
+        <v>54</v>
+      </c>
+      <c r="P147" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q147" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="148" spans="2:17">
+      <c r="C148" t="s">
+        <v>5</v>
+      </c>
+      <c r="D148" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="149" spans="2:17">
+      <c r="C149" t="s">
+        <v>7</v>
+      </c>
+      <c r="D149" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="150" spans="2:17">
+      <c r="C150" t="s">
+        <v>9</v>
+      </c>
+      <c r="D150" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="151" spans="2:17">
+      <c r="C151" t="s">
+        <v>11</v>
+      </c>
+      <c r="D151" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -3051,7 +5687,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D7C2EE-C8B5-4851-B670-42D9DD8D67DA}">
-  <dimension ref="B2:D29"/>
+  <dimension ref="B2:D69"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="2" spans="2:4">
@@ -3278,8 +5914,305 @@
         <v>207</v>
       </c>
     </row>
+    <row r="30" spans="2:4">
+      <c r="B30">
+        <v>15</v>
+      </c>
+      <c r="C30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4">
+      <c r="D31" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
+      <c r="B32">
+        <v>16</v>
+      </c>
+      <c r="C32" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="D33" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="D34" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35">
+        <v>17</v>
+      </c>
+      <c r="C35" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="D36" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="B37">
+        <v>18</v>
+      </c>
+      <c r="C37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="D38" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="B39">
+        <v>19</v>
+      </c>
+      <c r="C39" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="D40" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="B41">
+        <v>20</v>
+      </c>
+      <c r="C41" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4">
+      <c r="D42" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4">
+      <c r="B43">
+        <v>21</v>
+      </c>
+      <c r="C43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4">
+      <c r="D44" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="D45" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46">
+        <v>22</v>
+      </c>
+      <c r="C46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="D47" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4">
+      <c r="D48" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4">
+      <c r="B49">
+        <v>23</v>
+      </c>
+      <c r="C49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4">
+      <c r="D50" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4">
+      <c r="D51" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4">
+      <c r="B52">
+        <v>24</v>
+      </c>
+      <c r="C52" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4">
+      <c r="D53" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4">
+      <c r="D54" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4">
+      <c r="B55">
+        <v>25</v>
+      </c>
+      <c r="C55" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4">
+      <c r="D56" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4">
+      <c r="D57" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4">
+      <c r="B58">
+        <v>26</v>
+      </c>
+      <c r="C58" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4">
+      <c r="D59" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4">
+      <c r="D60" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4">
+      <c r="B61">
+        <v>27</v>
+      </c>
+      <c r="C61" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4">
+      <c r="D62" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4">
+      <c r="D63" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4">
+      <c r="B64">
+        <v>28</v>
+      </c>
+      <c r="C64" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4">
+      <c r="D65" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4">
+      <c r="D66" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4">
+      <c r="B67">
+        <v>29</v>
+      </c>
+      <c r="C67" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4">
+      <c r="B68">
+        <v>30</v>
+      </c>
+      <c r="C68" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4">
+      <c r="D69" t="s">
+        <v>312</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/UX検定_基礎.xlsx
+++ b/UX検定_基礎.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\UX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06F838A-7458-4D3A-ADFD-E05C5829A159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C586C9A4-737F-49C4-BA70-77A398F61041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="模擬" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="498">
   <si>
     <t>UXインテリジェンスが生み出す価値として重要視するものを、次の中から選びなさい。</t>
     <phoneticPr fontId="1"/>
@@ -2656,6 +2656,3404 @@
     </rPh>
     <rPh sb="26" eb="27">
       <t>ヒト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>認知バイアスのUXデザインへの影響として、適切なものは次のうちどれか？</t>
+    <rPh sb="0" eb="2">
+      <t>ニンチ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>エイキョウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>認知バイアスはUIのレイアウトにのみ影響する</t>
+    <rPh sb="0" eb="2">
+      <t>ニンチ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>エイキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが情報を処理する際の「思い込み」を理解して、それに配慮した設計が求められる</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>リカイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ハイリョ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>モト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>認知バイアスを排除することで、デザインが均一化される</t>
+    <rPh sb="0" eb="2">
+      <t>ニンチ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハイジョ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>キンイツ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>認知バイアスのあるユーザーはUX設計の対象にしない方がよい</t>
+    <rPh sb="0" eb="2">
+      <t>ニンチ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人間は合理的に判断しているようで実際には「思い込み」や「錯覚」に影響されているため、</t>
+    <rPh sb="0" eb="2">
+      <t>ニンゲン</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ゴウリテキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハンダン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>サッカク</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>エイキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXデザインではそれを前提に設計する必要があります。</t>
+    <rPh sb="11" eb="13">
+      <t>ゼンテイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インセプションデッキの目的の説明として、適切なものは次のうちどれか？</t>
+    <rPh sb="11" eb="13">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー調査の分析結果を記録するため</t>
+    <rPh sb="4" eb="6">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>キロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロジェクトの初期段階において、関係者間の共通理解を得るため</t>
+    <rPh sb="7" eb="9">
+      <t>ショキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ダンカイ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>カンケイシャ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>キョウツウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>リカイ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>エ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンセプトの検証後に、リリース判断を下すため</t>
+    <rPh sb="6" eb="8">
+      <t>ケンショウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ハンダン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>クダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スプリントごとの振り返り資料として使用するため</t>
+    <rPh sb="8" eb="9">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インセプションデッキは、チームの目標や価値観を言語化して、</t>
+    <rPh sb="16" eb="18">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>カチカン</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>ゲンゴカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>関係者全員が共通認識を持つための資料です。</t>
+    <rPh sb="0" eb="3">
+      <t>カンケイシャ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゼンイン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キョウツウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ニンシキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DevOpsやDesignOpsがUXに貢献する理由として、適切なものは次のうちどれか？</t>
+    <rPh sb="20" eb="22">
+      <t>コウケン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>リユウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイナーがエンジニアのタスクを肩代わりするため</t>
+    <rPh sb="16" eb="18">
+      <t>カタガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイン・開発・運用を連携させて、UX改善を高速で回す仕組みを整えるため</t>
+    <rPh sb="5" eb="7">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ウンヨウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>レンケイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>コウソク</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>シク</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>トトノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インフラ運用における負荷分散を目的とした戦略であるため</t>
+    <rPh sb="4" eb="6">
+      <t>ウンヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="14">
+      <t>フカブンサン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>センリャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザインコストの削減を第一に優先する運用方針であるため</t>
+    <rPh sb="8" eb="10">
+      <t>サクゲン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ダイイチ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ユウセン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ウンヨウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ホウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DevOps/DesignOpsは、デザイン・開発・運用を統合して、</t>
+    <rPh sb="23" eb="25">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ウンヨウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>トウゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チーム全体でUX改善を継続的に推進するためのマインド、構成のことです。</t>
+    <rPh sb="3" eb="5">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ケイゾクテキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>スイシン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>コウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「反復デザイン（Iterative Design）」の特徴の説明として、適切なものは次のうちどれか？</t>
+    <rPh sb="1" eb="3">
+      <t>ハンプク</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>トクチョウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完成度の高い成果物を一発で仕上げるプロセス</t>
+    <rPh sb="0" eb="3">
+      <t>カンセイド</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>セイカブツ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イッパツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>組織的な決済を経て1回で完成させる手法</t>
+    <rPh sb="0" eb="3">
+      <t>ソシキテキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケッサイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヘ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザインの方向性を固定してから作りこむスタイル</t>
+    <rPh sb="5" eb="8">
+      <t>ホウコウセイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コテイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストフィードバックを繰り返しながら改善していくアプローチ</t>
+    <rPh sb="11" eb="12">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>反復デザインとは、「作る→試す→修正する」を繰り返すプロセスであり、</t>
+    <rPh sb="0" eb="2">
+      <t>ハンプク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>タメ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>カエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXデザインにおける学習と改善の基本的な手法です。</t>
+    <rPh sb="10" eb="12">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>キホンテキ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロスペクト理論に基づくUX設計として、適切なものは次のうちどれか？</t>
+    <rPh sb="6" eb="8">
+      <t>リロン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中立的な表現で判断のバイアスを排除する</t>
+    <rPh sb="0" eb="3">
+      <t>チュウリツテキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハンダン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ハイジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利得より損失の提示を優先して、行動を引き出す構成にする</t>
+    <rPh sb="0" eb="2">
+      <t>リトク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ソンシツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>テイジ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ユウセン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>コウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>提示順序によってユーザーの選択を誤らせる</t>
+    <rPh sb="0" eb="2">
+      <t>テイジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジュンジョ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>アヤマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>損失を隠し、利得だけを誇張して伝える</t>
+    <rPh sb="0" eb="2">
+      <t>ソンシツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>リトク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コチョウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロスペクト理論では、人は、損失を避けたいという心理に強く反応するため、</t>
+    <rPh sb="6" eb="8">
+      <t>リロン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ソンシツ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シンリ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ツヨ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ハンノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UX設計では、損失の明示や損失回避を強調することで行動を促すことがあります。</t>
+    <rPh sb="2" eb="4">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ソンシツ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>メイジ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ソンシツ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カイヒ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>キョウチョウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ウナガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UX評価におけるKPI設計で重要視されるべき観点は、次のうちどれか？</t>
+    <rPh sb="2" eb="4">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>ジュウヨウシ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>カンテン</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UX以外の指標も含めてあらゆる数値を一括管理する</t>
+    <rPh sb="2" eb="4">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シヒョウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>スウチ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>イッカツ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー体験の質を定量的に測るための具体的な行動指標を設定する</t>
+    <rPh sb="4" eb="6">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>シツ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>テイリョウテキ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ハカ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>グタイテキ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シヒョウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>評価基準を固定化し、変更しないことを徹底する</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キジュン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>コテイカ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>テッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ページビューや広告表示回数のみを最優先に指標化する</t>
+    <rPh sb="7" eb="9">
+      <t>コウコク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カイスウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ユウセン</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>シヒョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXのKPIでは、コンバージョンだけでなく、操作成功率・行動継続率など、</t>
+    <rPh sb="22" eb="24">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ケイゾク</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー体験を定量的に表す指標が必要です。</t>
+    <rPh sb="4" eb="6">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>テイリョウテキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シヒョウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次のうち、シャッケルのユーザビリティの3構成要素に含まれないものはどれか？</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーティリティ（有用性）</t>
+    <rPh sb="8" eb="11">
+      <t>ユウヨウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リーダビリティ（可読性）</t>
+    <rPh sb="8" eb="11">
+      <t>カドクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ライカビリティ（好感度）</t>
+    <rPh sb="8" eb="11">
+      <t>コウカンド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザビリティ（使いやすさ）</t>
+    <rPh sb="8" eb="9">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シャッケルの定義においては「ユーティリティ（有用性）」「ユーザビリティ（使いやすさ）」</t>
+    <rPh sb="6" eb="8">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>ユウヨウセイ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ライカビリティ（好感度）」の3つが構成要素とされています。</t>
+    <rPh sb="9" eb="12">
+      <t>コウカンド</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ヨウソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>情報構造（IA）における「サイトマップ」の役割として、適切なものは次のうちどれか？</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゾウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヤクワリ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザインの方向性を定義するカラーパターン図</t>
+    <rPh sb="5" eb="8">
+      <t>ホウコウセイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ページ間の関係や構成を視覚的に表した全体設計図</t>
+    <rPh sb="3" eb="4">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>シカクテキ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>セッケイズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース設計におけるER図の一種</t>
+    <rPh sb="6" eb="8">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>イッシュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>検索エンジン最適化（SEO）におけるリンク設計書</t>
+    <rPh sb="0" eb="2">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>サイテキカ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>セッケイショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サイトマップは、ユーザーが迷うことなく情報にアクセスできるように、</t>
+    <rPh sb="13" eb="14">
+      <t>マヨ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ページ構成や階層構造を可視化した図であり、IA（情報設計）の基本です。</t>
+    <rPh sb="3" eb="5">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カイソウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウゾウ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>カシカ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>キホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXカーブを活用する目的の説明として、適切なものは次のうちどれか？</t>
+    <rPh sb="6" eb="8">
+      <t>カツヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機能改善の優先度をUXの波形から定量的に測定する</t>
+    <rPh sb="0" eb="2">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ユウセンド</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ハケイ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>テイリョウテキ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ソクテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サービスの収益曲線を分析し、LTVを算出する</t>
+    <rPh sb="5" eb="7">
+      <t>シュウエキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キョクセン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>サンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの体験を時系列でグラフ化して、感情の起伏を可視化する</t>
+    <rPh sb="5" eb="7">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>ジケイレツ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カンジョウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>キフク</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>カシカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの移動距離をマッピングしてUXを評価する</t>
+    <rPh sb="5" eb="7">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ヒョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXカーブは、ユーザーの体験を時間軸で可視化して、どのタイミングでポジティブまたはネガティブな</t>
+    <rPh sb="12" eb="14">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>ジカンジク</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>カシカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>感情が生じたかを明らかにするツールです。</t>
+    <rPh sb="0" eb="2">
+      <t>カンジョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ショウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>アキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人間中心設計（HCD）プロセスにおけるユーザー要求定義の役割として、適切なものは次のうちどれか？</t>
+    <rPh sb="0" eb="2">
+      <t>ニンゲン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>チュウシン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヨウキュウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ヤクワリ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIの配色やレイアウトを定義する作業</t>
+    <rPh sb="3" eb="5">
+      <t>ハイショク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>サギョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイナー個人の感覚で優先事項を決める工程</t>
+    <rPh sb="5" eb="7">
+      <t>コジン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンカク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ユウセン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジコウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>コウテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実装スケジュールを定める工程</t>
+    <rPh sb="0" eb="2">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>サダ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コウテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの文脈ゴールを基に、設計に必要な条件を明確にする</t>
+    <rPh sb="5" eb="7">
+      <t>ブンミャク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>メイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー要求定義は、ユーザー調査によって得られたニーズや課題を基に、製品やサービスに</t>
+    <rPh sb="4" eb="6">
+      <t>ヨウキュウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>エ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>セイヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>求められる要件を具体化するプロセスです。</t>
+    <rPh sb="0" eb="1">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヨウケン</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>グタイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMO（Online Merges with Offline）の概念の説明として、適切なものは次のうちどれか？</t>
+    <rPh sb="32" eb="34">
+      <t>ガイネン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オンラインとオフラインを完全に分けて体験設計を行う</t>
+    <rPh sb="12" eb="14">
+      <t>カンゼン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オフライン体験のみを最適化するためのUI設計手法</t>
+    <rPh sb="5" eb="7">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>サイテキカ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オンライン広告に依存してリアル店舗の導線を削減する手法</t>
+    <rPh sb="5" eb="7">
+      <t>コウコク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>イゾン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>テンポ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ドウセン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>サクゲン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「オンラインとオフラインの融合」という意味であり、リアルタイムな一貫体験を提供する考え方</t>
+    <rPh sb="13" eb="15">
+      <t>ユウゴウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>イミ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>イッカン</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>テイキョウ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>カタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMOは「オンラインとオフラインの融合」という意味であり、どちらかを補完するのではなく、</t>
+    <rPh sb="17" eb="19">
+      <t>ユウゴウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>イミ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ホカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>体験の境界をなくして、より良い顧客体験を目指すマーケティング戦略です。</t>
+    <rPh sb="0" eb="2">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キョウカイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コキャク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>メザ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>センリャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXにおいて「データリテラシー」が重要とされる理由として、はどれか？</t>
+    <rPh sb="17" eb="19">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>リユウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>統計学の専門知識がなければUX改善は不可能なため</t>
+    <rPh sb="0" eb="3">
+      <t>トウケイガク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センモン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チシキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>フカノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー行動や満足度の変化を正確に読み取り、改善につなげる力が求められるため</t>
+    <rPh sb="4" eb="6">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>マンゾクド</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セイカク</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>チカラ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>モト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>数字を信頼せず、感覚でUXを判断すべきだから</t>
+    <rPh sb="0" eb="2">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シンライ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンカク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハンダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データは分析部門に任せ、デザイナーは関与しない方が効率的なため</t>
+    <rPh sb="4" eb="6">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>マカ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カンヨ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>コウリツテキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXデザインでも、定量・定性データを正確に読み取る力は必須であり、</t>
+    <rPh sb="9" eb="11">
+      <t>テイリョウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>テイセイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>セイカク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>チカラ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ヒッス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仮説検証や施策判断のための源泉になります。</t>
+    <rPh sb="0" eb="2">
+      <t>カセツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケンショウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シサク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハンダン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ゲンセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユニバーサルデザインの考え方として、適切なものは次のうちどれか？</t>
+    <rPh sb="11" eb="12">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>障がい者専用のUIを別で用意すること</t>
+    <rPh sb="0" eb="1">
+      <t>ショウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>センヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヨウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デバイスごとに異なる操作性を提供すること</t>
+    <rPh sb="7" eb="8">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ソウサセイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>テイキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>年齢・性別・身体的能力などに関わらず、だれでも使える設計を目指すこと</t>
+    <rPh sb="0" eb="2">
+      <t>ネンレイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>セイベツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シンタイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ノウリョク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カカ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>メザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特定ターゲットに限定したエキスパート向けのUIを設計すること</t>
+    <rPh sb="0" eb="2">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユニバーサルデザインは「すべての人にとって使いやすい」を目指すコンセプトであり、</t>
+    <rPh sb="16" eb="17">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>メザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アクセシビリティとも密接な関係がある概念です。</t>
+    <rPh sb="10" eb="12">
+      <t>ミッセツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ガイネン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>認知負荷が高いUI設計に見られがちな特徴は、次のうちどれか？</t>
+    <rPh sb="0" eb="2">
+      <t>ニンチ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>フカ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>トクチョウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>色数や装飾が少なく、直感的に操作しやすい</t>
+    <rPh sb="0" eb="2">
+      <t>イロスウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ソウショク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>スク</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>チョッカンテキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ソウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示内容が少なく、余白が広く取られている</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>スク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヨハク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ヒロ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>情報量が多く、選択肢や操作が一度に提示されている</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>テイジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイコンやラベルが明確で、導線が視覚的に誘導されている</t>
+    <rPh sb="9" eb="11">
+      <t>メイカク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ドウセン</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>シカクテキ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ユウドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>認知負荷とは、ユーザーが情報を処理するときに感じる負担であり、選択肢が多く、</t>
+    <rPh sb="0" eb="2">
+      <t>ニンチ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>フカ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>フタン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>オオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>情報が整理されていないUIは、この負荷を増やすことになります。</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>セイリ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>フカ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「デザインシステム」の目的についての説明として、適切なものは次のうちどれか？</t>
+    <rPh sb="11" eb="13">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>各プロジェクトで自由にUIを構成できるようにする</t>
+    <rPh sb="0" eb="1">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジユウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>コウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザインの属人生を高めて独創的に仕上げる</t>
+    <rPh sb="5" eb="6">
+      <t>ゾク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジンセイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ドクソウテキ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クラウド上にプロトタイプを保存するための仕組み</t>
+    <rPh sb="4" eb="5">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>統一されたルールとコンポーネントでUI・UXの一貫性を保つ</t>
+    <rPh sb="0" eb="2">
+      <t>トウイツ</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>イッカンセイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>タモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザインシステムはUI・UXの共通基盤であり、複数のチームでも一貫性があるデザインを保てるように、</t>
+    <rPh sb="15" eb="17">
+      <t>キョウツウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>キバン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>フクスウ</t>
+    </rPh>
+    <rPh sb="31" eb="34">
+      <t>イッカンセイ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>タモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ガイドラインやコンポーネントを共有します。</t>
+    <rPh sb="15" eb="17">
+      <t>キョウユウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの主観的評価を収集する手法として、適切なものは次のうちどれか？</t>
+    <rPh sb="5" eb="8">
+      <t>シュカンテキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シュウシュウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シュホウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒートマップを用いて注視エリアを把握する</t>
+    <rPh sb="7" eb="8">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>チュウシ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ハアク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アンケートにより満足度や感情を数値化する</t>
+    <rPh sb="8" eb="11">
+      <t>マンゾクド</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カンジョウ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>スウチカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>操作ログを記録して行動傾向を分析する</t>
+    <rPh sb="0" eb="2">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ケイコウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ブンセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フォールバックとして業務指示書を見直す</t>
+    <rPh sb="10" eb="12">
+      <t>ギョウム</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>シジショ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ミナオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>主観評価とは、アンケートなどで、ユーザーが感じた満足度や感情を自己申告することにより、</t>
+    <rPh sb="0" eb="2">
+      <t>シュカン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>マンゾクド</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>カンジョウ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ジコ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>シンコク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それを数値化することです。</t>
+    <rPh sb="3" eb="6">
+      <t>スウチカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXリサーチにおける「行動ギャップ」の説明として、適切なものは次のうちどれか？</t>
+    <rPh sb="11" eb="13">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サイトの表示速度によって発生するユーザー離脱の傾向</t>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>リダツ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ケイコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーがインタビューで話した内容と実際の行動が一致していない現象</t>
+    <rPh sb="12" eb="13">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>イッチ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ゲンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開発チームが把握していない未検出の行動パターン</t>
+    <rPh sb="0" eb="2">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハアク</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ミケンシュツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>コウドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが1度も利用しなかった機能との距離感</t>
+    <rPh sb="6" eb="7">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>キョリカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行動ギャップとは、ユーザーが言ったことと実際の行動の間にズレがあることです。</t>
+    <rPh sb="0" eb="2">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>アイダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>情報アーキテクチャ（IA）における「カードソート法」の目的として、適切なものは次のうちどれか？</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンテンツの視覚的表現を整えること</t>
+    <rPh sb="6" eb="8">
+      <t>シカク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>トトノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>情報の重要度に応じて配色を調整すること</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ジュウヨウド</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ハイショク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザインの方向性を図形化してプレゼン資料にすること</t>
+    <rPh sb="5" eb="7">
+      <t>ホウコウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ズケイカ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの視点により情報の分類やグルーピングを行うこと</t>
+    <rPh sb="5" eb="7">
+      <t>シテン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ブンルイ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カードソートとは、ユーザーに情報カードを分類してもらい、</t>
+    <rPh sb="14" eb="16">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ブンルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自然なグルーピングや情報構造を見つける手法です。</t>
+    <rPh sb="0" eb="2">
+      <t>シゼン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コウゾウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザビリティテストの「回顧法」の手法についての説明として、適切なものは次のうちどれか？</t>
+    <rPh sb="12" eb="14">
+      <t>カイコ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シュホウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーに操作しながら感じたことを逐一発話してもらう</t>
+    <rPh sb="5" eb="7">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>チクイチ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ハツワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの行動をリアルタイムで録画し、後から専門家が分析する</t>
+    <rPh sb="5" eb="7">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ロクガ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>センモンカ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ブンセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト終了後、ユーザーに体験を振り返ってもらいながら感想を聞き出す</t>
+    <rPh sb="3" eb="6">
+      <t>シュウリョウゴ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>カンソウ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開発チームが過去の類似プロジェクトを参考に振り返る手法</t>
+    <rPh sb="0" eb="2">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ルイジ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>サンコウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回顧法は、テスト終了後、ユーザーに自分の判断や行動を思い出してもらい、</t>
+    <rPh sb="0" eb="2">
+      <t>カイコ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>シュウリョウゴ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ハンダン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>思考過程などを引き出すための手法です。</t>
+    <rPh sb="0" eb="2">
+      <t>シコウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カテイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UX改善のKPIとして「LTV（顧客生涯価値）」が重要視される理由として、適切なものはどれか？</t>
+    <rPh sb="2" eb="4">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>コキャク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ショウガイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カチ</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>ジュウヨウシ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>リユウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>テキセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンテンツ消費量が少ないユーザーの割合を測るため</t>
+    <rPh sb="5" eb="8">
+      <t>ショウヒリョウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>スク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ワリアイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ハカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>広告費削減のために初回購入だけを重視できるため</t>
+    <rPh sb="0" eb="3">
+      <t>コウコクヒ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サクゲン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ショカイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウニュウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジュウシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>長期的な顧客関係から取得可能な価値を定量化できるため</t>
+    <rPh sb="0" eb="3">
+      <t>チョウキテキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コキャク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カチ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>テイリョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー数の総計をリアルタイムで取得できるため</t>
+    <rPh sb="4" eb="5">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ソウケイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LTV（Life Time Value）は、ユーザーが長期的に生み出す価値を示す指標であり、</t>
+    <rPh sb="27" eb="30">
+      <t>チョウキテキ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>カチ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>シメ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>シヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXグロースでは短期的な結果よりも継続的な関係性が重視されます。</t>
+    <rPh sb="8" eb="11">
+      <t>タンキテキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>ケイゾクテキ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>カンケイセイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ジュウシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの「期待値」がUXに与える影響として、適切なものは次のうちどれか？</t>
+    <rPh sb="6" eb="9">
+      <t>キタイチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>エイキョウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>期待が大きいほど、体験満足度は常に高くなる</t>
+    <rPh sb="0" eb="2">
+      <t>キタイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>マンゾクド</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツネ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>タカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>期待と実体験のギャップが、満足度や再利用意欲につながる</t>
+    <rPh sb="0" eb="2">
+      <t>キタイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ジツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>マンゾクド</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>サイリヨウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>イヨク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サービス内容を過剰にアピールすることで期待値を引き上げるべきである</t>
+    <rPh sb="4" eb="6">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カジョウ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>キタイチ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>期待値はユーザーによって変わるため、設計では無視する</t>
+    <rPh sb="0" eb="3">
+      <t>キタイチ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ムシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXにおいては、期待していた通りだったかどうかが満足度につながります。</t>
+    <rPh sb="8" eb="10">
+      <t>キタイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>マンゾクド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>期待値を正しく管理することが重要なUX戦略になります。</t>
+    <rPh sb="0" eb="3">
+      <t>キタイチ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>センリャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>KPI改善のためにA/Bテストを設計する場合、最初に行うべきことは、次のうちどれか？</t>
+    <rPh sb="3" eb="5">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー行動と指標に基づいた明確な仮説を立てる</t>
+    <rPh sb="4" eb="6">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シヒョウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>メイカク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カセツ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>予算に応じて仮説なしで複数パターンを用意する</t>
+    <rPh sb="0" eb="2">
+      <t>ヨサン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カセツ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>フクスウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヨウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成果が出そうなアイデアをランダムに試す</t>
+    <rPh sb="0" eb="2">
+      <t>セイカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>タメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト結果が良かった方をすぐに本番反映する</t>
+    <rPh sb="3" eb="5">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ホンバン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ハンエイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A/Bテストは仮説検証型のアプローチであり、どうして変更が効果的か、</t>
+    <rPh sb="7" eb="9">
+      <t>カセツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ケンショウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="29" eb="32">
+      <t>コウカテキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>どの様な行動が変わるのかという仮説設定が重要になります。</t>
+    <rPh sb="2" eb="3">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カセツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「オズの魔法使い」と呼ばれるプロトタイプ手法の特徴として、適切なものは次のうちどれか？</t>
+    <rPh sb="4" eb="7">
+      <t>マホウツカ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シュホウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>トクチョウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実際のUIコードを先に構築することで、動作確認を行う手法</t>
+    <rPh sb="0" eb="2">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウチク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ドウサ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>裏側で人間が仕組みを操作し、まるで完成品のように見せる手法</t>
+    <rPh sb="0" eb="2">
+      <t>ウラガワ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ニンゲン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>カンセイヒン</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイナーがプロトタイプを実演しながら操作する手法</t>
+    <rPh sb="13" eb="15">
+      <t>ジツエン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ハイファイなUIを用いたABテスト用プロトタイプを作る方法</t>
+    <rPh sb="9" eb="10">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オズの魔法使い法は、ユーザーには完成品のように見せながら、実際には人が裏で操作する</t>
+    <rPh sb="3" eb="5">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヒン</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ウラ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ソウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロトタイピング手法のことで、早期検証に有効とされています。</t>
+    <rPh sb="8" eb="10">
+      <t>シュホウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ソウキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ケンショウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ユウコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「タスク分析」の目的についての説明として、適切なものは次のうちどれか？</t>
+    <rPh sb="4" eb="6">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの職務内容を可視化する</t>
+    <rPh sb="5" eb="7">
+      <t>ショクム</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>カシカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが目的を達成するための行動ステップを可視化する</t>
+    <rPh sb="5" eb="7">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>タッセイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>カシカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>操作の成功率を数値的に測る</t>
+    <rPh sb="0" eb="2">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>スウチ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ハカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIパーツごとの配置を最適化するための調査</t>
+    <rPh sb="8" eb="10">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サイテキ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>チョウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスク分析は、ユーザーがどんな手順で目的を達成するかを明確にする手法であり、</t>
+    <rPh sb="3" eb="5">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>テジュン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>タッセイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>メイカク</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>効率性やユーザー迷いの多少を評価できます。</t>
+    <rPh sb="0" eb="2">
+      <t>コウリツ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>マヨ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>タショウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UX視点でコンバージョン改善における有効なアプローチは次のうちどれか？</t>
+    <rPh sb="2" eb="4">
+      <t>シテン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ユウコウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボタンの色や形を目立たせることでユーザーを誘導する</t>
+    <rPh sb="4" eb="5">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カタチ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>メダ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ユウドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面の遷移数を意図的に増やし、情報を繰り返し見せる</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>イトテキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの心配や迷いを減らすため、流れ全体を明確に設計する</t>
+    <rPh sb="5" eb="7">
+      <t>シンパイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>マヨ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ヘ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>メイカク</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用規約や注意事項は目立たないように小さく表示する</t>
+    <rPh sb="0" eb="2">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キヤク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>チュウイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジコウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>メダ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>チイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンバージョン率を高めるには、迷うことなく進められるUXが重要です。</t>
+    <rPh sb="7" eb="8">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>マヨ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ペルソナ設計ではまり込みやすい誤用として、適切なものは次のうちどれか？</t>
+    <rPh sb="4" eb="6">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ゴヨウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>調査データに基づき、具体的なニーズを表現する</t>
+    <rPh sb="0" eb="2">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>グタイテキ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイナーやチームの主観のみで自由にキャラクターを作る</t>
+    <rPh sb="10" eb="12">
+      <t>シュカン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジユウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>架空の人物として描写する</t>
+    <rPh sb="0" eb="2">
+      <t>カクウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジンブツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ビョウシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実在のインタビュー対象者をモデル化する</t>
+    <rPh sb="0" eb="2">
+      <t>ジツザイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ペルソナは実際の調査データによる仮想ユーザー像でなければならず、</t>
+    <rPh sb="5" eb="7">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カソウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>主観的に創作すると現実との乖離が生じる可能性があります。</t>
+    <rPh sb="0" eb="3">
+      <t>シュカンテキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ソウサク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ゲンジツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カイリ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ショウ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>カノウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行動ログに基づくKPI設計において、留意すべきことは、次のうちどれか？</t>
+    <rPh sb="0" eb="2">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>リュウイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー行動とサービス体験の関連性を意識しながら指標を設計すること</t>
+    <rPh sb="4" eb="6">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>カンレンセイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>イシキ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シヒョウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設計者の感覚的な指標をそのままKPIとすること</t>
+    <rPh sb="0" eb="3">
+      <t>セッケイシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カンカク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すべてのユーザーに共通の指標を使うこと</t>
+    <rPh sb="9" eb="11">
+      <t>キョウツウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シヒョウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>KPIは事業側が決めるもので、UXチームは関与しないこと</t>
+    <rPh sb="4" eb="6">
+      <t>ジギョウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カンヨ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4185,7 +7583,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D63812B-C002-4F55-8D6D-817F494D0664}">
-  <dimension ref="B2:Q151"/>
+  <dimension ref="B2:Q286"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="17" max="17" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -5679,6 +9077,1338 @@
         <v>311</v>
       </c>
     </row>
+    <row r="152" spans="2:17">
+      <c r="B152">
+        <v>31</v>
+      </c>
+      <c r="C152" t="s">
+        <v>313</v>
+      </c>
+      <c r="O152" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P152" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q152" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="153" spans="2:17">
+      <c r="C153" t="s">
+        <v>5</v>
+      </c>
+      <c r="D153" t="s">
+        <v>314</v>
+      </c>
+      <c r="P153" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="154" spans="2:17">
+      <c r="C154" t="s">
+        <v>7</v>
+      </c>
+      <c r="D154" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="155" spans="2:17">
+      <c r="C155" t="s">
+        <v>9</v>
+      </c>
+      <c r="D155" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="156" spans="2:17">
+      <c r="C156" t="s">
+        <v>11</v>
+      </c>
+      <c r="D156" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="157" spans="2:17">
+      <c r="B157">
+        <v>32</v>
+      </c>
+      <c r="C157" t="s">
+        <v>320</v>
+      </c>
+      <c r="O157" t="s">
+        <v>54</v>
+      </c>
+      <c r="P157" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q157" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="158" spans="2:17">
+      <c r="C158" t="s">
+        <v>5</v>
+      </c>
+      <c r="D158" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="159" spans="2:17">
+      <c r="C159" t="s">
+        <v>7</v>
+      </c>
+      <c r="D159" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="160" spans="2:17">
+      <c r="C160" t="s">
+        <v>9</v>
+      </c>
+      <c r="D160" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="161" spans="2:17">
+      <c r="C161" t="s">
+        <v>11</v>
+      </c>
+      <c r="D161" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="162" spans="2:17">
+      <c r="B162">
+        <v>33</v>
+      </c>
+      <c r="C162" t="s">
+        <v>327</v>
+      </c>
+      <c r="O162" t="s">
+        <v>54</v>
+      </c>
+      <c r="P162" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q162" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="163" spans="2:17">
+      <c r="C163" t="s">
+        <v>5</v>
+      </c>
+      <c r="D163" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="164" spans="2:17">
+      <c r="C164" t="s">
+        <v>7</v>
+      </c>
+      <c r="D164" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="165" spans="2:17">
+      <c r="C165" t="s">
+        <v>9</v>
+      </c>
+      <c r="D165" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="166" spans="2:17">
+      <c r="C166" t="s">
+        <v>11</v>
+      </c>
+      <c r="D166" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="167" spans="2:17">
+      <c r="B167">
+        <v>34</v>
+      </c>
+      <c r="C167" t="s">
+        <v>334</v>
+      </c>
+      <c r="O167" t="s">
+        <v>54</v>
+      </c>
+      <c r="P167" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q167" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="168" spans="2:17">
+      <c r="C168" t="s">
+        <v>5</v>
+      </c>
+      <c r="D168" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="169" spans="2:17">
+      <c r="C169" t="s">
+        <v>7</v>
+      </c>
+      <c r="D169" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="170" spans="2:17">
+      <c r="C170" t="s">
+        <v>9</v>
+      </c>
+      <c r="D170" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="171" spans="2:17">
+      <c r="C171" t="s">
+        <v>11</v>
+      </c>
+      <c r="D171" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="172" spans="2:17">
+      <c r="B172">
+        <v>35</v>
+      </c>
+      <c r="C172" t="s">
+        <v>341</v>
+      </c>
+      <c r="O172" t="s">
+        <v>54</v>
+      </c>
+      <c r="P172" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q172" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="173" spans="2:17">
+      <c r="C173" t="s">
+        <v>5</v>
+      </c>
+      <c r="D173" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="174" spans="2:17">
+      <c r="C174" t="s">
+        <v>7</v>
+      </c>
+      <c r="D174" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="175" spans="2:17">
+      <c r="C175" t="s">
+        <v>9</v>
+      </c>
+      <c r="D175" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="176" spans="2:17">
+      <c r="C176" t="s">
+        <v>11</v>
+      </c>
+      <c r="D176" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="177" spans="2:17">
+      <c r="B177">
+        <v>36</v>
+      </c>
+      <c r="C177" t="s">
+        <v>348</v>
+      </c>
+      <c r="O177" t="s">
+        <v>54</v>
+      </c>
+      <c r="P177" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q177" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="178" spans="2:17">
+      <c r="C178" t="s">
+        <v>5</v>
+      </c>
+      <c r="D178" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="179" spans="2:17">
+      <c r="C179" t="s">
+        <v>7</v>
+      </c>
+      <c r="D179" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="180" spans="2:17">
+      <c r="C180" t="s">
+        <v>9</v>
+      </c>
+      <c r="D180" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="181" spans="2:17">
+      <c r="C181" t="s">
+        <v>11</v>
+      </c>
+      <c r="D181" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="182" spans="2:17">
+      <c r="B182">
+        <v>37</v>
+      </c>
+      <c r="C182" t="s">
+        <v>355</v>
+      </c>
+      <c r="O182" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P182" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q182" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="183" spans="2:17">
+      <c r="C183" t="s">
+        <v>5</v>
+      </c>
+      <c r="D183" t="s">
+        <v>356</v>
+      </c>
+      <c r="P183" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="184" spans="2:17">
+      <c r="C184" t="s">
+        <v>7</v>
+      </c>
+      <c r="D184" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="185" spans="2:17">
+      <c r="C185" t="s">
+        <v>9</v>
+      </c>
+      <c r="D185" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="186" spans="2:17">
+      <c r="C186" t="s">
+        <v>11</v>
+      </c>
+      <c r="D186" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="187" spans="2:17">
+      <c r="B187">
+        <v>38</v>
+      </c>
+      <c r="C187" t="s">
+        <v>362</v>
+      </c>
+      <c r="O187" t="s">
+        <v>54</v>
+      </c>
+      <c r="P187" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q187" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="188" spans="2:17">
+      <c r="C188" t="s">
+        <v>5</v>
+      </c>
+      <c r="D188" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="189" spans="2:17">
+      <c r="C189" t="s">
+        <v>7</v>
+      </c>
+      <c r="D189" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="190" spans="2:17">
+      <c r="C190" t="s">
+        <v>9</v>
+      </c>
+      <c r="D190" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="191" spans="2:17">
+      <c r="C191" t="s">
+        <v>11</v>
+      </c>
+      <c r="D191" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="192" spans="2:17">
+      <c r="B192">
+        <v>39</v>
+      </c>
+      <c r="C192" t="s">
+        <v>369</v>
+      </c>
+      <c r="O192" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P192" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q192" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="193" spans="2:17">
+      <c r="C193" t="s">
+        <v>5</v>
+      </c>
+      <c r="D193" t="s">
+        <v>370</v>
+      </c>
+      <c r="P193" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="194" spans="2:17">
+      <c r="C194" t="s">
+        <v>7</v>
+      </c>
+      <c r="D194" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="195" spans="2:17">
+      <c r="C195" t="s">
+        <v>9</v>
+      </c>
+      <c r="D195" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="196" spans="2:17">
+      <c r="C196" t="s">
+        <v>11</v>
+      </c>
+      <c r="D196" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="197" spans="2:17">
+      <c r="B197">
+        <v>40</v>
+      </c>
+      <c r="C197" t="s">
+        <v>376</v>
+      </c>
+      <c r="O197" t="s">
+        <v>54</v>
+      </c>
+      <c r="P197" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q197" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="198" spans="2:17">
+      <c r="C198" t="s">
+        <v>5</v>
+      </c>
+      <c r="D198" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="199" spans="2:17">
+      <c r="C199" t="s">
+        <v>7</v>
+      </c>
+      <c r="D199" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="200" spans="2:17">
+      <c r="C200" t="s">
+        <v>9</v>
+      </c>
+      <c r="D200" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="201" spans="2:17">
+      <c r="C201" t="s">
+        <v>11</v>
+      </c>
+      <c r="D201" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="202" spans="2:17">
+      <c r="B202">
+        <v>41</v>
+      </c>
+      <c r="C202" t="s">
+        <v>383</v>
+      </c>
+      <c r="O202" t="s">
+        <v>54</v>
+      </c>
+      <c r="P202" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q202" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="203" spans="2:17">
+      <c r="C203" t="s">
+        <v>5</v>
+      </c>
+      <c r="D203" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="204" spans="2:17">
+      <c r="C204" t="s">
+        <v>7</v>
+      </c>
+      <c r="D204" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="205" spans="2:17">
+      <c r="C205" t="s">
+        <v>9</v>
+      </c>
+      <c r="D205" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="206" spans="2:17">
+      <c r="C206" t="s">
+        <v>11</v>
+      </c>
+      <c r="D206" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="207" spans="2:17">
+      <c r="B207">
+        <v>42</v>
+      </c>
+      <c r="C207" t="s">
+        <v>390</v>
+      </c>
+      <c r="O207" t="s">
+        <v>54</v>
+      </c>
+      <c r="P207" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q207" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="208" spans="2:17">
+      <c r="C208" t="s">
+        <v>5</v>
+      </c>
+      <c r="D208" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="209" spans="2:17">
+      <c r="C209" t="s">
+        <v>7</v>
+      </c>
+      <c r="D209" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="210" spans="2:17">
+      <c r="C210" t="s">
+        <v>9</v>
+      </c>
+      <c r="D210" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="211" spans="2:17">
+      <c r="C211" t="s">
+        <v>11</v>
+      </c>
+      <c r="D211" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="212" spans="2:17">
+      <c r="B212">
+        <v>43</v>
+      </c>
+      <c r="C212" t="s">
+        <v>397</v>
+      </c>
+      <c r="O212" t="s">
+        <v>54</v>
+      </c>
+      <c r="P212" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q212" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="213" spans="2:17">
+      <c r="C213" t="s">
+        <v>5</v>
+      </c>
+      <c r="D213" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="214" spans="2:17">
+      <c r="C214" t="s">
+        <v>7</v>
+      </c>
+      <c r="D214" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="215" spans="2:17">
+      <c r="C215" t="s">
+        <v>9</v>
+      </c>
+      <c r="D215" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="216" spans="2:17">
+      <c r="C216" t="s">
+        <v>11</v>
+      </c>
+      <c r="D216" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="217" spans="2:17">
+      <c r="B217">
+        <v>44</v>
+      </c>
+      <c r="C217" t="s">
+        <v>404</v>
+      </c>
+      <c r="O217" t="s">
+        <v>54</v>
+      </c>
+      <c r="P217" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q217" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="218" spans="2:17">
+      <c r="C218" t="s">
+        <v>5</v>
+      </c>
+      <c r="D218" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="219" spans="2:17">
+      <c r="C219" t="s">
+        <v>7</v>
+      </c>
+      <c r="D219" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="220" spans="2:17">
+      <c r="C220" t="s">
+        <v>9</v>
+      </c>
+      <c r="D220" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="221" spans="2:17">
+      <c r="C221" t="s">
+        <v>11</v>
+      </c>
+      <c r="D221" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="222" spans="2:17">
+      <c r="B222">
+        <v>45</v>
+      </c>
+      <c r="C222" t="s">
+        <v>411</v>
+      </c>
+      <c r="O222" t="s">
+        <v>54</v>
+      </c>
+      <c r="P222" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q222" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="223" spans="2:17">
+      <c r="C223" t="s">
+        <v>5</v>
+      </c>
+      <c r="D223" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="224" spans="2:17">
+      <c r="C224" t="s">
+        <v>7</v>
+      </c>
+      <c r="D224" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="225" spans="2:17">
+      <c r="C225" t="s">
+        <v>9</v>
+      </c>
+      <c r="D225" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="226" spans="2:17">
+      <c r="C226" t="s">
+        <v>11</v>
+      </c>
+      <c r="D226" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="227" spans="2:17">
+      <c r="B227">
+        <v>46</v>
+      </c>
+      <c r="C227" t="s">
+        <v>418</v>
+      </c>
+      <c r="O227" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P227" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q227" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="228" spans="2:17">
+      <c r="C228" t="s">
+        <v>5</v>
+      </c>
+      <c r="D228" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="229" spans="2:17">
+      <c r="C229" t="s">
+        <v>7</v>
+      </c>
+      <c r="D229" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="230" spans="2:17">
+      <c r="C230" t="s">
+        <v>9</v>
+      </c>
+      <c r="D230" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="231" spans="2:17">
+      <c r="C231" t="s">
+        <v>11</v>
+      </c>
+      <c r="D231" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="232" spans="2:17">
+      <c r="B232">
+        <v>47</v>
+      </c>
+      <c r="C232" t="s">
+        <v>425</v>
+      </c>
+      <c r="O232" t="s">
+        <v>54</v>
+      </c>
+      <c r="P232" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q232" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="233" spans="2:17">
+      <c r="C233" t="s">
+        <v>5</v>
+      </c>
+      <c r="D233" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="234" spans="2:17">
+      <c r="C234" t="s">
+        <v>7</v>
+      </c>
+      <c r="D234" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="235" spans="2:17">
+      <c r="C235" t="s">
+        <v>9</v>
+      </c>
+      <c r="D235" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="236" spans="2:17">
+      <c r="C236" t="s">
+        <v>11</v>
+      </c>
+      <c r="D236" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="237" spans="2:17">
+      <c r="B237">
+        <v>48</v>
+      </c>
+      <c r="C237" t="s">
+        <v>431</v>
+      </c>
+      <c r="O237" t="s">
+        <v>54</v>
+      </c>
+      <c r="P237" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q237" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="238" spans="2:17">
+      <c r="C238" t="s">
+        <v>5</v>
+      </c>
+      <c r="D238" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="239" spans="2:17">
+      <c r="C239" t="s">
+        <v>7</v>
+      </c>
+      <c r="D239" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="240" spans="2:17">
+      <c r="C240" t="s">
+        <v>9</v>
+      </c>
+      <c r="D240" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="241" spans="2:17">
+      <c r="C241" t="s">
+        <v>11</v>
+      </c>
+      <c r="D241" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="242" spans="2:17">
+      <c r="B242">
+        <v>49</v>
+      </c>
+      <c r="C242" t="s">
+        <v>438</v>
+      </c>
+      <c r="O242" t="s">
+        <v>54</v>
+      </c>
+      <c r="P242" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q242" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="243" spans="2:17">
+      <c r="C243" t="s">
+        <v>5</v>
+      </c>
+      <c r="D243" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="244" spans="2:17">
+      <c r="C244" t="s">
+        <v>7</v>
+      </c>
+      <c r="D244" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="245" spans="2:17">
+      <c r="C245" t="s">
+        <v>9</v>
+      </c>
+      <c r="D245" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="246" spans="2:17">
+      <c r="C246" t="s">
+        <v>11</v>
+      </c>
+      <c r="D246" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="247" spans="2:17">
+      <c r="B247">
+        <v>50</v>
+      </c>
+      <c r="C247" t="s">
+        <v>445</v>
+      </c>
+      <c r="O247" t="s">
+        <v>54</v>
+      </c>
+      <c r="P247" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q247" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="248" spans="2:17">
+      <c r="C248" t="s">
+        <v>5</v>
+      </c>
+      <c r="D248" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="249" spans="2:17">
+      <c r="C249" t="s">
+        <v>7</v>
+      </c>
+      <c r="D249" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="250" spans="2:17">
+      <c r="C250" t="s">
+        <v>9</v>
+      </c>
+      <c r="D250" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="251" spans="2:17">
+      <c r="C251" t="s">
+        <v>11</v>
+      </c>
+      <c r="D251" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="252" spans="2:17">
+      <c r="B252">
+        <v>51</v>
+      </c>
+      <c r="C252" t="s">
+        <v>452</v>
+      </c>
+      <c r="O252" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P252" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q252" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="253" spans="2:17">
+      <c r="C253" t="s">
+        <v>5</v>
+      </c>
+      <c r="D253" t="s">
+        <v>453</v>
+      </c>
+      <c r="P253" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="254" spans="2:17">
+      <c r="C254" t="s">
+        <v>7</v>
+      </c>
+      <c r="D254" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="255" spans="2:17">
+      <c r="C255" t="s">
+        <v>9</v>
+      </c>
+      <c r="D255" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="256" spans="2:17">
+      <c r="C256" t="s">
+        <v>11</v>
+      </c>
+      <c r="D256" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="257" spans="2:17">
+      <c r="B257">
+        <v>52</v>
+      </c>
+      <c r="C257" t="s">
+        <v>459</v>
+      </c>
+      <c r="O257" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P257" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q257" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="258" spans="2:17">
+      <c r="C258" t="s">
+        <v>5</v>
+      </c>
+      <c r="D258" t="s">
+        <v>460</v>
+      </c>
+      <c r="P258" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="259" spans="2:17">
+      <c r="C259" t="s">
+        <v>7</v>
+      </c>
+      <c r="D259" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="260" spans="2:17">
+      <c r="C260" t="s">
+        <v>9</v>
+      </c>
+      <c r="D260" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="261" spans="2:17">
+      <c r="C261" t="s">
+        <v>11</v>
+      </c>
+      <c r="D261" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="262" spans="2:17">
+      <c r="B262">
+        <v>53</v>
+      </c>
+      <c r="C262" t="s">
+        <v>466</v>
+      </c>
+      <c r="O262" t="s">
+        <v>54</v>
+      </c>
+      <c r="P262" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q262" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="263" spans="2:17">
+      <c r="C263" t="s">
+        <v>5</v>
+      </c>
+      <c r="D263" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="264" spans="2:17">
+      <c r="C264" t="s">
+        <v>7</v>
+      </c>
+      <c r="D264" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="265" spans="2:17">
+      <c r="C265" t="s">
+        <v>9</v>
+      </c>
+      <c r="D265" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="266" spans="2:17">
+      <c r="C266" t="s">
+        <v>11</v>
+      </c>
+      <c r="D266" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="267" spans="2:17">
+      <c r="B267">
+        <v>54</v>
+      </c>
+      <c r="C267" t="s">
+        <v>473</v>
+      </c>
+      <c r="O267" t="s">
+        <v>54</v>
+      </c>
+      <c r="P267" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q267" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="268" spans="2:17">
+      <c r="C268" t="s">
+        <v>5</v>
+      </c>
+      <c r="D268" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="269" spans="2:17">
+      <c r="C269" t="s">
+        <v>7</v>
+      </c>
+      <c r="D269" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="270" spans="2:17">
+      <c r="C270" t="s">
+        <v>9</v>
+      </c>
+      <c r="D270" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="271" spans="2:17">
+      <c r="C271" t="s">
+        <v>11</v>
+      </c>
+      <c r="D271" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="272" spans="2:17">
+      <c r="B272">
+        <v>55</v>
+      </c>
+      <c r="C272" t="s">
+        <v>480</v>
+      </c>
+      <c r="O272" t="s">
+        <v>54</v>
+      </c>
+      <c r="P272" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q272" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="273" spans="2:17">
+      <c r="C273" t="s">
+        <v>5</v>
+      </c>
+      <c r="D273" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="274" spans="2:17">
+      <c r="C274" t="s">
+        <v>7</v>
+      </c>
+      <c r="D274" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="275" spans="2:17">
+      <c r="C275" t="s">
+        <v>9</v>
+      </c>
+      <c r="D275" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="276" spans="2:17">
+      <c r="C276" t="s">
+        <v>11</v>
+      </c>
+      <c r="D276" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="277" spans="2:17">
+      <c r="B277">
+        <v>56</v>
+      </c>
+      <c r="C277" t="s">
+        <v>486</v>
+      </c>
+      <c r="O277" t="s">
+        <v>54</v>
+      </c>
+      <c r="P277" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q277" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="278" spans="2:17">
+      <c r="C278" t="s">
+        <v>5</v>
+      </c>
+      <c r="D278" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="279" spans="2:17">
+      <c r="C279" t="s">
+        <v>7</v>
+      </c>
+      <c r="D279" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="280" spans="2:17">
+      <c r="C280" t="s">
+        <v>9</v>
+      </c>
+      <c r="D280" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="281" spans="2:17">
+      <c r="C281" t="s">
+        <v>11</v>
+      </c>
+      <c r="D281" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="282" spans="2:17">
+      <c r="B282">
+        <v>57</v>
+      </c>
+      <c r="C282" t="s">
+        <v>493</v>
+      </c>
+      <c r="Q282" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="283" spans="2:17">
+      <c r="C283" t="s">
+        <v>5</v>
+      </c>
+      <c r="D283" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="284" spans="2:17">
+      <c r="C284" t="s">
+        <v>7</v>
+      </c>
+      <c r="D284" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="285" spans="2:17">
+      <c r="C285" t="s">
+        <v>9</v>
+      </c>
+      <c r="D285" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="286" spans="2:17">
+      <c r="C286" t="s">
+        <v>11</v>
+      </c>
+      <c r="D286" t="s">
+        <v>497</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5687,7 +10417,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D7C2EE-C8B5-4851-B670-42D9DD8D67DA}">
-  <dimension ref="B2:D69"/>
+  <dimension ref="B2:D146"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="2" spans="2:4">
@@ -6208,6 +10938,547 @@
     <row r="69" spans="2:4">
       <c r="D69" t="s">
         <v>312</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4">
+      <c r="B70">
+        <v>31</v>
+      </c>
+      <c r="C70" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4">
+      <c r="D71" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4">
+      <c r="D72" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4">
+      <c r="B73">
+        <v>32</v>
+      </c>
+      <c r="C73" t="s">
+        <v>7</v>
+      </c>
+      <c r="D73" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4">
+      <c r="D74" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4">
+      <c r="D75" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4">
+      <c r="B76">
+        <v>33</v>
+      </c>
+      <c r="C76" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4">
+      <c r="D77" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4">
+      <c r="D78" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4">
+      <c r="B79">
+        <v>34</v>
+      </c>
+      <c r="C79" t="s">
+        <v>11</v>
+      </c>
+      <c r="D79" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4">
+      <c r="D80" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4">
+      <c r="D81" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4">
+      <c r="B82">
+        <v>35</v>
+      </c>
+      <c r="C82" t="s">
+        <v>7</v>
+      </c>
+      <c r="D82" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4">
+      <c r="D83" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4">
+      <c r="D84" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4">
+      <c r="B85">
+        <v>36</v>
+      </c>
+      <c r="C85" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4">
+      <c r="D86" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4">
+      <c r="D87" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4">
+      <c r="B88">
+        <v>37</v>
+      </c>
+      <c r="C88" t="s">
+        <v>7</v>
+      </c>
+      <c r="D88" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4">
+      <c r="D89" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4">
+      <c r="D90" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4">
+      <c r="B91">
+        <v>38</v>
+      </c>
+      <c r="C91" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4">
+      <c r="D92" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4">
+      <c r="D93" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4">
+      <c r="B94">
+        <v>39</v>
+      </c>
+      <c r="C94" t="s">
+        <v>9</v>
+      </c>
+      <c r="D94" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4">
+      <c r="D95" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4">
+      <c r="D96" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4">
+      <c r="B97">
+        <v>40</v>
+      </c>
+      <c r="C97" t="s">
+        <v>11</v>
+      </c>
+      <c r="D97" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4">
+      <c r="D98" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4">
+      <c r="D99" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4">
+      <c r="B100">
+        <v>41</v>
+      </c>
+      <c r="C100" t="s">
+        <v>11</v>
+      </c>
+      <c r="D100" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4">
+      <c r="D101" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4">
+      <c r="D102" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4">
+      <c r="B103">
+        <v>42</v>
+      </c>
+      <c r="C103" t="s">
+        <v>7</v>
+      </c>
+      <c r="D103" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4">
+      <c r="D104" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4">
+      <c r="D105" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4">
+      <c r="B106">
+        <v>43</v>
+      </c>
+      <c r="C106" t="s">
+        <v>9</v>
+      </c>
+      <c r="D106" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="107" spans="2:4">
+      <c r="D107" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4">
+      <c r="D108" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4">
+      <c r="B109">
+        <v>44</v>
+      </c>
+      <c r="C109" t="s">
+        <v>9</v>
+      </c>
+      <c r="D109" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="110" spans="2:4">
+      <c r="D110" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="111" spans="2:4">
+      <c r="D111" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="112" spans="2:4">
+      <c r="B112">
+        <v>45</v>
+      </c>
+      <c r="C112" t="s">
+        <v>11</v>
+      </c>
+      <c r="D112" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4">
+      <c r="D113" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4">
+      <c r="D114" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4">
+      <c r="B115">
+        <v>46</v>
+      </c>
+      <c r="C115" t="s">
+        <v>7</v>
+      </c>
+      <c r="D115" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4">
+      <c r="D116" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4">
+      <c r="D117" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4">
+      <c r="B118">
+        <v>47</v>
+      </c>
+      <c r="C118" t="s">
+        <v>7</v>
+      </c>
+      <c r="D118" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4">
+      <c r="D119" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4">
+      <c r="B120">
+        <v>48</v>
+      </c>
+      <c r="C120" t="s">
+        <v>11</v>
+      </c>
+      <c r="D120" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4">
+      <c r="D121" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4">
+      <c r="D122" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4">
+      <c r="B123">
+        <v>49</v>
+      </c>
+      <c r="C123" t="s">
+        <v>9</v>
+      </c>
+      <c r="D123" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4">
+      <c r="D124" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4">
+      <c r="D125" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4">
+      <c r="B126">
+        <v>50</v>
+      </c>
+      <c r="C126" t="s">
+        <v>9</v>
+      </c>
+      <c r="D126" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4">
+      <c r="D127" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4">
+      <c r="D128" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4">
+      <c r="B129">
+        <v>51</v>
+      </c>
+      <c r="C129" t="s">
+        <v>7</v>
+      </c>
+      <c r="D129" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4">
+      <c r="D130" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4">
+      <c r="D131" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4">
+      <c r="B132">
+        <v>52</v>
+      </c>
+      <c r="C132" t="s">
+        <v>5</v>
+      </c>
+      <c r="D132" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4">
+      <c r="D133" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4">
+      <c r="D134" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4">
+      <c r="B135">
+        <v>53</v>
+      </c>
+      <c r="C135" t="s">
+        <v>7</v>
+      </c>
+      <c r="D135" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4">
+      <c r="D136" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4">
+      <c r="D137" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4">
+      <c r="B138">
+        <v>54</v>
+      </c>
+      <c r="C138" t="s">
+        <v>7</v>
+      </c>
+      <c r="D138" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4">
+      <c r="D139" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4">
+      <c r="D140" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="141" spans="2:4">
+      <c r="B141">
+        <v>55</v>
+      </c>
+      <c r="C141" t="s">
+        <v>9</v>
+      </c>
+      <c r="D141" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4">
+      <c r="D142" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4">
+      <c r="B143">
+        <v>56</v>
+      </c>
+      <c r="C143" t="s">
+        <v>7</v>
+      </c>
+      <c r="D143" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4">
+      <c r="D144" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="D145" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="B146">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/UX検定_基礎.xlsx
+++ b/UX検定_基礎.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\UX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C586C9A4-737F-49C4-BA70-77A398F61041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64DA082-D977-4086-92E7-2755AF84CFE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="模擬" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="598">
   <si>
     <t>UXインテリジェンスが生み出す価値として重要視するものを、次の中から選びなさい。</t>
     <phoneticPr fontId="1"/>
@@ -6054,6 +6054,1933 @@
     </rPh>
     <rPh sb="21" eb="23">
       <t>カンヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>KPIは、UX体験とユーザー行動のつながりを意識して設計すべきであり、</t>
+    <rPh sb="7" eb="9">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>イシキ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXに直結した指標であることが重要です。</t>
+    <rPh sb="3" eb="5">
+      <t>チョッケツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シヒョウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ジョブ理論」におけるジョブの捉え方として、適切なものは次のうちどれか？</t>
+    <rPh sb="4" eb="6">
+      <t>リロン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>トラ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業の組織図上の役割と職務</t>
+    <rPh sb="0" eb="2">
+      <t>キギョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ソシキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヤクワリ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ショクム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの職業属性に基づく課題分類</t>
+    <rPh sb="5" eb="7">
+      <t>ショクギョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ブンルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが進歩したいと望む本質的な目的や達成したい結果</t>
+    <rPh sb="5" eb="7">
+      <t>シンポ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ホンシツテキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>タッセイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスクフローの中で発生する作業単位のこと</t>
+    <rPh sb="7" eb="8">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>タンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バリュープロポジションキャンパスを活用する目的として、適切なものは次のうちどれか？</t>
+    <rPh sb="17" eb="19">
+      <t>カツヨウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>製品の画面構成を視覚的に整理すること</t>
+    <rPh sb="0" eb="2">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>シカクテキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セイリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>組織内の責任分担を定義すること</t>
+    <rPh sb="0" eb="2">
+      <t>ソシキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セキニン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ブンタン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>顧客の課題と価値を整理して、提供すべき体験を明らかにすること</t>
+    <rPh sb="0" eb="2">
+      <t>コキャク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カチ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セイリ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>テイキョウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>アキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロジェクトの実装スケジュールを管理すること</t>
+    <rPh sb="7" eb="9">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジョブ理論（Jobs To Be Done）における「ジョブ」とは、ユーザーが製品やサービスを</t>
+    <rPh sb="3" eb="5">
+      <t>リロン</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>セイヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>購入する目的そのものであり、ジョブ理論はユーザーの購入行動を理解する際に使用される理論です。</t>
+    <rPh sb="0" eb="2">
+      <t>コウニュウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>リロン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>コウニュウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>リカイ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>リロン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バリュープロポジションは、ユーザーが本当に欲しい価値とは何かを明確化するフレームワークです。</t>
+    <rPh sb="18" eb="20">
+      <t>ホントウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ホ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カチ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="31" eb="34">
+      <t>メイカクカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人間中心設計の「マインドセット」における考え方として、適切なものはどれか？</t>
+    <rPh sb="0" eb="2">
+      <t>ニンゲン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>チュウシン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>テキセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの声は重要だが、最終判断は経営者が行うべきである</t>
+    <rPh sb="5" eb="6">
+      <t>コエ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>サイシュウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハンダン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ケイエイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用者の視点を深く理解し、共創の姿勢で設計に取り組む</t>
+    <rPh sb="0" eb="3">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シテン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>フカ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>リカイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>トモ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ツクル</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シセイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイナーの感性に従って新しさを追求することが最優先である</t>
+    <rPh sb="6" eb="8">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>シタガ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ツイキュウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ユウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの発言を忠実に再現することで満足度は高まる</t>
+    <rPh sb="5" eb="7">
+      <t>ハツゲン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>チュウジツ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サイゲン</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>マンゾクド</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>タカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ｂ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人間中心設計のマインドセットでは、利用者に対する理解と共創姿勢が重視され、</t>
+    <rPh sb="0" eb="2">
+      <t>ニンゲン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>チュウシン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>リカイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>トモ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ツクル</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>シセイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ジュウシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設計のすべての工程に利用者視点を取り入れることが大切です。</t>
+    <rPh sb="0" eb="2">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コウテイ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シテン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>タイセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXにおける「世界観の体現」が重視される理由として、適切なものはどれか？</t>
+    <rPh sb="7" eb="10">
+      <t>セカイカン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>タイゲン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジュウシ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>リユウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>テキセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンテンツの世界観が体験全体に一貫して伝わることにより、ユーザーの共感と信頼を生むため</t>
+    <rPh sb="6" eb="8">
+      <t>セカイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>イッカン</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ツタ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>キョウカン</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>シンライ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>統一されたビジュアルにより、見た目での差別化ができるため</t>
+    <rPh sb="0" eb="2">
+      <t>トウイツ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>サベツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ビジネスモデルを多様化させるため、世界観は毎回変更すべきだから</t>
+    <rPh sb="8" eb="11">
+      <t>タヨウカ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>セカイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>マイカイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業やサービスの価値観が体験全体に一貫して伝わることにより、ユーザーの共感と信頼を生むため</t>
+    <rPh sb="0" eb="2">
+      <t>キギョウ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>カチカン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イッカン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ツタ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>キョウカン</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>シンライ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>世界観の体現とは、UX企画力の中核となるもので、ブランドの思想や価値観を体験全体に</t>
+    <rPh sb="0" eb="2">
+      <t>セカイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>タイゲン</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>キカクリョク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>チュウカク</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>シソウ</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>カチカン</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ゼンタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一貫して表現することです。</t>
+    <rPh sb="0" eb="2">
+      <t>イッカン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「認知的ウォークスルー」の特徴についての説明として、適切なものはどれか？</t>
+    <rPh sb="1" eb="4">
+      <t>ニンチテキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>トクチョウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>テキセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーにテストを実施し、思考を発話してもらう方法</t>
+    <rPh sb="9" eb="11">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シコウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ハツワ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>専門家がユーザーの視点で操作手順をトレースし、問題点を洗い出す手法</t>
+    <rPh sb="0" eb="3">
+      <t>センモンカ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シテン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>テジュン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>アラ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エンジニアがコードをレビューする際の思考プロセス</t>
+    <rPh sb="16" eb="17">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの無意識下の感情変化を測定する実験手法</t>
+    <rPh sb="5" eb="8">
+      <t>ムイシキ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カンジョウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ソクテイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジッケン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>認知的ウォークスルーは、UXの専門家がユーザーがどのように考えるかを想定して</t>
+    <rPh sb="0" eb="3">
+      <t>ニンチテキ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>センモンカ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ソウテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面遷移を確認して、UIの問題を発見する手法です。</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ハッケン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ユーザーリテンション（継続率）」向上のためのUX施策として、適切なものは次のうちどれか？</t>
+    <rPh sb="12" eb="14">
+      <t>ケイゾク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>コウジョウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>シサク</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初回利用者への通知を減らし、シンプルな導線を優先する</t>
+    <rPh sb="0" eb="2">
+      <t>ショカイ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ツウチ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ヘ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ドウセン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ユウセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>継続利用するほど新たな価値や楽しみが得られるUXを設計する</t>
+    <rPh sb="0" eb="2">
+      <t>ケイゾク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>アラ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>タノ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>エ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>離脱ユーザーに対して広告リターゲティングを強化する</t>
+    <rPh sb="0" eb="2">
+      <t>リダツ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウコク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用頻度に応じた価格変動で、離脱を防ぐ戦略をとる</t>
+    <rPh sb="0" eb="2">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヒンド</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カカク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヘンドウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>リダツ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>フセ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>センリャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXでリテンションを高めるには、続ける理由がUX内にある必要があるため、</t>
+    <rPh sb="10" eb="11">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>リユウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ウチ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新たな発見やメリットが得られるよう設計します。</t>
+    <rPh sb="0" eb="1">
+      <t>アラ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハッケン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>エ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サービスブループリントのメインの目的として、適切なものは次のうちどれか？</t>
+    <rPh sb="16" eb="18">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIの設計指針を定義し、コンポーネントを図解化すること</t>
+    <rPh sb="3" eb="5">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シシン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ズカイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面遷移図やワイヤーフレームとあわせてプレゼン資料をつくること</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>シリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>組織体制や役職の構成を説明するための図式</t>
+    <rPh sb="0" eb="2">
+      <t>ソシキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タイセイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヤクショク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ズシキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー体験の裏側にある業務やシステムプロセスを可視化すること</t>
+    <rPh sb="4" eb="6">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ウラガワ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ギョウム</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>カシカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サービスブループリントは、ユーザーの行動だけでなく、サービスの裏側も含めて</t>
+    <rPh sb="18" eb="20">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ウラガワ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>体験全体を設計する手法です。</t>
+    <rPh sb="0" eb="2">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXと倫理に関する考え方として、適切なものは次のうちどれか？</t>
+    <rPh sb="3" eb="5">
+      <t>リンリ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UX改善は収益性のみを重視し、ユーザーの自由は制限してもよい</t>
+    <rPh sb="2" eb="4">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>シュウエキセイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジュウシ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ジユウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>セイゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXデザインにはユーザーの尊厳や選択の自由を損なわない配慮が求められる</t>
+    <rPh sb="13" eb="15">
+      <t>ソンゲン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジユウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ソコ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ハイリョ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>モト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの行動を操る設計ができれば、それは優れたUXである</t>
+    <rPh sb="5" eb="7">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>アヤツ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>スグ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データが取得できる限り、すべての情報を活用するべきである</t>
+    <rPh sb="4" eb="6">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カギ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UX設計では、個人の尊厳、選択権、情報コントロールといった倫理的な視点が不可欠</t>
+    <rPh sb="2" eb="4">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コジン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ソンゲン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="29" eb="32">
+      <t>リンリテキ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>シテン</t>
+    </rPh>
+    <rPh sb="36" eb="39">
+      <t>フカケツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>であるとされています。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モバイルUX設計で配慮すべきポイントとして、適切なものは次のうちどれか？</t>
+    <rPh sb="6" eb="8">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ハイリョ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デスクトップと同じ情報量・構成を維持する</t>
+    <rPh sb="7" eb="8">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>イジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>操作環境や画面サイズなどに配慮して、導線や操作の最小化を意識する</t>
+    <rPh sb="0" eb="2">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ハイリョ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ドウセン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>サイショウカ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>イシキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スマートフォンは視認性が高いため、情報はできるだけ1画面に詰め込む</t>
+    <rPh sb="8" eb="11">
+      <t>シニンセイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通信環境に左右されるため、動画や動きのある表現を増やす</t>
+    <rPh sb="0" eb="2">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サユウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ドウガ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モバイルUXは、通信遅延、視認性、タップなどの制約を考慮して、</t>
+    <rPh sb="8" eb="10">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>チエン</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>シニンセイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>セイヤク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>コウリョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最小限で迷いのない導線を設計することがポイントになります。</t>
+    <rPh sb="0" eb="3">
+      <t>サイショウゲン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>マヨ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ドウセン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーリサーチでの「ダイアリー法」の特徴として、適切なものはどれか？</t>
+    <rPh sb="16" eb="17">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>トクチョウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>テキセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一対一で深く話を聞き出すインタビュー手法の一種</t>
+    <rPh sb="0" eb="3">
+      <t>イッタイイチ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>フカ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ハナシ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シュホウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>イッシュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー自身が一定期間、体験や行動などを記録して、後日分析する方法</t>
+    <rPh sb="4" eb="6">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イッテイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キカン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ゴジツ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リサーチャーが利用者を観察し続け、リアルタイムで記録する方法</t>
+    <rPh sb="7" eb="10">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カンサツ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>短時間で集中的に行うグループインタビュー手法</t>
+    <rPh sb="0" eb="3">
+      <t>タンジカン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>シュウチュウテキ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダイアリー法は、ユーザーが日常的な体験や行動を自ら記録することにより、</t>
+    <rPh sb="5" eb="6">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ニチジョウテキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ミズカ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>キロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>長期的で実生活に即したデータを取得する手法です。</t>
+    <rPh sb="0" eb="3">
+      <t>チョウキテキ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ジッセイカツ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ソク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒューリスティック評価の原則として、適切なものは次のうちどれか？</t>
+    <rPh sb="9" eb="11">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ゲンソク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>評価者はユーザー調査の知識を持たないほうが良い</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>チシキ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>制御性、一貫性、エラーメッセージなどの経験則を基にした原則でUIを評価する</t>
+    <rPh sb="0" eb="3">
+      <t>セイギョセイ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>イッカンセイ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>ケイケンソク</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ゲンソク</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ヒョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実際のユーザーが操作しないため、信頼性が低い</t>
+    <rPh sb="0" eb="2">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>シンライセイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ヒク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>視覚的デザインの美しさを主観で評価する</t>
+    <rPh sb="0" eb="2">
+      <t>シカク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シュカン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒューリスティック評価は、UXの専門家が経験則に基づいてUIをチェックする方法であり、</t>
+    <rPh sb="9" eb="11">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>センモンカ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>ケイケンソク</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>代表的なものにニールセンの10原則などがあります。</t>
+    <rPh sb="0" eb="3">
+      <t>ダイヒョウテキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ゲンソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー観察の実施におけるスタンスとして、適切なものは次のうちどれか？</t>
+    <rPh sb="4" eb="6">
+      <t>カンサツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>できるだけ観察対象者に話しかけ、意図を確認する</t>
+    <rPh sb="5" eb="7">
+      <t>カンサツ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>タイショウシャ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>イト</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あらかじめ設定した仮説を前提に、目的の行動のみを観察する</t>
+    <rPh sb="5" eb="7">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カセツ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ゼンテイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カンサツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>観察中に見られた課題を即座にフィードバックし改善指示を出す</t>
+    <rPh sb="0" eb="3">
+      <t>カンサツチュウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ソクザ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シジ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの自然な行動を妨げず、ひそかに記録し、分析する</t>
+    <rPh sb="5" eb="7">
+      <t>シゼン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>サマタ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ブンセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー観察は、ありのままの行動や感情の動きを把握するため、</t>
+    <rPh sb="4" eb="6">
+      <t>カンサツ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カンジョウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ハアク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出来る限り介入しない姿勢が重視されます。</t>
+    <rPh sb="0" eb="2">
+      <t>デキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カギ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カイニュウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シセイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジュウシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「エンパシーマップ」の目的として、適切なものは次のうちどれか？</t>
+    <rPh sb="11" eb="13">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの体験と感情を可視化して、共感を深めるため</t>
+    <rPh sb="5" eb="7">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンジョウ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>カシカ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>キョウカン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>フカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ペルソナをもとにサービスの情報設計を図解化するため</t>
+    <rPh sb="13" eb="15">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ズカイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの収益構造と職務体系を明確にするため</t>
+    <rPh sb="5" eb="7">
+      <t>シュウエキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コウゾウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ショクム</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>タイケイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>メイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>顧客情報を整理してCRMシステムに登録するため</t>
+    <rPh sb="0" eb="2">
+      <t>コキャク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セイリ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エンパシーマップとは、ユーザーが見て、聞いて、考えて、感じていることを体系化し、</t>
+    <rPh sb="16" eb="17">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>タイケイ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チームで共通認識を深めるためのツールです。</t>
+    <rPh sb="4" eb="6">
+      <t>キョウツウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ニンシキ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>フカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ペルソナとカスタマージャーニーマップの関係性として、適切なものは次のうちどれか？</t>
+    <rPh sb="19" eb="22">
+      <t>カンケイセイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ペルソナがなくてもジャーニーマップは問題なく作れる</t>
+    <rPh sb="18" eb="20">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ペルソナに基づいて、1人のユーザーの行動と感情の流れを見える化するのがジャーニーマップ</t>
+    <rPh sb="5" eb="6">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ニン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カンジョウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャーニーマップは複数のペルソナの平均像に基づいて作成する</t>
+    <rPh sb="9" eb="11">
+      <t>フクスウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヘイキン</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ゾウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ペルソナとジャーニーマップは競合する手法であり、いずれかを選択する</t>
+    <rPh sb="14" eb="16">
+      <t>キョウゴウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シュホウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カスタマージャーニーマップは、特定のペルソナの体験を時系列に可視化したものであり、</t>
+    <rPh sb="15" eb="17">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>ジケイレツ</t>
+    </rPh>
+    <rPh sb="30" eb="33">
+      <t>カシカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ペルソナがあることが前提で、はじめて意味のあるジャーニー設計ができます。</t>
+    <rPh sb="10" eb="12">
+      <t>ゼンテイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>イミ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>セッケイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7583,7 +9510,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D63812B-C002-4F55-8D6D-817F494D0664}">
-  <dimension ref="B2:Q286"/>
+  <dimension ref="B2:Q356"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="17" max="17" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -10373,8 +12300,14 @@
       <c r="C282" t="s">
         <v>493</v>
       </c>
+      <c r="O282" t="s">
+        <v>54</v>
+      </c>
+      <c r="P282" t="s">
+        <v>6</v>
+      </c>
       <c r="Q282" s="1">
-        <v>46084</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="283" spans="2:17">
@@ -10409,15 +12342,708 @@
         <v>497</v>
       </c>
     </row>
+    <row r="287" spans="2:17">
+      <c r="B287">
+        <v>58</v>
+      </c>
+      <c r="C287" t="s">
+        <v>500</v>
+      </c>
+      <c r="O287" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P287" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q287" s="1">
+        <v>46085</v>
+      </c>
+    </row>
+    <row r="288" spans="2:17">
+      <c r="C288" t="s">
+        <v>5</v>
+      </c>
+      <c r="D288" t="s">
+        <v>501</v>
+      </c>
+      <c r="P288" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="289" spans="2:17">
+      <c r="C289" t="s">
+        <v>7</v>
+      </c>
+      <c r="D289" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="290" spans="2:17">
+      <c r="C290" t="s">
+        <v>9</v>
+      </c>
+      <c r="D290" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="291" spans="2:17">
+      <c r="C291" t="s">
+        <v>11</v>
+      </c>
+      <c r="D291" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="292" spans="2:17">
+      <c r="B292">
+        <v>59</v>
+      </c>
+      <c r="C292" t="s">
+        <v>505</v>
+      </c>
+      <c r="O292" t="s">
+        <v>54</v>
+      </c>
+      <c r="P292" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q292" s="1">
+        <v>46085</v>
+      </c>
+    </row>
+    <row r="293" spans="2:17">
+      <c r="C293" t="s">
+        <v>5</v>
+      </c>
+      <c r="D293" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="294" spans="2:17">
+      <c r="C294" t="s">
+        <v>7</v>
+      </c>
+      <c r="D294" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="295" spans="2:17">
+      <c r="C295" t="s">
+        <v>9</v>
+      </c>
+      <c r="D295" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="296" spans="2:17">
+      <c r="C296" t="s">
+        <v>11</v>
+      </c>
+      <c r="D296" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="297" spans="2:17">
+      <c r="B297">
+        <v>60</v>
+      </c>
+      <c r="C297" t="s">
+        <v>513</v>
+      </c>
+      <c r="O297" t="s">
+        <v>54</v>
+      </c>
+      <c r="P297" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q297" s="1">
+        <v>46085</v>
+      </c>
+    </row>
+    <row r="298" spans="2:17">
+      <c r="C298" t="s">
+        <v>5</v>
+      </c>
+      <c r="D298" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="299" spans="2:17">
+      <c r="C299" t="s">
+        <v>7</v>
+      </c>
+      <c r="D299" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="300" spans="2:17">
+      <c r="C300" t="s">
+        <v>9</v>
+      </c>
+      <c r="D300" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="301" spans="2:17">
+      <c r="C301" t="s">
+        <v>11</v>
+      </c>
+      <c r="D301" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="302" spans="2:17">
+      <c r="B302">
+        <v>61</v>
+      </c>
+      <c r="C302" t="s">
+        <v>521</v>
+      </c>
+      <c r="O302" t="s">
+        <v>54</v>
+      </c>
+      <c r="P302" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q302" s="1">
+        <v>46085</v>
+      </c>
+    </row>
+    <row r="303" spans="2:17">
+      <c r="C303" t="s">
+        <v>5</v>
+      </c>
+      <c r="D303" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="304" spans="2:17">
+      <c r="C304" t="s">
+        <v>7</v>
+      </c>
+      <c r="D304" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="305" spans="2:17">
+      <c r="C305" t="s">
+        <v>9</v>
+      </c>
+      <c r="D305" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="306" spans="2:17">
+      <c r="C306" t="s">
+        <v>11</v>
+      </c>
+      <c r="D306" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="307" spans="2:17">
+      <c r="B307">
+        <v>62</v>
+      </c>
+      <c r="C307" t="s">
+        <v>528</v>
+      </c>
+      <c r="O307" t="s">
+        <v>54</v>
+      </c>
+      <c r="P307" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q307" s="1">
+        <v>46085</v>
+      </c>
+    </row>
+    <row r="308" spans="2:17">
+      <c r="C308" t="s">
+        <v>5</v>
+      </c>
+      <c r="D308" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="309" spans="2:17">
+      <c r="C309" t="s">
+        <v>7</v>
+      </c>
+      <c r="D309" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="310" spans="2:17">
+      <c r="C310" t="s">
+        <v>9</v>
+      </c>
+      <c r="D310" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="311" spans="2:17">
+      <c r="C311" t="s">
+        <v>11</v>
+      </c>
+      <c r="D311" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="312" spans="2:17">
+      <c r="B312">
+        <v>63</v>
+      </c>
+      <c r="C312" t="s">
+        <v>535</v>
+      </c>
+      <c r="O312" t="s">
+        <v>54</v>
+      </c>
+      <c r="P312" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q312" s="1">
+        <v>46085</v>
+      </c>
+    </row>
+    <row r="313" spans="2:17">
+      <c r="C313" t="s">
+        <v>5</v>
+      </c>
+      <c r="D313" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="314" spans="2:17">
+      <c r="C314" t="s">
+        <v>7</v>
+      </c>
+      <c r="D314" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="315" spans="2:17">
+      <c r="C315" t="s">
+        <v>9</v>
+      </c>
+      <c r="D315" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="316" spans="2:17">
+      <c r="C316" t="s">
+        <v>11</v>
+      </c>
+      <c r="D316" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="317" spans="2:17">
+      <c r="B317">
+        <v>64</v>
+      </c>
+      <c r="C317" t="s">
+        <v>542</v>
+      </c>
+      <c r="O317" t="s">
+        <v>54</v>
+      </c>
+      <c r="P317" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q317" s="1">
+        <v>46085</v>
+      </c>
+    </row>
+    <row r="318" spans="2:17">
+      <c r="C318" t="s">
+        <v>5</v>
+      </c>
+      <c r="D318" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="319" spans="2:17">
+      <c r="C319" t="s">
+        <v>7</v>
+      </c>
+      <c r="D319" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="320" spans="2:17">
+      <c r="C320" t="s">
+        <v>9</v>
+      </c>
+      <c r="D320" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="321" spans="2:17">
+      <c r="C321" t="s">
+        <v>11</v>
+      </c>
+      <c r="D321" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="322" spans="2:17">
+      <c r="B322">
+        <v>65</v>
+      </c>
+      <c r="C322" t="s">
+        <v>549</v>
+      </c>
+      <c r="O322" t="s">
+        <v>54</v>
+      </c>
+      <c r="P322" t="s">
+        <v>518</v>
+      </c>
+      <c r="Q322" s="1">
+        <v>46085</v>
+      </c>
+    </row>
+    <row r="323" spans="2:17">
+      <c r="C323" t="s">
+        <v>5</v>
+      </c>
+      <c r="D323" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="324" spans="2:17">
+      <c r="C324" t="s">
+        <v>7</v>
+      </c>
+      <c r="D324" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="325" spans="2:17">
+      <c r="C325" t="s">
+        <v>9</v>
+      </c>
+      <c r="D325" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="326" spans="2:17">
+      <c r="C326" t="s">
+        <v>11</v>
+      </c>
+      <c r="D326" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="327" spans="2:17">
+      <c r="B327">
+        <v>66</v>
+      </c>
+      <c r="C327" t="s">
+        <v>556</v>
+      </c>
+      <c r="O327" t="s">
+        <v>54</v>
+      </c>
+      <c r="P327" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q327" s="1">
+        <v>46085</v>
+      </c>
+    </row>
+    <row r="328" spans="2:17">
+      <c r="C328" t="s">
+        <v>5</v>
+      </c>
+      <c r="D328" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="329" spans="2:17">
+      <c r="C329" t="s">
+        <v>7</v>
+      </c>
+      <c r="D329" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="330" spans="2:17">
+      <c r="C330" t="s">
+        <v>9</v>
+      </c>
+      <c r="D330" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="331" spans="2:17">
+      <c r="C331" t="s">
+        <v>11</v>
+      </c>
+      <c r="D331" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="332" spans="2:17">
+      <c r="B332">
+        <v>67</v>
+      </c>
+      <c r="C332" t="s">
+        <v>563</v>
+      </c>
+      <c r="O332" t="s">
+        <v>54</v>
+      </c>
+      <c r="P332" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q332" s="1">
+        <v>46085</v>
+      </c>
+    </row>
+    <row r="333" spans="2:17">
+      <c r="C333" t="s">
+        <v>5</v>
+      </c>
+      <c r="D333" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="334" spans="2:17">
+      <c r="C334" t="s">
+        <v>7</v>
+      </c>
+      <c r="D334" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="335" spans="2:17">
+      <c r="C335" t="s">
+        <v>9</v>
+      </c>
+      <c r="D335" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="336" spans="2:17">
+      <c r="C336" t="s">
+        <v>11</v>
+      </c>
+      <c r="D336" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="337" spans="2:17">
+      <c r="B337">
+        <v>68</v>
+      </c>
+      <c r="C337" t="s">
+        <v>570</v>
+      </c>
+      <c r="O337" t="s">
+        <v>54</v>
+      </c>
+      <c r="P337" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q337" s="1">
+        <v>46085</v>
+      </c>
+    </row>
+    <row r="338" spans="2:17">
+      <c r="C338" t="s">
+        <v>5</v>
+      </c>
+      <c r="D338" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="339" spans="2:17">
+      <c r="C339" t="s">
+        <v>7</v>
+      </c>
+      <c r="D339" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="340" spans="2:17">
+      <c r="C340" t="s">
+        <v>9</v>
+      </c>
+      <c r="D340" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="341" spans="2:17">
+      <c r="C341" t="s">
+        <v>11</v>
+      </c>
+      <c r="D341" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="342" spans="2:17">
+      <c r="B342">
+        <v>69</v>
+      </c>
+      <c r="C342" t="s">
+        <v>577</v>
+      </c>
+      <c r="O342" t="s">
+        <v>54</v>
+      </c>
+      <c r="P342" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q342" s="1">
+        <v>46085</v>
+      </c>
+    </row>
+    <row r="343" spans="2:17">
+      <c r="C343" t="s">
+        <v>5</v>
+      </c>
+      <c r="D343" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="344" spans="2:17">
+      <c r="C344" t="s">
+        <v>7</v>
+      </c>
+      <c r="D344" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="345" spans="2:17">
+      <c r="C345" t="s">
+        <v>9</v>
+      </c>
+      <c r="D345" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="346" spans="2:17">
+      <c r="C346" t="s">
+        <v>11</v>
+      </c>
+      <c r="D346" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="347" spans="2:17">
+      <c r="B347">
+        <v>70</v>
+      </c>
+      <c r="C347" t="s">
+        <v>584</v>
+      </c>
+      <c r="O347" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P347" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q347" s="1">
+        <v>46085</v>
+      </c>
+    </row>
+    <row r="348" spans="2:17">
+      <c r="C348" t="s">
+        <v>5</v>
+      </c>
+      <c r="D348" t="s">
+        <v>585</v>
+      </c>
+      <c r="P348" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="349" spans="2:17">
+      <c r="C349" t="s">
+        <v>7</v>
+      </c>
+      <c r="D349" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="350" spans="2:17">
+      <c r="C350" t="s">
+        <v>9</v>
+      </c>
+      <c r="D350" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="351" spans="2:17">
+      <c r="C351" t="s">
+        <v>11</v>
+      </c>
+      <c r="D351" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="352" spans="2:17">
+      <c r="B352">
+        <v>71</v>
+      </c>
+      <c r="C352" t="s">
+        <v>591</v>
+      </c>
+      <c r="O352" t="s">
+        <v>54</v>
+      </c>
+      <c r="P352" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q352" s="1">
+        <v>46085</v>
+      </c>
+    </row>
+    <row r="353" spans="3:4">
+      <c r="C353" t="s">
+        <v>5</v>
+      </c>
+      <c r="D353" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="354" spans="3:4">
+      <c r="C354" t="s">
+        <v>7</v>
+      </c>
+      <c r="D354" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="355" spans="3:4">
+      <c r="C355" t="s">
+        <v>9</v>
+      </c>
+      <c r="D355" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="356" spans="3:4">
+      <c r="C356" t="s">
+        <v>11</v>
+      </c>
+      <c r="D356" t="s">
+        <v>595</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D7C2EE-C8B5-4851-B670-42D9DD8D67DA}">
-  <dimension ref="B2:D146"/>
+  <dimension ref="B2:D189"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="2" spans="2:4">
@@ -11479,6 +14105,311 @@
     <row r="146" spans="2:4">
       <c r="B146">
         <v>57</v>
+      </c>
+      <c r="C146" t="s">
+        <v>6</v>
+      </c>
+      <c r="D146" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="D147" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
+      <c r="D148" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149">
+        <v>58</v>
+      </c>
+      <c r="C149" t="s">
+        <v>9</v>
+      </c>
+      <c r="D149" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="D150" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="D151" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
+      <c r="B152">
+        <v>59</v>
+      </c>
+      <c r="C152" t="s">
+        <v>9</v>
+      </c>
+      <c r="D152" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="D153" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
+      <c r="B154">
+        <v>60</v>
+      </c>
+      <c r="C154" t="s">
+        <v>7</v>
+      </c>
+      <c r="D154" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="D155" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="D156" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157">
+        <v>61</v>
+      </c>
+      <c r="C157" t="s">
+        <v>7</v>
+      </c>
+      <c r="D157" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="D158" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="D159" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160">
+        <v>62</v>
+      </c>
+      <c r="C160" t="s">
+        <v>7</v>
+      </c>
+      <c r="D160" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4">
+      <c r="D161" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4">
+      <c r="D162" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4">
+      <c r="B163">
+        <v>63</v>
+      </c>
+      <c r="C163" t="s">
+        <v>7</v>
+      </c>
+      <c r="D163" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4">
+      <c r="D164" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4">
+      <c r="D165" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="166" spans="2:4">
+      <c r="B166">
+        <v>64</v>
+      </c>
+      <c r="C166" t="s">
+        <v>11</v>
+      </c>
+      <c r="D166" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="167" spans="2:4">
+      <c r="D167" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="168" spans="2:4">
+      <c r="D168" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4">
+      <c r="B169">
+        <v>65</v>
+      </c>
+      <c r="C169" t="s">
+        <v>7</v>
+      </c>
+      <c r="D169" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4">
+      <c r="D170" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4">
+      <c r="D171" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4">
+      <c r="B172">
+        <v>66</v>
+      </c>
+      <c r="C172" t="s">
+        <v>7</v>
+      </c>
+      <c r="D172" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4">
+      <c r="D173" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="174" spans="2:4">
+      <c r="D174" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="175" spans="2:4">
+      <c r="B175">
+        <v>67</v>
+      </c>
+      <c r="C175" t="s">
+        <v>7</v>
+      </c>
+      <c r="D175" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="176" spans="2:4">
+      <c r="D176" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="177" spans="2:4">
+      <c r="D177" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="178" spans="2:4">
+      <c r="B178">
+        <v>68</v>
+      </c>
+      <c r="C178" t="s">
+        <v>7</v>
+      </c>
+      <c r="D178" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="179" spans="2:4">
+      <c r="D179" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="180" spans="2:4">
+      <c r="D180" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="181" spans="2:4">
+      <c r="B181">
+        <v>69</v>
+      </c>
+      <c r="C181" t="s">
+        <v>11</v>
+      </c>
+      <c r="D181" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="182" spans="2:4">
+      <c r="D182" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="183" spans="2:4">
+      <c r="D183" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="184" spans="2:4">
+      <c r="B184">
+        <v>70</v>
+      </c>
+      <c r="C184" t="s">
+        <v>5</v>
+      </c>
+      <c r="D184" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="185" spans="2:4">
+      <c r="D185" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="186" spans="2:4">
+      <c r="D186" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="187" spans="2:4">
+      <c r="B187">
+        <v>71</v>
+      </c>
+      <c r="C187" t="s">
+        <v>7</v>
+      </c>
+      <c r="D187" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="188" spans="2:4">
+      <c r="D188" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="189" spans="2:4">
+      <c r="D189" t="s">
+        <v>597</v>
       </c>
     </row>
   </sheetData>

--- a/UX検定_基礎.xlsx
+++ b/UX検定_基礎.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\UX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64DA082-D977-4086-92E7-2755AF84CFE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB2CED0-7CB6-49ED-A5C0-B0DCA62C825E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="模擬" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1734" uniqueCount="783">
   <si>
     <t>UXインテリジェンスが生み出す価値として重要視するものを、次の中から選びなさい。</t>
     <phoneticPr fontId="1"/>
@@ -7981,6 +7981,3293 @@
     </rPh>
     <rPh sb="28" eb="30">
       <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フィールドワークの特徴として、適切なものは次のうちどれか？</t>
+    <rPh sb="9" eb="11">
+      <t>トクチョウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの利用環境に出向き、その行動や感情を観察する手法</t>
+    <rPh sb="5" eb="7">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>デム</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カンジョウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>カンサツ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仮説に基づいた構造化されたアンケートを用いる手法</t>
+    <rPh sb="0" eb="2">
+      <t>カセツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>コウゾウカ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの業務内容を代行することで課題を洗い出す手法</t>
+    <rPh sb="5" eb="7">
+      <t>ギョウム</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ダイコウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>アラ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ラボ環境でユーザーに操作をさせ、結果を数値化する手法</t>
+    <rPh sb="2" eb="4">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>スウチカ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フィールドワークは、現場での観察がポイントで、生活の中でのUXを見つけるために</t>
+    <rPh sb="10" eb="12">
+      <t>ゲンバ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カンサツ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>セイカツ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実施するリサーチ方法</t>
+    <rPh sb="0" eb="2">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXにおける「行動変容デザイン」の考え方として、適切なものは次のうちどれか？</t>
+    <rPh sb="7" eb="9">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヘンヨウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの行動を企業にとって都合の良い形に矯正する</t>
+    <rPh sb="5" eb="7">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キギョウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ツゴウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>カタチ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>キョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが自らの意思でポジティブな行動に移れるようにサポートする</t>
+    <rPh sb="5" eb="6">
+      <t>ミズカ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>イシ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ウツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの意思に反してでも、一定の成果が出れば良い</t>
+    <rPh sb="5" eb="7">
+      <t>イシ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ハン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>イッテイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>セイカ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行動は変えられないため、既存の習慣に完全に合わせるべき</t>
+    <rPh sb="0" eb="2">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>キゾン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シュウカン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カンゼン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが自身の価値観に沿って、より良い行動に進めるように支援することが</t>
+    <rPh sb="5" eb="7">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>カチカン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ソ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>シエン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設計が行動変容デザインの本質です。</t>
+    <rPh sb="0" eb="2">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヘンヨウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ホンシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UX評価指標を施策に活かす際に最も重要な考え方として、適切なものは次のうちどれか？</t>
+    <rPh sb="2" eb="4">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シヒョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シサク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>モット</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>毎回異なる指標を使い、柔軟に対応する</t>
+    <rPh sb="0" eb="2">
+      <t>マイカイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シヒョウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジュウナン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>定量評価だけで判断し、ユーザーの主観は無視する</t>
+    <rPh sb="0" eb="2">
+      <t>テイリョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハンダン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シュカン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ムシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UI変更後のアクセス数だけを追跡する</t>
+    <rPh sb="2" eb="4">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ツイセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>数値変化の原因をユーザー行動や体験と結びつけて把握する</t>
+    <rPh sb="0" eb="2">
+      <t>スウチ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ゲンイン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ムス</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ハアク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UX評価は、なぜ指標が変化したかをユーザーの体験や行動と結び付けて解釈することに</t>
+    <rPh sb="2" eb="4">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シヒョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ムス</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カイシャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>より施策に活かすため、数値の意味付けが重要になります。</t>
+    <rPh sb="2" eb="4">
+      <t>シサク</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>スウチ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>イミ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ヅ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIにおける「一貫性」がUXに貢献する理由として、適切なものは次のうちどれか？</t>
+    <rPh sb="7" eb="10">
+      <t>イッカンセイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コウケン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>リユウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが新しいデザインに常に刺激を感じられるようにするため</t>
+    <rPh sb="5" eb="6">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ツネ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シゲキ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一貫した表現により、学習コストを低くし、安心感を与えられるため</t>
+    <rPh sb="0" eb="2">
+      <t>イッカン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ヒク</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>アンシンカン</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIがランダムに変化することで注意を引き続けられるため</t>
+    <rPh sb="8" eb="10">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>チュウイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ツヅ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの想定を裏切ることで印象に残すため</t>
+    <rPh sb="5" eb="7">
+      <t>ソウテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ウラギ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>インショウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ノコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一貫性があるUIでは、ユーザーが迷わずに操作できるため、認知負荷を低減して、</t>
+    <rPh sb="0" eb="3">
+      <t>イッカンセイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>マヨ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ニンチ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>フカ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>テイゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>安心して使えるUXにつながります。</t>
+    <rPh sb="0" eb="2">
+      <t>アンシン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーインタビューを行う際に避けるべき質問の例として最も適切なものはどれか？</t>
+    <rPh sb="11" eb="12">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シツモン</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>モット</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>テキセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「その時、どのように感じましたか？」</t>
+    <rPh sb="3" eb="4">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「この機能は、使い勝手がいいですよね？」</t>
+    <rPh sb="3" eb="5">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガッテ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「その機能を使ってみて下さい」</t>
+    <rPh sb="3" eb="5">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>クダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「どのような手順で作業されていますか？」</t>
+    <rPh sb="6" eb="8">
+      <t>テジュン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>サギョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーインタビューでは、誘導的な質問を回避することが基本であり、</t>
+    <rPh sb="13" eb="16">
+      <t>ユウドウテキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シツモン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カイヒ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>キホン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正解（選択肢B）のような質問は、同意を誘導する表現になるため、やはり避けるべきです。</t>
+    <rPh sb="0" eb="2">
+      <t>セイカイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シツモン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ドウイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ユウドウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>サ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ローファイプロトタイプ」の特徴として、適切なものは次のうちどれか？</t>
+    <rPh sb="14" eb="16">
+      <t>トクチョウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ペーパーモックやワイヤーフレームなど、ラフなプロトタイプで構成される</t>
+    <rPh sb="29" eb="31">
+      <t>コウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開発に近い精度で実装され、テスト後すぐにリリースできる</t>
+    <rPh sb="0" eb="2">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>チカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セイド</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高精細なUIデザインで構成され、インタラクションも完全に実装されている</t>
+    <rPh sb="0" eb="3">
+      <t>コウセイサイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>カンゼン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コーディングにより、UIとロジックが連動している</t>
+    <rPh sb="18" eb="20">
+      <t>レンドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ローファイプロトタイプは、アイデア段階の検証に用いるプロトタイプであり、</t>
+    <rPh sb="17" eb="19">
+      <t>ダンカイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ケンショウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>モチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コストや時間をかけずに検討が進めることが出来ます。</t>
+    <rPh sb="4" eb="6">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ケントウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>デキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HCDサイクルにおける「4つの主要活動」に含まれないものは次のうちどれか？</t>
+    <rPh sb="15" eb="17">
+      <t>シュヨウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カツドウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>対称ユーザーの把握と明確化</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハアク</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>メイカクカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コーディングと実装</t>
+    <rPh sb="7" eb="9">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要求に合致したソリューションの設計</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウキュウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ガッチ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>対象ユーザー要求の明確化</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヨウキュウ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>メイカクカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コーディングや実装は、HCDの4つの主要活動に含まれません。</t>
+    <rPh sb="7" eb="9">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シュヨウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カツドウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アクセシビリティ実装におけるHTMLの基本的な対応として、適切なものはどれか？</t>
+    <rPh sb="8" eb="10">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>キホンテキ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>テキセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>視覚的に装飾されていれば、構造は重要ではない</t>
+    <rPh sb="0" eb="3">
+      <t>シカクテキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ソウショク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コウゾウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>alt属性は任意なので、省略しても問題ない</t>
+    <rPh sb="3" eb="5">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ニンイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ショウリャク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>モンダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボタンやリンクはすべて画像で表現するのが好ましい</t>
+    <rPh sb="11" eb="13">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>コノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ランドマーク（role属性）や適切な見出し構造を整備する</t>
+    <rPh sb="11" eb="13">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ミダ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>コウゾウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>セイビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ｄ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アクセシビリティ対応では、支援技術が正しく認識できるようにするために、</t>
+    <rPh sb="8" eb="10">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シエン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ギジュツ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ニンシキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HTMLの構造的意味づけ（セマンティクス）がとても重要です。</t>
+    <rPh sb="5" eb="8">
+      <t>コウゾウテキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>イミ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スプリントの短い開発サイクルにおける、UX設計での最重要アプローチは、次のうちどれか？</t>
+    <rPh sb="6" eb="7">
+      <t>ミジカ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>サイジュウヨウ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スプリント終了時にまとめてUX設計を行う</t>
+    <rPh sb="5" eb="8">
+      <t>シュウリョウジ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UX設計を前工程に集中させて、以後は触れないようにする</t>
+    <rPh sb="2" eb="4">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウテイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シュウチュウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>イゴ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>各スプリントにUX担当者が参加して、繰り返し検証・改善を行う</t>
+    <rPh sb="0" eb="1">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>サンカ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ケンショウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開発側に任せUX設計はドキュメントだけを提供する</t>
+    <rPh sb="0" eb="2">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>マカ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>テイキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アジャイル型開発では、UX設計もスプリントと同時進行し、その都度プロトタイピングや</t>
+    <rPh sb="5" eb="6">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ドウジ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>シンコウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ツド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーテストなどを繰り返しながら改善していくアプローチが重要です。</t>
+    <rPh sb="10" eb="11">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーセグメントを設計する目的として、適切なものは次のうちどれか？</t>
+    <rPh sb="10" eb="12">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全ユーザーに対して同じUXを提供するため</t>
+    <rPh sb="0" eb="1">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>テイキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用条件を限定して不必要な利用を制限するため</t>
+    <rPh sb="0" eb="2">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>フヒツヨウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セイゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの状況や課題に応じた体験を最適化するため</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>サイテキカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>広告表示の最適化だけを目的にするため</t>
+    <rPh sb="0" eb="2">
+      <t>コウコク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>サイテキカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>モクテキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーセグメント設計の目的は、ユーザーを属性やニーズで細分化し、</t>
+    <rPh sb="9" eb="11">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="28" eb="31">
+      <t>サイブンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マーケティング戦略やサービス最適化に役立てるために、</t>
+    <rPh sb="7" eb="9">
+      <t>センリャク</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>サイテキカ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヤクダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>より効果的なコミュニケーションや施策を展開することにあります。</t>
+    <rPh sb="2" eb="5">
+      <t>コウカテキ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シサク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>テンカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXライティングでの「トーン&amp;マナー」の目的として、適切なものは次のうちどれか？</t>
+    <rPh sb="20" eb="22">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表現に感情を込めすぎて差別化を図る</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カンジョウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>サベツカ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ハカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーごとに異なる表現を使い分ける</t>
+    <rPh sb="7" eb="8">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブランドらしさを感じさせる一貫性のあるイメージを与える</t>
+    <rPh sb="8" eb="9">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>イッカンセイ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文字数を統一して認識を早める</t>
+    <rPh sb="0" eb="3">
+      <t>モジスウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>トウイツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ニンシキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ハヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トーン&amp;マナーは、ブランドのメッセージが一貫性を保つためのルールのことです。</t>
+    <rPh sb="20" eb="23">
+      <t>イッカンセイ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>タモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト駆動のUX改善の特徴についての説明として、適切なものは次のうちどれか？</t>
+    <rPh sb="3" eb="5">
+      <t>クドウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>トクチョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A/Bテスト、ユーザーテストなどによって仮説を検証しながら改善する</t>
+    <rPh sb="20" eb="22">
+      <t>カセツ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ケンショウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの主観をもとに仮説を立てあい</t>
+    <rPh sb="5" eb="7">
+      <t>シュカン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カセツ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初回リリースで完成後を最大化するため、テストは控える</t>
+    <rPh sb="0" eb="2">
+      <t>ショカイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>サイダイカ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ヒカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>数値が良ければUXの良し悪しは関係ない</t>
+    <rPh sb="0" eb="2">
+      <t>スウチ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ワル</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カンケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト駆動開発は、テストを最初に実施するプログラミング方法として、</t>
+    <rPh sb="3" eb="5">
+      <t>クドウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アジャイル開発手法に多く取り入れられています。</t>
+    <rPh sb="5" eb="7">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シュホウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>情報過多のUX課題を解決する対策として、適切なものは次のうちどれか？</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カイケツ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>タイサク</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すべての情報を1ページに集約する</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シュウヤク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>情報量に応じてフォントサイズを小さくする</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>チイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>検索機能をなくし、一覧性を重視する</t>
+    <rPh sb="0" eb="2">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>イチランセイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジュウシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必要な情報だけを必要なタイミングで表示する設計にする</t>
+    <rPh sb="0" eb="2">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必要な情報だけを必要なタイミングで表示する設計は、ユーザーにとって使いやすく、</t>
+    <rPh sb="0" eb="2">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>情報を見つけやすいため、UX改善につながります。</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>KPIをUXチーム内で共有、可視化する目的として、適切なものは次のうちどれか？</t>
+    <rPh sb="9" eb="10">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キョウユウ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>カシカ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>外注先との契約評価を明確にするため</t>
+    <rPh sb="0" eb="3">
+      <t>ガイチュウサキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ケイヤク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>メイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>共通のUXゴールに向かってチームが行動できるようにするため</t>
+    <rPh sb="0" eb="2">
+      <t>キョウツウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>コウドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標を管理職にのみ伝えるため</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ショク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ツタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社外への実績アピールに活用するため</t>
+    <rPh sb="0" eb="2">
+      <t>シャガイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジッセキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>KPIをUXチーム内で共有、可視化する目的は、UXデザインの目標達成度を明確に把握し、</t>
+    <rPh sb="9" eb="10">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キョウユウ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>カシカ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>タッセイ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>メイカク</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ハアク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チームメンバー全員が同じ目標に向かって行動することです。</t>
+    <rPh sb="7" eb="9">
+      <t>ゼンイン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>コウドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの内的報酬を活用したUX施策の例として、適切なものは次のうちどれか？</t>
+    <rPh sb="5" eb="7">
+      <t>ナイテキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ホウシュウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カツヨウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シサク</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポイント付与などのインセンティブ</t>
+    <rPh sb="4" eb="6">
+      <t>フヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>友人に紹介するたびにクーポンを提供</t>
+    <rPh sb="0" eb="2">
+      <t>ユウジン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ショウカイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>テイキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>毎日使うことによりバッジがもらえる設計</t>
+    <rPh sb="0" eb="2">
+      <t>マイニチ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用時間に応じて広告を表示する</t>
+    <rPh sb="0" eb="2">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウコク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>内的報酬とは、給与などの外的報酬とは異なり、仕事そのものから得られる</t>
+    <rPh sb="0" eb="2">
+      <t>ナイテキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホウシュウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キュウヨ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ガイテキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ホウシュウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シゴト</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>エ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>心理的な満足感、やりがいなどを指します。</t>
+    <rPh sb="15" eb="16">
+      <t>サ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UX戦略における上位指針として、適切なものは次のうちどれか？</t>
+    <rPh sb="2" eb="4">
+      <t>センリャク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジョウイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シシン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIパターンの整理と統一</t>
+    <rPh sb="7" eb="9">
+      <t>セイリ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>トウイツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>提供価値・世界観・パーパスの設計</t>
+    <rPh sb="0" eb="2">
+      <t>テイキョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カチ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セカイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンポーネントの設計ルール</t>
+    <rPh sb="8" eb="10">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コーディング規約の標準化</t>
+    <rPh sb="6" eb="8">
+      <t>キヤク</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ヒョウジュンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マイクロインタラクションがUXに及ぼす効果として、適切なものは次のうちどれか？</t>
+    <rPh sb="16" eb="17">
+      <t>オヨ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>操作感に一貫性を持たせることにより、安心感を得る</t>
+    <rPh sb="0" eb="3">
+      <t>ソウサカン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>イッカンセイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>アンシン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>エ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIのレイアウトを統一的に構築できる</t>
+    <rPh sb="9" eb="12">
+      <t>トウイツテキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コウチク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンバージョン率を数値で直接測定できる</t>
+    <rPh sb="7" eb="8">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>スウチ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>チョクセツ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ソクテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>情報量を削減することで判断速度を高める</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>サクゲン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ハンダン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>タカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「アンカリング効果」がUXに影響する例として、適切なものは次のうちどれか？</t>
+    <rPh sb="7" eb="9">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>エイキョウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アプリ起動時に読み込み速度が遅いと離脱が高まる</t>
+    <rPh sb="3" eb="5">
+      <t>キドウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>オソ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>リダツ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>タカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初回に提示された価格がそれ以降の判断基準になる</t>
+    <rPh sb="0" eb="2">
+      <t>ショカイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>テイジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カカク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ハンダン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>キジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ナビゲーションが長いと情報を見落としやすくなる</t>
+    <rPh sb="8" eb="9">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ミオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フォームが多すぎると途中で離脱しやすい</t>
+    <rPh sb="5" eb="6">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>リダツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アンカリング効果とは、最初に見聞きした価格などが基準になり、</t>
+    <rPh sb="6" eb="8">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ミキ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カカク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>キジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それ以降の判断に影響を及ぼしてしまう心理効果のことです。</t>
+    <rPh sb="2" eb="4">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ハンダン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>エイキョウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>オヨ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シンリ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アジャイル開発におけるUXデザイナーが担うべき役割として、適切なものは次のうちどれか？</t>
+    <rPh sb="5" eb="7">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ニナ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヤクワリ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIデザインをまとめて初期に完了させる</t>
+    <rPh sb="11" eb="13">
+      <t>ショキ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー理解とプロトタイピングをスプリント内で継続する</t>
+    <rPh sb="4" eb="6">
+      <t>リカイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ケイゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スプリント内で開発の進捗を評価する</t>
+    <rPh sb="5" eb="6">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シンチョク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アジャイルにはUXデザイナーは関与しない</t>
+    <rPh sb="15" eb="17">
+      <t>カンヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スプリントごとにユーザー調査を実施し、得られた知見をプロトタイプに反映して、繰り返し検証することにより、</t>
+    <rPh sb="12" eb="14">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>エ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>チケン</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ハンエイ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ケンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーニーズに最適な製品・サービスを開発できます。</t>
+    <rPh sb="8" eb="10">
+      <t>サイテキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カイハツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「UXインテリジェンス」が目標とする社会像として、適切なものは次のうちどれか？</t>
+    <rPh sb="13" eb="15">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シャカイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ゾウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テクノロジーでユーザーの行動を完全に制御する社会</t>
+    <rPh sb="12" eb="14">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カンゼン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シャカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業が主導して効率性を最大化する社会</t>
+    <rPh sb="0" eb="2">
+      <t>キギョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュドウ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>コウリツセイ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>サイダイカ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シャカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>体験をデータ化し、常に最適解を自動提示する社会</t>
+    <rPh sb="0" eb="2">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ツネ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サイテキ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>テイジ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>シャカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが自らのデータと選択肢を把握して、主体的に行動できる社会</t>
+    <rPh sb="5" eb="6">
+      <t>ミズカ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ハアク</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>シュタイテキ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>シャカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXインテリジェンスが目指す社会像は、だれもが自らの選択肢を理解し、</t>
+    <rPh sb="11" eb="13">
+      <t>メザ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シャカイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ゾウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ミズカ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>センタクシ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>リカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自らの主体的な行動を通して価値を創造し、より良い生活を送れる社会です。</t>
+    <rPh sb="0" eb="1">
+      <t>ミズカ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>シュタイテキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カチ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ソウゾウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>セイカツ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>シャカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UX人材育成で重要な視点として、適切なものは次のうちどれか？</t>
+    <rPh sb="2" eb="4">
+      <t>ジンザイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>イクセイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シテン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIスキルだけを強化し、専門分化を進める</t>
+    <rPh sb="8" eb="10">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>センモン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ブンカ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>スス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>調査、設計、評価における幅広い視点と実践力を育てる</t>
+    <rPh sb="0" eb="2">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ハバヒロ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シテン</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>ジッセンリョク</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ソダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マネジメント視点を先に身につけ、設計は外注する</t>
+    <rPh sb="6" eb="8">
+      <t>シテン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ガイチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーリサーチは専門家に任せる方針を徹底する</t>
+    <rPh sb="9" eb="12">
+      <t>センモンカ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>マカ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ホウシン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>テッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーとの信頼関係を構築するUX設計において、重要な考え方は次のうちどれか？</t>
+    <rPh sb="6" eb="8">
+      <t>シンライ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウチク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同意なしに情報を収集することでUXを最適化する</t>
+    <rPh sb="0" eb="2">
+      <t>ドウイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シュウシュウ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>サイテキカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>操作を強制せずに、ユーザーの選択を優先する設計</t>
+    <rPh sb="0" eb="2">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キョウセイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ユウセン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>他サービスと同様の画面構成にする</t>
+    <rPh sb="0" eb="1">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ドウヨウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シンプルなUIで機能を最小限に抑える</t>
+    <rPh sb="8" eb="10">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>サイショウゲン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが特定の操作を強制されることなく、必要なときに必要な操作ができるようにすることで、</t>
+    <rPh sb="5" eb="7">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キョウセイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ソウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>使いやすさと満足度を向上させることが出来ます。</t>
+    <rPh sb="0" eb="1">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>マンゾクド</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウジョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>デキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXエバンジェリズムの目的として、適切なものは次のうちどれか？</t>
+    <rPh sb="11" eb="13">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXガイドラインを整備する専門業務</t>
+    <rPh sb="9" eb="11">
+      <t>セイビ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>センモン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ギョウム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>組織全体にUXの価値を伝達し、浸透させる活動</t>
+    <rPh sb="0" eb="2">
+      <t>ソシキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カチ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>デンタツ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シントウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXを外注化する際の契約支援</t>
+    <rPh sb="3" eb="6">
+      <t>ガイチュウカ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ケイヤク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シエン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UX評価指標を数値化するためのデータ管理</t>
+    <rPh sb="2" eb="4">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シヒョウ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>スウチカ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXにおけるダークパターンの問題として、適切なものは次のうちどれか？</t>
+    <rPh sb="14" eb="16">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あえてラベルの色を薄くして注意を引かない工夫</t>
+    <rPh sb="7" eb="8">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ウス</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>チュウイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>クフウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>情報量が多すぎて選択ができない構造</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コウゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの自由な選択を阻害して、意図しない行動を強制する設計</t>
+    <rPh sb="5" eb="7">
+      <t>ジユウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ソガイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>イト</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>キョウセイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文字サイズを調整して読みやすくする設計</t>
+    <rPh sb="0" eb="2">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダークパターンとは、ユーザーを騙して不利な意思決定をさせたり、</t>
+    <rPh sb="15" eb="16">
+      <t>ダマ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>フリ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>イシ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ケッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>意図に反した行動を促したりするインターフェースやデザインのことです。</t>
+    <rPh sb="0" eb="2">
+      <t>イト</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ハン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ウナガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バリュージャーニーの考え方の説明として、適切なものは次のうちどれか？</t>
+    <rPh sb="10" eb="11">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが支払う金額に対して提供する機能を分類すること</t>
+    <rPh sb="5" eb="7">
+      <t>シハラ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>テイキョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ブンルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UI要素をジャーニー順に並べて構成すること</t>
+    <rPh sb="2" eb="4">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ジュン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ナラ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ペルソナごとに使う製品カテゴリを分類すること</t>
+    <rPh sb="7" eb="8">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ブンルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが体験を通して価値を感じるまでの道のりを可視化すること</t>
+    <rPh sb="5" eb="7">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ミチ</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>カシカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXデザインでステークホルダー連携が重要な理由として、適切なものは次のうちどれか？</t>
+    <rPh sb="15" eb="17">
+      <t>レンケイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>リユウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイナーの意見を通すために協力体制を整える</t>
+    <rPh sb="6" eb="8">
+      <t>イケン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キョウリョク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>タイセイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>トトノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>意見対立を避けるため、最初から全員の要望を取り入れる</t>
+    <rPh sb="0" eb="2">
+      <t>イケン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タイリツ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ゼンイン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヨウボウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要件定義を他部門に丸投げするため</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウケン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>タブモン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>マルナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>組織内の目線を統一して、ユーザー体験の質を維持するため</t>
+    <rPh sb="0" eb="2">
+      <t>ソシキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>メセン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>トウイツ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>シツ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>イジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サービス提供型ビジネスにおけるUXの特徴として、適切なものは次のうちどれか？</t>
+    <rPh sb="4" eb="7">
+      <t>テイキョウガタ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>トクチョウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初回体験さえ良ければ、継続的な価値提供は不要である</t>
+    <rPh sb="0" eb="2">
+      <t>ショカイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ケイゾクテキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カチ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>テイキョウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>フヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>売り切り型の商品とは違い、継続的な体験の設計が要求される</t>
+    <rPh sb="0" eb="1">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ケイゾクテキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヨウキュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXは製品完成後に考えるものである</t>
+    <rPh sb="3" eb="5">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>カンガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>契約内容とUI設計が一致していればUXは十分である</t>
+    <rPh sb="0" eb="2">
+      <t>ケイヤク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イッチ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ジュウブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ラーニングカーブがUX設計に与える示唆として、適切なものは次のうちどれか？</t>
+    <rPh sb="11" eb="13">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シサ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>操作の難易度が高い方が印象に残る</t>
+    <rPh sb="0" eb="2">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ナンイド</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>インショウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ノコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>習熟に時間がかかるほどエンゲージメントは高まる</t>
+    <rPh sb="0" eb="2">
+      <t>シュウジュク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>タカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用初期における負荷を減らす設計が重要である</t>
+    <rPh sb="0" eb="2">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>フカ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ヘ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すべての機能を一度に学習させるのが効果的</t>
+    <rPh sb="4" eb="6">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>コウカテキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インフォームドコンセントに関する説明として、適切なものは次のうちどれか？</t>
+    <rPh sb="13" eb="14">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>調査やテストの前に参加者に目的や内容、リスクを説明し、同意を得ること</t>
+    <rPh sb="0" eb="2">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>サンカシャ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ドウイ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>エ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIの構成要素をユーザーにわかりやすく説明すること</t>
+    <rPh sb="3" eb="5">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーから許可を取らずに情報収集する行為</t>
+    <rPh sb="6" eb="8">
+      <t>キョカ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シュウシュウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>コウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すべての操作を事前に了承してもらう契約書のこと</t>
+    <rPh sb="4" eb="6">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジゼン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>リョウショウ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>ケイヤクショ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -7989,7 +11276,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8010,6 +11297,13 @@
       <name val="Segoe UI Symbol"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -8028,15 +11322,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="パーセント" xfId="1" builtinId="5"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -9510,7 +12809,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D63812B-C002-4F55-8D6D-817F494D0664}">
-  <dimension ref="B2:Q356"/>
+  <dimension ref="B2:Q502"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="17" max="17" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -13002,7 +16301,7 @@
         <v>46085</v>
       </c>
     </row>
-    <row r="353" spans="3:4">
+    <row r="353" spans="2:17">
       <c r="C353" t="s">
         <v>5</v>
       </c>
@@ -13010,7 +16309,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="354" spans="3:4">
+    <row r="354" spans="2:17">
       <c r="C354" t="s">
         <v>7</v>
       </c>
@@ -13018,7 +16317,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="355" spans="3:4">
+    <row r="355" spans="2:17">
       <c r="C355" t="s">
         <v>9</v>
       </c>
@@ -13026,12 +16325,1457 @@
         <v>594</v>
       </c>
     </row>
-    <row r="356" spans="3:4">
+    <row r="356" spans="2:17">
       <c r="C356" t="s">
         <v>11</v>
       </c>
       <c r="D356" t="s">
         <v>595</v>
+      </c>
+    </row>
+    <row r="357" spans="2:17">
+      <c r="B357">
+        <v>72</v>
+      </c>
+      <c r="C357" t="s">
+        <v>598</v>
+      </c>
+      <c r="O357" t="s">
+        <v>54</v>
+      </c>
+      <c r="P357" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q357" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="358" spans="2:17">
+      <c r="C358" t="s">
+        <v>5</v>
+      </c>
+      <c r="D358" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="359" spans="2:17">
+      <c r="C359" t="s">
+        <v>7</v>
+      </c>
+      <c r="D359" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="360" spans="2:17">
+      <c r="C360" t="s">
+        <v>9</v>
+      </c>
+      <c r="D360" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="361" spans="2:17">
+      <c r="C361" t="s">
+        <v>11</v>
+      </c>
+      <c r="D361" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="362" spans="2:17">
+      <c r="B362">
+        <v>73</v>
+      </c>
+      <c r="C362" t="s">
+        <v>605</v>
+      </c>
+      <c r="O362" t="s">
+        <v>54</v>
+      </c>
+      <c r="P362" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q362" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="363" spans="2:17">
+      <c r="C363" t="s">
+        <v>5</v>
+      </c>
+      <c r="D363" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="364" spans="2:17">
+      <c r="C364" t="s">
+        <v>7</v>
+      </c>
+      <c r="D364" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="365" spans="2:17">
+      <c r="C365" t="s">
+        <v>9</v>
+      </c>
+      <c r="D365" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="366" spans="2:17">
+      <c r="C366" t="s">
+        <v>11</v>
+      </c>
+      <c r="D366" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="367" spans="2:17">
+      <c r="B367">
+        <v>74</v>
+      </c>
+      <c r="C367" t="s">
+        <v>612</v>
+      </c>
+      <c r="O367" t="s">
+        <v>54</v>
+      </c>
+      <c r="P367" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q367" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="368" spans="2:17">
+      <c r="C368" t="s">
+        <v>5</v>
+      </c>
+      <c r="D368" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="369" spans="2:17">
+      <c r="C369" t="s">
+        <v>7</v>
+      </c>
+      <c r="D369" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="370" spans="2:17">
+      <c r="C370" t="s">
+        <v>9</v>
+      </c>
+      <c r="D370" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="371" spans="2:17">
+      <c r="C371" t="s">
+        <v>11</v>
+      </c>
+      <c r="D371" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="372" spans="2:17">
+      <c r="B372">
+        <v>75</v>
+      </c>
+      <c r="C372" t="s">
+        <v>619</v>
+      </c>
+      <c r="O372" t="s">
+        <v>54</v>
+      </c>
+      <c r="P372" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q372" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="373" spans="2:17">
+      <c r="C373" t="s">
+        <v>5</v>
+      </c>
+      <c r="D373" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="374" spans="2:17">
+      <c r="C374" t="s">
+        <v>7</v>
+      </c>
+      <c r="D374" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="375" spans="2:17">
+      <c r="C375" t="s">
+        <v>9</v>
+      </c>
+      <c r="D375" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="376" spans="2:17">
+      <c r="C376" t="s">
+        <v>11</v>
+      </c>
+      <c r="D376" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="377" spans="2:17">
+      <c r="B377">
+        <v>76</v>
+      </c>
+      <c r="C377" t="s">
+        <v>626</v>
+      </c>
+      <c r="O377" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P377" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q377" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="378" spans="2:17">
+      <c r="C378" t="s">
+        <v>5</v>
+      </c>
+      <c r="D378" t="s">
+        <v>627</v>
+      </c>
+      <c r="P378" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="379" spans="2:17">
+      <c r="C379" t="s">
+        <v>7</v>
+      </c>
+      <c r="D379" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="380" spans="2:17">
+      <c r="C380" t="s">
+        <v>9</v>
+      </c>
+      <c r="D380" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="381" spans="2:17">
+      <c r="C381" t="s">
+        <v>11</v>
+      </c>
+      <c r="D381" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="382" spans="2:17">
+      <c r="B382">
+        <v>77</v>
+      </c>
+      <c r="C382" t="s">
+        <v>633</v>
+      </c>
+      <c r="O382" t="s">
+        <v>54</v>
+      </c>
+      <c r="P382" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q382" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="383" spans="2:17">
+      <c r="C383" t="s">
+        <v>5</v>
+      </c>
+      <c r="D383" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="384" spans="2:17">
+      <c r="C384" t="s">
+        <v>7</v>
+      </c>
+      <c r="D384" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="385" spans="2:17">
+      <c r="C385" t="s">
+        <v>9</v>
+      </c>
+      <c r="D385" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="386" spans="2:17">
+      <c r="C386" t="s">
+        <v>11</v>
+      </c>
+      <c r="D386" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="387" spans="2:17">
+      <c r="B387">
+        <v>78</v>
+      </c>
+      <c r="C387" t="s">
+        <v>640</v>
+      </c>
+      <c r="O387" t="s">
+        <v>54</v>
+      </c>
+      <c r="P387" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q387" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="388" spans="2:17">
+      <c r="C388" t="s">
+        <v>5</v>
+      </c>
+      <c r="D388" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="389" spans="2:17">
+      <c r="C389" t="s">
+        <v>7</v>
+      </c>
+      <c r="D389" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="390" spans="2:17">
+      <c r="C390" t="s">
+        <v>9</v>
+      </c>
+      <c r="D390" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="391" spans="2:17">
+      <c r="C391" t="s">
+        <v>11</v>
+      </c>
+      <c r="D391" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="392" spans="2:17">
+      <c r="B392">
+        <v>79</v>
+      </c>
+      <c r="C392" t="s">
+        <v>646</v>
+      </c>
+      <c r="O392" t="s">
+        <v>54</v>
+      </c>
+      <c r="P392" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q392" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="393" spans="2:17">
+      <c r="C393" t="s">
+        <v>5</v>
+      </c>
+      <c r="D393" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="394" spans="2:17">
+      <c r="C394" t="s">
+        <v>7</v>
+      </c>
+      <c r="D394" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="395" spans="2:17">
+      <c r="C395" t="s">
+        <v>9</v>
+      </c>
+      <c r="D395" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="396" spans="2:17">
+      <c r="C396" t="s">
+        <v>11</v>
+      </c>
+      <c r="D396" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="397" spans="2:17">
+      <c r="B397">
+        <v>80</v>
+      </c>
+      <c r="C397" t="s">
+        <v>654</v>
+      </c>
+      <c r="O397" t="s">
+        <v>54</v>
+      </c>
+      <c r="P397" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q397" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="398" spans="2:17">
+      <c r="C398" t="s">
+        <v>5</v>
+      </c>
+      <c r="D398" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="399" spans="2:17">
+      <c r="C399" t="s">
+        <v>7</v>
+      </c>
+      <c r="D399" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="400" spans="2:17">
+      <c r="C400" t="s">
+        <v>9</v>
+      </c>
+      <c r="D400" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="401" spans="2:17">
+      <c r="C401" t="s">
+        <v>11</v>
+      </c>
+      <c r="D401" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="402" spans="2:17">
+      <c r="B402">
+        <v>81</v>
+      </c>
+      <c r="C402" t="s">
+        <v>661</v>
+      </c>
+      <c r="O402" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P402" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q402" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="403" spans="2:17">
+      <c r="C403" t="s">
+        <v>5</v>
+      </c>
+      <c r="D403" t="s">
+        <v>662</v>
+      </c>
+      <c r="P403" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="404" spans="2:17">
+      <c r="C404" t="s">
+        <v>7</v>
+      </c>
+      <c r="D404" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="405" spans="2:17">
+      <c r="C405" t="s">
+        <v>9</v>
+      </c>
+      <c r="D405" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="406" spans="2:17">
+      <c r="C406" t="s">
+        <v>11</v>
+      </c>
+      <c r="D406" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="407" spans="2:17">
+      <c r="B407">
+        <v>82</v>
+      </c>
+      <c r="C407" t="s">
+        <v>669</v>
+      </c>
+      <c r="O407" t="s">
+        <v>54</v>
+      </c>
+      <c r="P407" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q407" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="408" spans="2:17">
+      <c r="C408" t="s">
+        <v>5</v>
+      </c>
+      <c r="D408" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="409" spans="2:17">
+      <c r="C409" t="s">
+        <v>7</v>
+      </c>
+      <c r="D409" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="410" spans="2:17">
+      <c r="C410" t="s">
+        <v>9</v>
+      </c>
+      <c r="D410" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="411" spans="2:17">
+      <c r="C411" t="s">
+        <v>11</v>
+      </c>
+      <c r="D411" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="412" spans="2:17">
+      <c r="B412">
+        <v>83</v>
+      </c>
+      <c r="C412" t="s">
+        <v>675</v>
+      </c>
+      <c r="O412" t="s">
+        <v>54</v>
+      </c>
+      <c r="P412" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q412" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="413" spans="2:17">
+      <c r="C413" t="s">
+        <v>5</v>
+      </c>
+      <c r="D413" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="414" spans="2:17">
+      <c r="C414" t="s">
+        <v>7</v>
+      </c>
+      <c r="D414" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="415" spans="2:17">
+      <c r="C415" t="s">
+        <v>9</v>
+      </c>
+      <c r="D415" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="416" spans="2:17">
+      <c r="C416" t="s">
+        <v>11</v>
+      </c>
+      <c r="D416" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="417" spans="2:17">
+      <c r="B417">
+        <v>84</v>
+      </c>
+      <c r="C417" t="s">
+        <v>682</v>
+      </c>
+      <c r="O417" t="s">
+        <v>54</v>
+      </c>
+      <c r="P417" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q417" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="418" spans="2:17">
+      <c r="C418" t="s">
+        <v>5</v>
+      </c>
+      <c r="D418" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="419" spans="2:17">
+      <c r="C419" t="s">
+        <v>7</v>
+      </c>
+      <c r="D419" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="420" spans="2:17">
+      <c r="C420" t="s">
+        <v>9</v>
+      </c>
+      <c r="D420" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="421" spans="2:17">
+      <c r="C421" t="s">
+        <v>11</v>
+      </c>
+      <c r="D421" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="422" spans="2:17">
+      <c r="B422">
+        <v>85</v>
+      </c>
+      <c r="C422" t="s">
+        <v>689</v>
+      </c>
+      <c r="O422" t="s">
+        <v>54</v>
+      </c>
+      <c r="P422" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q422" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="423" spans="2:17">
+      <c r="C423" t="s">
+        <v>5</v>
+      </c>
+      <c r="D423" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="424" spans="2:17">
+      <c r="C424" t="s">
+        <v>7</v>
+      </c>
+      <c r="D424" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="425" spans="2:17">
+      <c r="C425" t="s">
+        <v>9</v>
+      </c>
+      <c r="D425" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="426" spans="2:17">
+      <c r="C426" t="s">
+        <v>11</v>
+      </c>
+      <c r="D426" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="427" spans="2:17">
+      <c r="B427">
+        <v>86</v>
+      </c>
+      <c r="C427" t="s">
+        <v>696</v>
+      </c>
+      <c r="O427" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P427" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q427" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="428" spans="2:17">
+      <c r="C428" t="s">
+        <v>5</v>
+      </c>
+      <c r="D428" t="s">
+        <v>697</v>
+      </c>
+      <c r="P428" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="429" spans="2:17">
+      <c r="C429" t="s">
+        <v>7</v>
+      </c>
+      <c r="D429" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="430" spans="2:17">
+      <c r="C430" t="s">
+        <v>9</v>
+      </c>
+      <c r="D430" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="431" spans="2:17">
+      <c r="C431" t="s">
+        <v>11</v>
+      </c>
+      <c r="D431" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="432" spans="2:17">
+      <c r="B432">
+        <v>87</v>
+      </c>
+      <c r="C432" t="s">
+        <v>703</v>
+      </c>
+      <c r="O432" t="s">
+        <v>54</v>
+      </c>
+      <c r="P432" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q432" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="433" spans="2:17">
+      <c r="C433" t="s">
+        <v>5</v>
+      </c>
+      <c r="D433" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="434" spans="2:17">
+      <c r="C434" t="s">
+        <v>7</v>
+      </c>
+      <c r="D434" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="435" spans="2:17">
+      <c r="C435" t="s">
+        <v>9</v>
+      </c>
+      <c r="D435" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="436" spans="2:17">
+      <c r="C436" t="s">
+        <v>11</v>
+      </c>
+      <c r="D436" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="437" spans="2:17">
+      <c r="B437">
+        <v>88</v>
+      </c>
+      <c r="C437" t="s">
+        <v>708</v>
+      </c>
+      <c r="O437" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P437" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q437" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="438" spans="2:17">
+      <c r="C438" t="s">
+        <v>5</v>
+      </c>
+      <c r="D438" t="s">
+        <v>709</v>
+      </c>
+      <c r="P438" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="439" spans="2:17">
+      <c r="C439" t="s">
+        <v>7</v>
+      </c>
+      <c r="D439" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="440" spans="2:17">
+      <c r="C440" t="s">
+        <v>9</v>
+      </c>
+      <c r="D440" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="441" spans="2:17">
+      <c r="C441" t="s">
+        <v>11</v>
+      </c>
+      <c r="D441" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="442" spans="2:17">
+      <c r="B442">
+        <v>89</v>
+      </c>
+      <c r="C442" t="s">
+        <v>713</v>
+      </c>
+      <c r="O442" t="s">
+        <v>54</v>
+      </c>
+      <c r="P442" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q442" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="443" spans="2:17">
+      <c r="C443" t="s">
+        <v>5</v>
+      </c>
+      <c r="D443" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="444" spans="2:17">
+      <c r="C444" t="s">
+        <v>7</v>
+      </c>
+      <c r="D444" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="445" spans="2:17">
+      <c r="C445" t="s">
+        <v>9</v>
+      </c>
+      <c r="D445" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="446" spans="2:17">
+      <c r="C446" t="s">
+        <v>11</v>
+      </c>
+      <c r="D446" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="447" spans="2:17">
+      <c r="B447">
+        <v>90</v>
+      </c>
+      <c r="C447" t="s">
+        <v>720</v>
+      </c>
+      <c r="O447" t="s">
+        <v>54</v>
+      </c>
+      <c r="P447" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q447" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="448" spans="2:17">
+      <c r="C448" t="s">
+        <v>5</v>
+      </c>
+      <c r="D448" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="449" spans="2:17">
+      <c r="C449" t="s">
+        <v>7</v>
+      </c>
+      <c r="D449" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="450" spans="2:17">
+      <c r="C450" t="s">
+        <v>9</v>
+      </c>
+      <c r="D450" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="451" spans="2:17">
+      <c r="C451" t="s">
+        <v>11</v>
+      </c>
+      <c r="D451" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="452" spans="2:17">
+      <c r="B452">
+        <v>91</v>
+      </c>
+      <c r="C452" t="s">
+        <v>727</v>
+      </c>
+      <c r="O452" t="s">
+        <v>54</v>
+      </c>
+      <c r="P452" t="s">
+        <v>651</v>
+      </c>
+      <c r="Q452" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="453" spans="2:17">
+      <c r="C453" t="s">
+        <v>5</v>
+      </c>
+      <c r="D453" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="454" spans="2:17">
+      <c r="C454" t="s">
+        <v>7</v>
+      </c>
+      <c r="D454" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="455" spans="2:17">
+      <c r="C455" t="s">
+        <v>9</v>
+      </c>
+      <c r="D455" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="456" spans="2:17">
+      <c r="C456" t="s">
+        <v>11</v>
+      </c>
+      <c r="D456" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="457" spans="2:17">
+      <c r="B457">
+        <v>92</v>
+      </c>
+      <c r="C457" t="s">
+        <v>734</v>
+      </c>
+      <c r="O457" t="s">
+        <v>54</v>
+      </c>
+      <c r="P457" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q457" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="458" spans="2:17">
+      <c r="C458" t="s">
+        <v>5</v>
+      </c>
+      <c r="D458" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="459" spans="2:17">
+      <c r="C459" t="s">
+        <v>7</v>
+      </c>
+      <c r="D459" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="460" spans="2:17">
+      <c r="C460" t="s">
+        <v>9</v>
+      </c>
+      <c r="D460" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="461" spans="2:17">
+      <c r="C461" t="s">
+        <v>11</v>
+      </c>
+      <c r="D461" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="462" spans="2:17">
+      <c r="B462">
+        <v>93</v>
+      </c>
+      <c r="C462" t="s">
+        <v>739</v>
+      </c>
+      <c r="O462" t="s">
+        <v>54</v>
+      </c>
+      <c r="P462" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q462" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="463" spans="2:17">
+      <c r="C463" t="s">
+        <v>5</v>
+      </c>
+      <c r="D463" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="464" spans="2:17">
+      <c r="C464" t="s">
+        <v>7</v>
+      </c>
+      <c r="D464" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="465" spans="2:17">
+      <c r="C465" t="s">
+        <v>9</v>
+      </c>
+      <c r="D465" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="466" spans="2:17">
+      <c r="C466" t="s">
+        <v>11</v>
+      </c>
+      <c r="D466" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="467" spans="2:17">
+      <c r="B467">
+        <v>94</v>
+      </c>
+      <c r="C467" t="s">
+        <v>746</v>
+      </c>
+      <c r="O467" t="s">
+        <v>54</v>
+      </c>
+      <c r="P467" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q467" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="468" spans="2:17">
+      <c r="C468" t="s">
+        <v>5</v>
+      </c>
+      <c r="D468" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="469" spans="2:17">
+      <c r="C469" t="s">
+        <v>7</v>
+      </c>
+      <c r="D469" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="470" spans="2:17">
+      <c r="C470" t="s">
+        <v>9</v>
+      </c>
+      <c r="D470" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="471" spans="2:17">
+      <c r="C471" t="s">
+        <v>11</v>
+      </c>
+      <c r="D471" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="472" spans="2:17">
+      <c r="B472">
+        <v>95</v>
+      </c>
+      <c r="C472" t="s">
+        <v>751</v>
+      </c>
+      <c r="O472" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P472" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q472" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="473" spans="2:17">
+      <c r="C473" t="s">
+        <v>5</v>
+      </c>
+      <c r="D473" t="s">
+        <v>752</v>
+      </c>
+      <c r="P473" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="474" spans="2:17">
+      <c r="C474" t="s">
+        <v>7</v>
+      </c>
+      <c r="D474" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="475" spans="2:17">
+      <c r="C475" t="s">
+        <v>9</v>
+      </c>
+      <c r="D475" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="476" spans="2:17">
+      <c r="C476" t="s">
+        <v>11</v>
+      </c>
+      <c r="D476" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="477" spans="2:17">
+      <c r="B477">
+        <v>96</v>
+      </c>
+      <c r="C477" t="s">
+        <v>758</v>
+      </c>
+      <c r="O477" t="s">
+        <v>54</v>
+      </c>
+      <c r="P477" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q477" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="478" spans="2:17">
+      <c r="C478" t="s">
+        <v>5</v>
+      </c>
+      <c r="D478" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="479" spans="2:17">
+      <c r="C479" t="s">
+        <v>7</v>
+      </c>
+      <c r="D479" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="480" spans="2:17">
+      <c r="C480" t="s">
+        <v>9</v>
+      </c>
+      <c r="D480" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="481" spans="2:17">
+      <c r="C481" t="s">
+        <v>11</v>
+      </c>
+      <c r="D481" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="482" spans="2:17">
+      <c r="B482">
+        <v>97</v>
+      </c>
+      <c r="C482" t="s">
+        <v>763</v>
+      </c>
+      <c r="O482" t="s">
+        <v>54</v>
+      </c>
+      <c r="P482" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q482" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="483" spans="2:17">
+      <c r="C483" t="s">
+        <v>5</v>
+      </c>
+      <c r="D483" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="484" spans="2:17">
+      <c r="C484" t="s">
+        <v>7</v>
+      </c>
+      <c r="D484" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="485" spans="2:17">
+      <c r="C485" t="s">
+        <v>9</v>
+      </c>
+      <c r="D485" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="486" spans="2:17">
+      <c r="C486" t="s">
+        <v>11</v>
+      </c>
+      <c r="D486" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="487" spans="2:17">
+      <c r="B487">
+        <v>98</v>
+      </c>
+      <c r="C487" t="s">
+        <v>768</v>
+      </c>
+      <c r="O487" t="s">
+        <v>54</v>
+      </c>
+      <c r="P487" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q487" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="488" spans="2:17">
+      <c r="C488" t="s">
+        <v>5</v>
+      </c>
+      <c r="D488" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="489" spans="2:17">
+      <c r="C489" t="s">
+        <v>7</v>
+      </c>
+      <c r="D489" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="490" spans="2:17">
+      <c r="C490" t="s">
+        <v>9</v>
+      </c>
+      <c r="D490" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="491" spans="2:17">
+      <c r="C491" t="s">
+        <v>11</v>
+      </c>
+      <c r="D491" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="492" spans="2:17">
+      <c r="B492">
+        <v>99</v>
+      </c>
+      <c r="C492" t="s">
+        <v>773</v>
+      </c>
+      <c r="O492" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P492" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q492" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="493" spans="2:17">
+      <c r="C493" t="s">
+        <v>5</v>
+      </c>
+      <c r="D493" t="s">
+        <v>774</v>
+      </c>
+      <c r="P493" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="494" spans="2:17">
+      <c r="C494" t="s">
+        <v>7</v>
+      </c>
+      <c r="D494" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="495" spans="2:17">
+      <c r="C495" t="s">
+        <v>9</v>
+      </c>
+      <c r="D495" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="496" spans="2:17">
+      <c r="C496" t="s">
+        <v>11</v>
+      </c>
+      <c r="D496" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="497" spans="2:17">
+      <c r="B497">
+        <v>100</v>
+      </c>
+      <c r="C497" t="s">
+        <v>778</v>
+      </c>
+      <c r="O497" t="s">
+        <v>54</v>
+      </c>
+      <c r="P497" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q497" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="498" spans="2:17">
+      <c r="C498" t="s">
+        <v>5</v>
+      </c>
+      <c r="D498" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="499" spans="2:17">
+      <c r="C499" t="s">
+        <v>7</v>
+      </c>
+      <c r="D499" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="500" spans="2:17">
+      <c r="C500" t="s">
+        <v>9</v>
+      </c>
+      <c r="D500" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="501" spans="2:17">
+      <c r="C501" t="s">
+        <v>11</v>
+      </c>
+      <c r="D501" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="502" spans="2:17">
+      <c r="O502" s="3">
+        <f>COUNTIF(O2:O501,"○")/COUNTA(O2:O501)</f>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -13043,7 +17787,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D7C2EE-C8B5-4851-B670-42D9DD8D67DA}">
-  <dimension ref="B2:D189"/>
+  <dimension ref="B2:D257"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="2" spans="2:4">
@@ -14410,6 +19154,520 @@
     <row r="189" spans="2:4">
       <c r="D189" t="s">
         <v>597</v>
+      </c>
+    </row>
+    <row r="190" spans="2:4">
+      <c r="B190">
+        <v>72</v>
+      </c>
+      <c r="C190" t="s">
+        <v>5</v>
+      </c>
+      <c r="D190" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="191" spans="2:4">
+      <c r="D191" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="192" spans="2:4">
+      <c r="D192" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="193" spans="2:4">
+      <c r="B193">
+        <v>73</v>
+      </c>
+      <c r="C193" t="s">
+        <v>7</v>
+      </c>
+      <c r="D193" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="194" spans="2:4">
+      <c r="D194" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="195" spans="2:4">
+      <c r="D195" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="196" spans="2:4">
+      <c r="B196">
+        <v>74</v>
+      </c>
+      <c r="C196" t="s">
+        <v>11</v>
+      </c>
+      <c r="D196" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="197" spans="2:4">
+      <c r="D197" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="198" spans="2:4">
+      <c r="D198" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="199" spans="2:4">
+      <c r="B199">
+        <v>75</v>
+      </c>
+      <c r="C199" t="s">
+        <v>7</v>
+      </c>
+      <c r="D199" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="200" spans="2:4">
+      <c r="D200" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="201" spans="2:4">
+      <c r="D201" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="202" spans="2:4">
+      <c r="B202">
+        <v>76</v>
+      </c>
+      <c r="C202" t="s">
+        <v>7</v>
+      </c>
+      <c r="D202" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="203" spans="2:4">
+      <c r="D203" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="204" spans="2:4">
+      <c r="D204" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="205" spans="2:4">
+      <c r="B205">
+        <v>77</v>
+      </c>
+      <c r="C205" t="s">
+        <v>5</v>
+      </c>
+      <c r="D205" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="206" spans="2:4">
+      <c r="D206" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="207" spans="2:4">
+      <c r="D207" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="208" spans="2:4">
+      <c r="B208">
+        <v>78</v>
+      </c>
+      <c r="C208" t="s">
+        <v>7</v>
+      </c>
+      <c r="D208" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="209" spans="2:4">
+      <c r="D209" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="210" spans="2:4">
+      <c r="B210">
+        <v>79</v>
+      </c>
+      <c r="C210" t="s">
+        <v>11</v>
+      </c>
+      <c r="D210" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="211" spans="2:4">
+      <c r="D211" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="212" spans="2:4">
+      <c r="D212" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="213" spans="2:4">
+      <c r="B213">
+        <v>80</v>
+      </c>
+      <c r="C213" t="s">
+        <v>9</v>
+      </c>
+      <c r="D213" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="214" spans="2:4">
+      <c r="D214" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="215" spans="2:4">
+      <c r="D215" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="216" spans="2:4">
+      <c r="B216">
+        <v>81</v>
+      </c>
+      <c r="C216" t="s">
+        <v>9</v>
+      </c>
+      <c r="D216" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="217" spans="2:4">
+      <c r="D217" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="218" spans="2:4">
+      <c r="D218" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="219" spans="2:4">
+      <c r="D219" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="220" spans="2:4">
+      <c r="B220">
+        <v>82</v>
+      </c>
+      <c r="C220" t="s">
+        <v>9</v>
+      </c>
+      <c r="D220" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="221" spans="2:4">
+      <c r="D221" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="222" spans="2:4">
+      <c r="B222">
+        <v>83</v>
+      </c>
+      <c r="C222" t="s">
+        <v>5</v>
+      </c>
+      <c r="D222" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="223" spans="2:4">
+      <c r="D223" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="224" spans="2:4">
+      <c r="D224" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="225" spans="2:4">
+      <c r="B225">
+        <v>84</v>
+      </c>
+      <c r="C225" t="s">
+        <v>11</v>
+      </c>
+      <c r="D225" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="226" spans="2:4">
+      <c r="D226" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="227" spans="2:4">
+      <c r="D227" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="228" spans="2:4">
+      <c r="B228">
+        <v>85</v>
+      </c>
+      <c r="C228" t="s">
+        <v>7</v>
+      </c>
+      <c r="D228" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="229" spans="2:4">
+      <c r="D229" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="230" spans="2:4">
+      <c r="D230" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="231" spans="2:4">
+      <c r="B231">
+        <v>86</v>
+      </c>
+      <c r="C231" t="s">
+        <v>9</v>
+      </c>
+      <c r="D231" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="232" spans="2:4">
+      <c r="D232" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="233" spans="2:4">
+      <c r="D233" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="234" spans="2:4">
+      <c r="B234">
+        <v>87</v>
+      </c>
+      <c r="C234" t="s">
+        <v>7</v>
+      </c>
+      <c r="D234" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="235" spans="2:4">
+      <c r="B235">
+        <v>88</v>
+      </c>
+      <c r="C235" t="s">
+        <v>5</v>
+      </c>
+      <c r="D235" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="236" spans="2:4">
+      <c r="B236">
+        <v>89</v>
+      </c>
+      <c r="C236" t="s">
+        <v>7</v>
+      </c>
+      <c r="D236" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="237" spans="2:4">
+      <c r="D237" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="238" spans="2:4">
+      <c r="D238" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="239" spans="2:4">
+      <c r="B239">
+        <v>90</v>
+      </c>
+      <c r="C239" t="s">
+        <v>7</v>
+      </c>
+      <c r="D239" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="240" spans="2:4">
+      <c r="D240" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="241" spans="2:4">
+      <c r="D241" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="242" spans="2:4">
+      <c r="B242">
+        <v>91</v>
+      </c>
+      <c r="C242" t="s">
+        <v>11</v>
+      </c>
+      <c r="D242" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="243" spans="2:4">
+      <c r="D243" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="244" spans="2:4">
+      <c r="D244" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="245" spans="2:4">
+      <c r="B245">
+        <v>92</v>
+      </c>
+      <c r="C245" t="s">
+        <v>7</v>
+      </c>
+      <c r="D245" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="246" spans="2:4">
+      <c r="B246">
+        <v>93</v>
+      </c>
+      <c r="C246" t="s">
+        <v>7</v>
+      </c>
+      <c r="D246" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="247" spans="2:4">
+      <c r="D247" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="248" spans="2:4">
+      <c r="D248" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="249" spans="2:4">
+      <c r="B249">
+        <v>94</v>
+      </c>
+      <c r="C249" t="s">
+        <v>7</v>
+      </c>
+      <c r="D249" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="250" spans="2:4">
+      <c r="B250">
+        <v>95</v>
+      </c>
+      <c r="C250" t="s">
+        <v>9</v>
+      </c>
+      <c r="D250" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="251" spans="2:4">
+      <c r="D251" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="252" spans="2:4">
+      <c r="D252" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="253" spans="2:4">
+      <c r="B253">
+        <v>96</v>
+      </c>
+      <c r="C253" t="s">
+        <v>11</v>
+      </c>
+      <c r="D253" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="254" spans="2:4">
+      <c r="B254">
+        <v>97</v>
+      </c>
+      <c r="C254" t="s">
+        <v>11</v>
+      </c>
+      <c r="D254" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="255" spans="2:4">
+      <c r="B255">
+        <v>98</v>
+      </c>
+      <c r="C255" t="s">
+        <v>7</v>
+      </c>
+      <c r="D255" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="256" spans="2:4">
+      <c r="B256">
+        <v>99</v>
+      </c>
+      <c r="C256" t="s">
+        <v>9</v>
+      </c>
+      <c r="D256" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="257" spans="2:4">
+      <c r="B257">
+        <v>100</v>
+      </c>
+      <c r="C257" t="s">
+        <v>5</v>
+      </c>
+      <c r="D257" t="s">
+        <v>779</v>
       </c>
     </row>
   </sheetData>

--- a/UX検定_基礎.xlsx
+++ b/UX検定_基礎.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\UX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\勉強\資格(取得)\UX\基礎\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB2CED0-7CB6-49ED-A5C0-B0DCA62C825E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76ECC59-41EE-4CE4-9575-A34FDFDC34D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="模擬" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,8 @@
     <sheet name="練習問題_応用" sheetId="4" r:id="rId4"/>
     <sheet name="対策問題_kindle" sheetId="5" r:id="rId5"/>
     <sheet name="対策問題_kindle_解答" sheetId="6" r:id="rId6"/>
+    <sheet name="試験問題_kindle" sheetId="7" r:id="rId7"/>
+    <sheet name="試験問題_kindle_解答" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,12 +38,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1734" uniqueCount="783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="798">
   <si>
     <t>UXインテリジェンスが生み出す価値として重要視するものを、次の中から選びなさい。</t>
     <phoneticPr fontId="1"/>
@@ -11269,6 +11274,66 @@
     <rPh sb="17" eb="20">
       <t>ケイヤクショ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UX（User Experience）の説明として最も適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>製品やサービスを通じてユーザーが得る体験全体</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Webサイトの見た目やデザインの美しさ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>操作画面のレイアウトやボタン配置</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業が提供する製品の機能一覧</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ISOにおけるUXの定義として最も適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>製品やサービスの見た目と操作性の良さ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用や使用を通じて生じる、ユーザーの知覚や反応、感情などを含む体験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの操作ミスを減らすための画面設計手法</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの行動を分析するためのデータ収集手法</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ニールセン・ノーマンによるUXの説明として最も適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サイトの視覚デザインに対するユーザーの評価</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利便性を高めるための操作ガイドライン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザビリティテストの実施手法</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが製品やサービスとのやり取り全体で感じる体験</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -11617,7 +11682,7 @@
   <dimension ref="B2:P46"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="15" max="16" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
@@ -12084,7 +12149,7 @@
   <dimension ref="B2:W23"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="23" max="23" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:23">
@@ -12316,7 +12381,7 @@
   <dimension ref="B2:R27"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="18" max="18" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18">
@@ -12586,7 +12651,7 @@
   <dimension ref="B2:V23"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="22" max="22" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:22">
@@ -12812,7 +12877,7 @@
   <dimension ref="B2:Q502"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="17" max="17" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17">
@@ -19675,4 +19740,1235 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C845BB36-B0DB-4C2A-95B5-F571F2C7EDEB}">
+  <dimension ref="B2:Q16"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="17" max="17" width="10.19921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:17">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>783</v>
+      </c>
+      <c r="O2" t="s">
+        <v>54</v>
+      </c>
+      <c r="P2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="3" spans="2:17">
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17">
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17">
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17">
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17">
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>788</v>
+      </c>
+      <c r="O7" t="s">
+        <v>54</v>
+      </c>
+      <c r="P7" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17">
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17">
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17">
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17">
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17">
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>793</v>
+      </c>
+      <c r="O12" t="s">
+        <v>54</v>
+      </c>
+      <c r="P12" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17">
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17">
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17">
+      <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="16" spans="2:17">
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>797</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7AE5092-D86D-475B-9058-32DEEFAA368E}">
+  <dimension ref="B2:C211"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="2" spans="2:3">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="B5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="B6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="B8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3">
+      <c r="B9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3">
+      <c r="B10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
+      <c r="B11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3">
+      <c r="B12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3">
+      <c r="B13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3">
+      <c r="B14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3">
+      <c r="B15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3">
+      <c r="B16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2">
+      <c r="B80">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2">
+      <c r="B88">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2">
+      <c r="B89">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2">
+      <c r="B90">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2">
+      <c r="B91">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2">
+      <c r="B92">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2">
+      <c r="B93">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2">
+      <c r="B94">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2">
+      <c r="B95">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2">
+      <c r="B96">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2">
+      <c r="B98">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2">
+      <c r="B99">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2">
+      <c r="B100">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2">
+      <c r="B101">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2">
+      <c r="B102">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2">
+      <c r="B103">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2">
+      <c r="B104">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="2:2">
+      <c r="B105">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2">
+      <c r="B106">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2">
+      <c r="B107">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2">
+      <c r="B108">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2">
+      <c r="B109">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2">
+      <c r="B110">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2">
+      <c r="B111">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2">
+      <c r="B112">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2">
+      <c r="B113">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2">
+      <c r="B114">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2">
+      <c r="B115">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2">
+      <c r="B116">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2">
+      <c r="B117">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2">
+      <c r="B118">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2">
+      <c r="B119">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2">
+      <c r="B120">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2">
+      <c r="B121">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2">
+      <c r="B122">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2">
+      <c r="B123">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2">
+      <c r="B124">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2">
+      <c r="B125">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2">
+      <c r="B126">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2">
+      <c r="B127">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="2:2">
+      <c r="B128">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2">
+      <c r="B129">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2">
+      <c r="B130">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2">
+      <c r="B131">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2">
+      <c r="B132">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2">
+      <c r="B133">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="2:2">
+      <c r="B134">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2">
+      <c r="B135">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2">
+      <c r="B136">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="2:2">
+      <c r="B137">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2">
+      <c r="B138">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2">
+      <c r="B139">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="2:2">
+      <c r="B140">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="2:2">
+      <c r="B141">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2">
+      <c r="B142">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="2:2">
+      <c r="B143">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="2:2">
+      <c r="B144">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2">
+      <c r="B145">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2">
+      <c r="B146">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2">
+      <c r="B147">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2">
+      <c r="B148">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2">
+      <c r="B149">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="2:2">
+      <c r="B150">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2">
+      <c r="B151">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2">
+      <c r="B152">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="2:2">
+      <c r="B153">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="2:2">
+      <c r="B154">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="2:2">
+      <c r="B155">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2">
+      <c r="B156">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="2:2">
+      <c r="B157">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2">
+      <c r="B158">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="2:2">
+      <c r="B159">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160" spans="2:2">
+      <c r="B160">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2">
+      <c r="B161">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2">
+      <c r="B162">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2">
+      <c r="B163">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2">
+      <c r="B164">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" spans="2:2">
+      <c r="B165">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2">
+      <c r="B166">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2">
+      <c r="B167">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2">
+      <c r="B168">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="2:2">
+      <c r="B169">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="2:2">
+      <c r="B170">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" spans="2:2">
+      <c r="B171">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2">
+      <c r="B172">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="2:2">
+      <c r="B173">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" spans="2:2">
+      <c r="B174">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" spans="2:2">
+      <c r="B175">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="2:2">
+      <c r="B176">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2">
+      <c r="B178">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2">
+      <c r="B179">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="2:2">
+      <c r="B180">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181" spans="2:2">
+      <c r="B181">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="2:2">
+      <c r="B182">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" spans="2:2">
+      <c r="B183">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" spans="2:2">
+      <c r="B184">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="2:2">
+      <c r="B185">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="2:2">
+      <c r="B186">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" spans="2:2">
+      <c r="B187">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188" spans="2:2">
+      <c r="B188">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189" spans="2:2">
+      <c r="B189">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190" spans="2:2">
+      <c r="B190">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191" spans="2:2">
+      <c r="B191">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192" spans="2:2">
+      <c r="B192">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193" spans="2:2">
+      <c r="B193">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198" spans="2:2">
+      <c r="B198">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199" spans="2:2">
+      <c r="B199">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200" spans="2:2">
+      <c r="B200">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201" spans="2:2">
+      <c r="B201">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="202" spans="2:2">
+      <c r="B202">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="203" spans="2:2">
+      <c r="B203">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="204" spans="2:2">
+      <c r="B204">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="205" spans="2:2">
+      <c r="B205">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="206" spans="2:2">
+      <c r="B206">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="207" spans="2:2">
+      <c r="B207">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="208" spans="2:2">
+      <c r="B208">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="209" spans="2:2">
+      <c r="B209">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="210" spans="2:2">
+      <c r="B210">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="211" spans="2:2">
+      <c r="B211">
+        <v>210</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/UX検定_基礎.xlsx
+++ b/UX検定_基礎.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\勉強\資格(取得)\UX\基礎\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76ECC59-41EE-4CE4-9575-A34FDFDC34D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A69786-6A51-47DE-9162-B5C8ACFB1540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="模擬" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,12 @@
     <sheet name="練習問題_応用" sheetId="4" r:id="rId4"/>
     <sheet name="対策問題_kindle" sheetId="5" r:id="rId5"/>
     <sheet name="対策問題_kindle_解答" sheetId="6" r:id="rId6"/>
-    <sheet name="試験問題_kindle" sheetId="7" r:id="rId7"/>
-    <sheet name="試験問題_kindle_解答" sheetId="8" r:id="rId8"/>
+    <sheet name="試験問題_Lv1_kindle" sheetId="7" r:id="rId7"/>
+    <sheet name="試験問題_kindle_Lv1_解答" sheetId="8" r:id="rId8"/>
+    <sheet name="試験問題_Lv2_kindle" sheetId="9" r:id="rId9"/>
+    <sheet name="試験問題_kindle_Lv2_解答" sheetId="10" r:id="rId10"/>
+    <sheet name="試験問題_Lv3_kindle" sheetId="11" r:id="rId11"/>
+    <sheet name="試験問題_kindle_Lv3_解答" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2543" uniqueCount="1117">
   <si>
     <t>UXインテリジェンスが生み出す価値として重要視するものを、次の中から選びなさい。</t>
     <phoneticPr fontId="1"/>
@@ -11334,6 +11338,1291 @@
   </si>
   <si>
     <t>ユーザーが製品やサービスとのやり取り全体で感じる体験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXPA（User Experience Professionals Association）によるUXの説明として最も適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サービスの広告に対するユーザーの評価</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIデザインの完成度</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーと製品・サービスとのやり取りを通じた知覚、感情、反応などの体験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>システム開発工程の効率と生産性</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXのハニカム構造で示される重要な視点として最も適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開発プロセスと工数管理の最適化</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Useful（役に立つ）、Usable（使いやすい）、Desirable（望ましい）など複数の要素から成る</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIデザインのみを最適化するための指標</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業のブランドロゴ設計に関するガイドライン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXの５階層モデルで最も基礎となる層はどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戦略（Strategy）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>構造（Structure）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表層（Surface）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>骨格（Skeleton）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ハッセンツァール・モデルにおいて、UXの重要な構成要素として挙げられるのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業の市場シェアと投資対効果</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品のパッケージデザインのみ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実用的品質と感性的品質</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サービス運用コストと広告効果</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UX白書モデルが示すUXの特徴として最も適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIのデザイン品質だけで決まる体験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文脈、時間、個人の状態により変化する動的な体験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機能要件を満たしているかどうかのみで判断される体験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブランド広告の印象によって決まる体験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXとユーザビリティの関係として最も適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXはユーザビリティを含むより広い概念である</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザビリティはUXを包含し、UXの派生概念である</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXとユーザビリティはほぼ同義で区別する必要はない</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXは機能性の評価、ユーザビリティは感情の評価を指す</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIの説明として最も適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの感情や体験全体</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー調査や体験設計のプロセス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>システムの内部構造と処理方式</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーとシステムが接触する見た目や操作方法などの接点</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DXの最も基本的な説明として適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新しいITツールを導入すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紙の業務をデジタル化することだけを指す</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デジタル技術を活用し、ビジネスモデルや業務、顧客体験を変革すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社内のIT機器を最新モデルに更新すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CXの基本的な説明として最も適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Webサイトの操作性に特化した指標</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIデザインを最適化するプロセス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社内業務プロセス改善の取り組み</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業やブランドと顧客が接点を持つすべての体験・印象</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EXの基本的な説明として最も適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>顧客と企業の接点全体を指す概念</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>従業員が企業との関わりを通じて得る体験や印象</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>システム操作時の使いやすさに関する評価</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIデザイン品質を高める取り組み</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OMOの最も基本的な説明として適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オンラインとオフラインの体験が統合され、境界なくつながる考え方</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オフライン中心でオンラインを補助的に使う戦略</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インターネットを使わない顧客接点の最適化手法</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オンライン広告の効果を高めるための施策</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D2Cモデルの最も基本的な説明として適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>量販店経由で顧客に販売するモデル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小売業者と提携して販路を拡大する戦略</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブランドが中間業者を介さず、直接顧客に販売するモデル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業間取引のみを行う販売モデル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プラットフォームビジネスの最も基本的な説明として適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自社製品を大量生産し販売するモデル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>参加者同士が価値を交換する場を企業が提供し、ネットワーク効果を生むモデル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業が小売店を通じて商品を販売するモデル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>組織内部の業務効率を向上するビジネスモデル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXにおけるユーザーとステークホルダーの広がりを最も適切に説明しているのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXはデザイナーのみが関与する領域になった</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXは主に経営層の意思決定だけに影響する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXの対象が、顧客だけでなく従業員、パートナー、社会全体に広がっている</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXはサービス利用者のみを対象とするべきである</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXにおける「ビッグデータ」が示す役割として最も適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー行動や利用状況を大量かつ多面的に把握し、体験の改善に活用する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サービスの見た目を華やかにするために使用する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小規模なユーザー調査を代替する唯一の手法である</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>年齢、性別、居住地域など、ユーザーの基本情報</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXよりも企業の財務戦略に特化したデータのこと</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>属性データの説明として最も適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アプリの利用ログやクリックデータ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セッション内での遷移履歴</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>顧客が購入した商品の一覧</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>行動データの説明として最も適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが実際に行った操作や行動に関する記録</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの性別や年齢などの基本情報</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業内部の経理データ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マーケティング担当者の主観的評価</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXにおける「ID統合」の説明として最も適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業がユーザーのデバイスを管理する仕組み</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>複数のサービスやチャネルで同じユーザーIDを利用できるようにする仕組み</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社内で利用される従業員IDの発行ルール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SNSアカウントの削除手続き</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UX文脈におけるデータリテラシーの説明として最も適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データを収集せず経験則で意思決定する力</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プログラミング言語を習得する能力</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データを理解し活用して改善につなげる力</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>顧客データを営業部署に渡す権限</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AIの普及がUXに影響を与える理由として最も適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AIが全てのサービス開発を自動化するため</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AIによりユーザー個別の状況に応じた体験の最適化が進むため</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AIは主に社内業務効率化のみを目的とするため</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UX設計が不要になるため</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXデザインの基本的な目的として最も適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業の利益を最優先にすること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最新技術を積極的に導入すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが心地よく目的を達成できる体験を設計すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザインを見た目だけで魅力的にすること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXデザイナーの役割として最も適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プログラムコードの最適化のみを担当する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー視点で体験全体を設計し、使いやすさと満足度を高める</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>製品の販売促進や広告戦略のみを担当する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グラフィック要素の制作に特化した職種である</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「アフターデジタル」という考え方を最も正しく説明しているのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デジタル技術が不要になる社会</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オフライン体験を重視し、オンラインは排除する社会</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デジタル化が未成熟な社会</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オンラインとオフラインの区別がなく、常にデジタルが前提となる社会</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「体験提供型」のビジネスとはどのような考え方を指すか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>製品やサービスそのものより、ユーザーが得る体験価値を中心に設計・提供する考え方</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コスト削減を最優先にする経営手法</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザインよりも販売戦略を重視する手法</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>技術力をアピールして顧客を獲得する戦略</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「バリュージャーニー」とは何を表す概念か、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業内部の業務フローを最適化する仕組み</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが製品・サービスを通じて得る価値体験のプロセス全体</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>広告から購入までのマーケティング施策の一覧</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サービスの費用対効果を測定する会計手法</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「バリューチェーン」の基本的な説明として最も適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業の財務データを分析する仕組み</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>顧客の購買心理を段階的に整理する理論</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>製品やサービスが価値を生み出す一連の活動のつながりを分析する枠組み</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>組織の広告宣伝活動のみを評価する手法</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXの観点における特定シーンにおける大きな成功を正しく説明しているのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業が短期的に利益を上げること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが特定の状況・文脈で高い満足や価値を感じる体験を実現すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>広告キャンペーンで注目を集めること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UX全体ではなく、一部機能だけに注力すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ジャーニー使用料請求モデル」の基本的な考え方として最も適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サービス利用開始時に一律の料金を請求するモデル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>製品の所有権を顧客に完全に移転するモデル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの利用プロセスや体験の価値に応じて料金を設定するモデル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>広告閲覧回数に応じて課金するモデル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>無料版ジャーニーへの潜在顧客滞留とはどのような現象を指すか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>無料版ユーザーが即座に解約する現象</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>無料版を長期間利用し続けるが、有料版に移行しない状態が続く現象</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>有料版ユーザーが無料版を併用して利用する現象</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>無料期間終了後にアカウントが自動削除される現象</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXの文脈で「機能提供者」とは主にどのような立場を指すか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが利用する機能やサービスを設計・提供する側</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サービスの利用者自身</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>製品の販売代理店</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マーケティングデータを分析する外部企業</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「売り切り型収益モデル」を最も正しく説明しているのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サービス利用期間に応じて継続的に料金を支払うモデル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用データに基づいて成果報酬を支払うモデル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品やサービスを一度購入すれば取引が完結するモデル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>無料利用を通じて広告収入を得るモデル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ファネル型マーケティング」の基本的な考え方として最も適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>顧客を一度に大量に獲得することだけを目的とする手法</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全ユーザーに同一のメッセージを送る仕組み</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すべての段階で広告費を均等に配分する戦略</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>潜在顧客を上から順に絞り込み、最終的に購買や契約に至るプロセスとして捉える手法</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「UXグロース」を最も正しく説明しているのはどれか、次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー体験を継続的に改善し、事業成長につなげる考え方</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXデザインを一度完成させたら、そのまま維持する考え方</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新機能を次々追加してユーザー数を増やす戦略</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>広告費を増やして顧客を拡大するマーケティング手法</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXグロースにおける「グロースチーム」の主な役割として最も適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>経理や法務などのバックオフィス業務を担当する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データ分析・UX改善・マーケティングを横断して、事業成長を推進する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UIデザインのみを専門的に行う</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新規事業の立ち上げを担当する部署の別名</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「トップダウン型UXグロース活動」を最も正しく説明しているのはどれか、次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現場チームが自律的にUX改善を進める活動</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>外部コンサルタントにUX戦略を全面委託する取り組み</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>経営層やマネジメントが主導して、組織全体でUX向上を推進する活動</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー自身がUX改善の方針を決定する仕組み</t>
+    <rPh sb="4" eb="6">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ホウシン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ケッテイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>シク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ボトムアップ型UXグロース活動」を最も正しく説明しているのはどれか、次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現場メンバーが自発的にUX改善を提案・実践し、組織に広げていく活動</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>経営層が戦略的にUXを指示する活動</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>外部コンサルタントによるUX分析を中心とする活動</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用者が直接UX改善に参加する活動</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXにおける抜本改善とはどのような取り組みを指すか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザインの配色や文言など小さな変更を繰り返す改善</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>既存の仕組みを根本から見直し、体験の構造や価値そのものを再設計する改善</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不具合修正など、短期的な調整作業</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用マニュアルを更新するだけの改善</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXにおける高速改善とはどのような取り組みを指すか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>改善施策を一度決めたら長期間変更しない手法</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー調査を省略してコスト削減を目的とする手法</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小さな仮説を立てて素早く検証し、短いサイクルで改善を重ねる手法</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>改善を一括で行い、大規模リリースを繰り返す手法</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXにおける「選択の自由」を最も正しく説明しているのはどれか、次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業がユーザーの選択肢を制限し、最適な行動に誘導すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXデザイナーが想定した行動だけをユーザーに選ばせること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サービス提供者が全ての操作を自動化すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが自分の目的や状況に応じて、最適な体験を自由に選択できる状態を実現すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「多様な自由の調和」をUXの理念として最も正しく説明しているのはどれか、次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業が提供する体験を統一し、ユーザーの自由を制限すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー、企業、社会など、立場の異なる関係者の自由や価値観を調和させ、共に満足できる体験を目指すこと</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの自由を最優先し、企業の目的を無視すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UX設計を特定の文化圏や属性に限定して行うこと</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社会アーキテクチャーの設計の分散化を最も正しく説明しているのはどれか、次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>政府や企業が社会システムを一元的に設計・管理すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXデザイナーのみが体験全体を決定すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーやコミュニティなど多様な主体が、社会やサービスの設計に参加できるようにすること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ITシステムのサーバーを分散配置すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXの観点で「テクノロジー悪用によるディストピア」とはどのような状況を指すか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テクノロジーが人々の体験や自由を制限し、監視や操作が進む社会</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新しいテクノロジーが便利なUXを実現する社会</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人工知能が正しく倫理的に活用されている社会</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用者が自分でサービスを選び体験を最適化できる社会</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXの理念としての「ユーザー管理・コントロール」を最も正しく説明しているのはどれか、次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業がユーザーの行動を効率的に管理・監視すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー自身が、自分のデータや体験の在り方を主体的に管理・選択できること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>管理者が全ての操作を自動化してユーザーを介在させないこと</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UX設計者がユーザーの行動を完全に誘導すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「データのUX還元」とはどのような考え方を指すか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>収集したデータをマーケティング広告のみに利用すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データを社内で保管し、外部には一切公開しないこと</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーから得たデータを分析し、体験価値の向上やサービス改善に活かすこと</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データを利用せず、感覚的にUXを設計すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UX企画力を最も正しく説明しているのはどれか、次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザインツールの操作技術を高める力</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー体験の価値を中心に、製品やサービスの企画を立案する力</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プログラムコードを効率よく書く力</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>売上目標だけに基づいて製品を設計する力</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXにおける「ユーザー理解」とは何を意味するか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの目的・行動・感情・文脈を深く把握し、体験設計に反映すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>顧客情報を数値として分析し、売上を最大化すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自社製品の特徴をユーザーに理解させること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アクセス数を増やすための施策を考えること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXインテリジェンスの理念における「ビジネス構築」とは何を指すか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業の収益を最大化するためにUXを削減すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マーケティング部門のみで事業を設計すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXデザイナーが広告戦略を担当すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー体験を軸に、価値提供と収益構造を設計すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXにおける「世界観の体現」を最も正しく説明しているのはどれか、次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業のビジョンや理念をスローガンとして表示すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>広告やロゴのデザインを統一すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブランドやサービスが持つ価値観やストーリーを、ユーザー体験全体を通して感じさせること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>世界的なトレンドを反映したデザインを採用すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「グロースチーム運用」を最も正しく説明しているのはどれか、次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>営業部門が売上向上のために単独で行う活動</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイン・開発・マーケティングなどの専門職が協働し、データに基づいてUX改善を継続的に行う運営体制</t>
+  </si>
+  <si>
+    <t>プロジェクトごとに独立して動く短期的チームのこと</t>
+  </si>
+  <si>
+    <t>経営層だけでUX施策を意思決定する体制</t>
+  </si>
+  <si>
+    <t>人間中心デザインにおける「利用者視点」を最も正しく説明しているのはどれか、次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイナーの好みや感性を中心にデザインを決定すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>経営者の意向を優先してシステムを構築すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>製品やサービスを利用する人の目的・文脈・感情を理解し、その体験を中心に設計すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>技術的制約を優先してデザインを簡略化すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人間中心デザインにおける「共創」を最も正しく説明しているのはどれか、次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイナーだけが中心となって製品を完成させること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業がユーザーに完成品を提示して意見を求めること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの行動を観察するが、設計には参加させないこと</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業・デザイナー・ユーザーなど多様な関係者が協働して、新たな体験価値を生み出すこと</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人間中心デザインの基本的な考え方として最も適切なのはどれか、次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイナーの感性やセンスを最優先して設計する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>技術的制約を基準にして設計方針を決める</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用者の目的・行動・感情を理解し、その体験をより良くするために設計を行う</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成果物を早く完成させることを最優先にする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ISO 9241-210で定義されている人間中心デザインの６原則のうち正しい内容はどれか、次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイナーの主観を中心に設計する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>技術的要件を最優先して設計を進める</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>経営層の意思決定に基づいてUXを固定化する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設計は利用者のニーズ、要求、状況の理解に基づく</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人間中心デザインにおける「目標達成」の考え方として最も正しいものはどれか、次の中から選びなさい。</t>
+  </si>
+  <si>
+    <t>利用者が自分の目的を効率的かつ満足感を持って達成できるように設計する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業の売上目標を最優先にして機能を配置する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開発者が使いやすい設計を目指す</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザインの見た目を優先して体験価値を後回しにする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人間中心デザインの「４つの主要活動」として正しいものはどれか、次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>計画 → 評価 → 開発 → 販売</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用状況の理解 → 要件の明確化 → 解決策の作成 → 設計の評価</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標設定 → 実行 → 管理 → 改善</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>調査 → 設計 → 実装 → リリース</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人間中心デザインにおける「ユーザー」の定義として最も正しいものはどれか、次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>製品やサービスを販売する企業の社員</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サービスを設計する開発チーム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実際に製品やサービスを使用する人</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サービスを監督・承認する経営層</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユニバーサルデザインの基本的な考え方として最も正しいものはどれか、次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特定の障がい者向けに特化したデザイン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>年齢・性別・障がいの有無などにかかわらず、すべての人が利用しやすいデザイン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザインを簡素化してコストを下げる考え方</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最新のテクノロジーを優先的に取り入れるデザイン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザインマネジメントの目的として最も適切なのはどれか、次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイナー個人の感性を最大限に表現するための活動</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザインを芸術として評価するための組織体制の整備</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>製品の見た目を統一することだけを目的とする活動</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザインを経営資源として活用し、組織全体の価値創造につなげる活動</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイン思考における「デザイン」という言葉の意味として最も正しいものはどれか、次の中から選びなさい。</t>
+  </si>
+  <si>
+    <t>プロダクトの外観や色彩の美しさを整えること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アート作品のように感性を表現すること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人間の課題を理解し、創造的に解決するための思考・プロセス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>広告やロゴを制作するための視覚的活動</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイン思考における「ユーザー視点」の基本的な考え方として最も正しいものはどれか、次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの立場に立ち、ニーズや感情を理解した上で解決策を考える</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが望む内容をすべて取り入れて設計する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>市場データや競合分析の結果のみを重視して設計を行う</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイナーの経験と直感を優先して意思決定する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイン思考における「課題・ニーズの発見」で最も重要な姿勢はどれか、正しいものを次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業の目標を中心に、ユーザーの意見は参考程度に扱う</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの行動や感情を観察し、表面的な要望の奥にある本質的な課題を見つける</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>過去の成功事例を模倣し、安定した課題設定を行う</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">統計データだけをもとに課題を数値化する </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダブルダイヤモンドモデルの基本的な構成として最も正しいものはどれか、次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>観察 → 発想 → 実装 → 評価</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企画 → 設計 → 実装 → 運用</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>調査 → 企画 → 広告 → 販売</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>課題の発見 → 課題の定義 → 解決策の創出 → 解決策の実現</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザイン思考の５つのステップのうち、正しい順序として最も適切なのはどれか、次の中から選びなさい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>定義 → 共感 → 発想 → プロトタイプ → テスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>発想 → 定義 → 共感 → テスト → プロトタイプ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>共感 → 発想 → 定義 → テスト → プロトタイプ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アジャイル開発の基本的な考え方として最も正しいものはどれか、次の中から選びなさい。</t>
+  </si>
+  <si>
+    <t>仕様を最初に完全に決定し、変更を極力避ける</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>変化に柔軟に対応しながら、短いサイクルで改善を繰り返す</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロジェクトの全工程を文書化し、厳格に管理する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>成果物を一度だけリリースして評価する</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -12144,6 +13433,36 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2A52FAF-5790-423D-A8DD-955A034BED2E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17AF59C5-DF61-42ED-8998-32028D4B8AB2}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BCCF900-BD63-43AD-930D-63CB47F7722D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD902BA-2E46-4FD5-988A-568EC1B1B6E2}">
   <dimension ref="B2:W23"/>
@@ -19744,7 +21063,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C845BB36-B0DB-4C2A-95B5-F571F2C7EDEB}">
-  <dimension ref="B2:Q16"/>
+  <dimension ref="B2:Q336"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="17" max="17" width="10.19921875" bestFit="1" customWidth="1"/>
@@ -19757,15 +21076,6 @@
       <c r="C2" t="s">
         <v>783</v>
       </c>
-      <c r="O2" t="s">
-        <v>54</v>
-      </c>
-      <c r="P2" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q2" s="1">
-        <v>46103</v>
-      </c>
     </row>
     <row r="3" spans="2:17">
       <c r="C3" t="s">
@@ -19774,6 +21084,15 @@
       <c r="D3" t="s">
         <v>784</v>
       </c>
+      <c r="O3" t="s">
+        <v>54</v>
+      </c>
+      <c r="P3" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>46103</v>
+      </c>
     </row>
     <row r="4" spans="2:17">
       <c r="C4" t="s">
@@ -19806,15 +21125,6 @@
       <c r="C7" t="s">
         <v>788</v>
       </c>
-      <c r="O7" t="s">
-        <v>54</v>
-      </c>
-      <c r="P7" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>46103</v>
-      </c>
     </row>
     <row r="8" spans="2:17">
       <c r="C8" t="s">
@@ -19823,6 +21133,15 @@
       <c r="D8" t="s">
         <v>789</v>
       </c>
+      <c r="O8" t="s">
+        <v>54</v>
+      </c>
+      <c r="P8" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>46103</v>
+      </c>
     </row>
     <row r="9" spans="2:17">
       <c r="C9" t="s">
@@ -19855,15 +21174,6 @@
       <c r="C12" t="s">
         <v>793</v>
       </c>
-      <c r="O12" t="s">
-        <v>54</v>
-      </c>
-      <c r="P12" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>46103</v>
-      </c>
     </row>
     <row r="13" spans="2:17">
       <c r="C13" t="s">
@@ -19872,6 +21182,15 @@
       <c r="D13" t="s">
         <v>794</v>
       </c>
+      <c r="O13" t="s">
+        <v>54</v>
+      </c>
+      <c r="P13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>46103</v>
+      </c>
     </row>
     <row r="14" spans="2:17">
       <c r="C14" t="s">
@@ -19895,6 +21214,3157 @@
       </c>
       <c r="D16" t="s">
         <v>797</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17">
+      <c r="B17">
+        <v>4</v>
+      </c>
+      <c r="C17" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17">
+      <c r="C18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" t="s">
+        <v>799</v>
+      </c>
+      <c r="O18" t="s">
+        <v>54</v>
+      </c>
+      <c r="P18" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17">
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17">
+      <c r="C20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17">
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17">
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17">
+      <c r="C23" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" t="s">
+        <v>804</v>
+      </c>
+      <c r="O23" t="s">
+        <v>54</v>
+      </c>
+      <c r="P23" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17">
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17">
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17">
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17">
+      <c r="B27">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17">
+      <c r="C28" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" t="s">
+        <v>809</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P28" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17">
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" t="s">
+        <v>810</v>
+      </c>
+      <c r="P29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17">
+      <c r="C30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17">
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17">
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17">
+      <c r="C33" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" t="s">
+        <v>814</v>
+      </c>
+      <c r="O33" t="s">
+        <v>54</v>
+      </c>
+      <c r="P33" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17">
+      <c r="C34" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17">
+      <c r="C35" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="36" spans="2:17">
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17">
+      <c r="B37">
+        <v>8</v>
+      </c>
+      <c r="C37" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="38" spans="2:17">
+      <c r="C38" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" t="s">
+        <v>819</v>
+      </c>
+      <c r="O38" t="s">
+        <v>54</v>
+      </c>
+      <c r="P38" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17">
+      <c r="C39" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="40" spans="2:17">
+      <c r="C40" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="41" spans="2:17">
+      <c r="C41" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17">
+      <c r="B42">
+        <v>9</v>
+      </c>
+      <c r="C42" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17">
+      <c r="C43" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43" t="s">
+        <v>824</v>
+      </c>
+      <c r="O43" t="s">
+        <v>54</v>
+      </c>
+      <c r="P43" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17">
+      <c r="C44" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17">
+      <c r="C45" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17">
+      <c r="C46" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17">
+      <c r="B47">
+        <v>10</v>
+      </c>
+      <c r="C47" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17">
+      <c r="C48" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" t="s">
+        <v>829</v>
+      </c>
+      <c r="O48" t="s">
+        <v>54</v>
+      </c>
+      <c r="P48" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q48" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="49" spans="2:17">
+      <c r="C49" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="50" spans="2:17">
+      <c r="C50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="51" spans="2:17">
+      <c r="C51" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="52" spans="2:17">
+      <c r="B52">
+        <v>11</v>
+      </c>
+      <c r="C52" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="53" spans="2:17">
+      <c r="C53" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53" t="s">
+        <v>834</v>
+      </c>
+      <c r="O53" t="s">
+        <v>54</v>
+      </c>
+      <c r="P53" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q53" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="54" spans="2:17">
+      <c r="C54" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="55" spans="2:17">
+      <c r="C55" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="56" spans="2:17">
+      <c r="C56" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="57" spans="2:17">
+      <c r="B57">
+        <v>12</v>
+      </c>
+      <c r="C57" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="58" spans="2:17">
+      <c r="C58" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" t="s">
+        <v>839</v>
+      </c>
+      <c r="O58" t="s">
+        <v>54</v>
+      </c>
+      <c r="P58" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q58" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="59" spans="2:17">
+      <c r="C59" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="60" spans="2:17">
+      <c r="C60" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="61" spans="2:17">
+      <c r="C61" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="62" spans="2:17">
+      <c r="B62">
+        <v>13</v>
+      </c>
+      <c r="C62" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="63" spans="2:17">
+      <c r="C63" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63" t="s">
+        <v>844</v>
+      </c>
+      <c r="O63" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q63" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="64" spans="2:17">
+      <c r="C64" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" t="s">
+        <v>845</v>
+      </c>
+      <c r="P64" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17">
+      <c r="C65" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17">
+      <c r="C66" t="s">
+        <v>11</v>
+      </c>
+      <c r="D66" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17">
+      <c r="B67">
+        <v>14</v>
+      </c>
+      <c r="C67" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="68" spans="2:17">
+      <c r="C68" t="s">
+        <v>5</v>
+      </c>
+      <c r="D68" t="s">
+        <v>849</v>
+      </c>
+      <c r="O68" t="s">
+        <v>54</v>
+      </c>
+      <c r="P68" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q68" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17">
+      <c r="C69" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17">
+      <c r="C70" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17">
+      <c r="C71" t="s">
+        <v>11</v>
+      </c>
+      <c r="D71" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17">
+      <c r="B72">
+        <v>15</v>
+      </c>
+      <c r="C72" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17">
+      <c r="C73" t="s">
+        <v>5</v>
+      </c>
+      <c r="D73" t="s">
+        <v>854</v>
+      </c>
+      <c r="O73" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P73" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q73" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17">
+      <c r="C74" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74" t="s">
+        <v>855</v>
+      </c>
+      <c r="P74" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17">
+      <c r="C75" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17">
+      <c r="C76" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17">
+      <c r="B77">
+        <v>16</v>
+      </c>
+      <c r="C77" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="78" spans="2:17">
+      <c r="C78" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" t="s">
+        <v>859</v>
+      </c>
+      <c r="O78" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P78" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q78" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17">
+      <c r="C79" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79" t="s">
+        <v>860</v>
+      </c>
+      <c r="P79" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="2:17">
+      <c r="C80" t="s">
+        <v>9</v>
+      </c>
+      <c r="D80" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="81" spans="2:17">
+      <c r="C81" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="82" spans="2:17">
+      <c r="B82">
+        <v>17</v>
+      </c>
+      <c r="C82" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="83" spans="2:17">
+      <c r="C83" t="s">
+        <v>5</v>
+      </c>
+      <c r="D83" t="s">
+        <v>864</v>
+      </c>
+      <c r="O83" t="s">
+        <v>54</v>
+      </c>
+      <c r="P83" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q83" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="84" spans="2:17">
+      <c r="C84" t="s">
+        <v>7</v>
+      </c>
+      <c r="D84" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="85" spans="2:17">
+      <c r="C85" t="s">
+        <v>9</v>
+      </c>
+      <c r="D85" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="86" spans="2:17">
+      <c r="C86" t="s">
+        <v>11</v>
+      </c>
+      <c r="D86" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="87" spans="2:17">
+      <c r="B87">
+        <v>18</v>
+      </c>
+      <c r="C87" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="88" spans="2:17">
+      <c r="C88" t="s">
+        <v>5</v>
+      </c>
+      <c r="D88" t="s">
+        <v>869</v>
+      </c>
+      <c r="O88" t="s">
+        <v>54</v>
+      </c>
+      <c r="P88" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q88" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="89" spans="2:17">
+      <c r="C89" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="90" spans="2:17">
+      <c r="C90" t="s">
+        <v>9</v>
+      </c>
+      <c r="D90" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="91" spans="2:17">
+      <c r="C91" t="s">
+        <v>11</v>
+      </c>
+      <c r="D91" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="92" spans="2:17">
+      <c r="B92">
+        <v>19</v>
+      </c>
+      <c r="C92" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="93" spans="2:17">
+      <c r="C93" t="s">
+        <v>5</v>
+      </c>
+      <c r="D93" t="s">
+        <v>875</v>
+      </c>
+      <c r="O93" t="s">
+        <v>54</v>
+      </c>
+      <c r="P93" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q93" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="94" spans="2:17">
+      <c r="C94" t="s">
+        <v>7</v>
+      </c>
+      <c r="D94" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="95" spans="2:17">
+      <c r="C95" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="96" spans="2:17">
+      <c r="C96" t="s">
+        <v>11</v>
+      </c>
+      <c r="D96" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="97" spans="2:17">
+      <c r="B97">
+        <v>20</v>
+      </c>
+      <c r="C97" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="98" spans="2:17">
+      <c r="C98" t="s">
+        <v>5</v>
+      </c>
+      <c r="D98" t="s">
+        <v>879</v>
+      </c>
+      <c r="O98" t="s">
+        <v>54</v>
+      </c>
+      <c r="P98" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q98" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="99" spans="2:17">
+      <c r="C99" t="s">
+        <v>7</v>
+      </c>
+      <c r="D99" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="100" spans="2:17">
+      <c r="C100" t="s">
+        <v>9</v>
+      </c>
+      <c r="D100" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="101" spans="2:17">
+      <c r="C101" t="s">
+        <v>11</v>
+      </c>
+      <c r="D101" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="102" spans="2:17">
+      <c r="B102">
+        <v>21</v>
+      </c>
+      <c r="C102" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="103" spans="2:17">
+      <c r="C103" t="s">
+        <v>5</v>
+      </c>
+      <c r="D103" t="s">
+        <v>884</v>
+      </c>
+      <c r="O103" t="s">
+        <v>54</v>
+      </c>
+      <c r="P103" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q103" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="104" spans="2:17">
+      <c r="C104" t="s">
+        <v>7</v>
+      </c>
+      <c r="D104" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="105" spans="2:17">
+      <c r="C105" t="s">
+        <v>9</v>
+      </c>
+      <c r="D105" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="106" spans="2:17">
+      <c r="C106" t="s">
+        <v>11</v>
+      </c>
+      <c r="D106" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="107" spans="2:17">
+      <c r="B107">
+        <v>22</v>
+      </c>
+      <c r="C107" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="108" spans="2:17">
+      <c r="C108" t="s">
+        <v>5</v>
+      </c>
+      <c r="D108" t="s">
+        <v>889</v>
+      </c>
+      <c r="O108" t="s">
+        <v>54</v>
+      </c>
+      <c r="P108" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q108" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="109" spans="2:17">
+      <c r="C109" t="s">
+        <v>7</v>
+      </c>
+      <c r="D109" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="110" spans="2:17">
+      <c r="C110" t="s">
+        <v>9</v>
+      </c>
+      <c r="D110" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="111" spans="2:17">
+      <c r="C111" t="s">
+        <v>11</v>
+      </c>
+      <c r="D111" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="112" spans="2:17">
+      <c r="B112">
+        <v>23</v>
+      </c>
+      <c r="C112" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="113" spans="2:17">
+      <c r="C113" t="s">
+        <v>5</v>
+      </c>
+      <c r="D113" t="s">
+        <v>894</v>
+      </c>
+      <c r="O113" t="s">
+        <v>54</v>
+      </c>
+      <c r="P113" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q113" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="114" spans="2:17">
+      <c r="C114" t="s">
+        <v>7</v>
+      </c>
+      <c r="D114" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="115" spans="2:17">
+      <c r="C115" t="s">
+        <v>9</v>
+      </c>
+      <c r="D115" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="116" spans="2:17">
+      <c r="C116" t="s">
+        <v>11</v>
+      </c>
+      <c r="D116" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="117" spans="2:17">
+      <c r="B117">
+        <v>24</v>
+      </c>
+      <c r="C117" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="118" spans="2:17">
+      <c r="C118" t="s">
+        <v>5</v>
+      </c>
+      <c r="D118" t="s">
+        <v>899</v>
+      </c>
+      <c r="O118" t="s">
+        <v>54</v>
+      </c>
+      <c r="P118" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q118" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="119" spans="2:17">
+      <c r="C119" t="s">
+        <v>7</v>
+      </c>
+      <c r="D119" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="120" spans="2:17">
+      <c r="C120" t="s">
+        <v>9</v>
+      </c>
+      <c r="D120" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="121" spans="2:17">
+      <c r="C121" t="s">
+        <v>11</v>
+      </c>
+      <c r="D121" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="122" spans="2:17">
+      <c r="B122">
+        <v>25</v>
+      </c>
+      <c r="C122" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="123" spans="2:17">
+      <c r="C123" t="s">
+        <v>5</v>
+      </c>
+      <c r="D123" t="s">
+        <v>904</v>
+      </c>
+      <c r="O123" t="s">
+        <v>54</v>
+      </c>
+      <c r="P123" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q123" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="124" spans="2:17">
+      <c r="C124" t="s">
+        <v>7</v>
+      </c>
+      <c r="D124" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="125" spans="2:17">
+      <c r="C125" t="s">
+        <v>9</v>
+      </c>
+      <c r="D125" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="126" spans="2:17">
+      <c r="C126" t="s">
+        <v>11</v>
+      </c>
+      <c r="D126" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="127" spans="2:17">
+      <c r="B127">
+        <v>26</v>
+      </c>
+      <c r="C127" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="128" spans="2:17">
+      <c r="C128" t="s">
+        <v>5</v>
+      </c>
+      <c r="D128" t="s">
+        <v>909</v>
+      </c>
+      <c r="O128" t="s">
+        <v>54</v>
+      </c>
+      <c r="P128" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q128" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="129" spans="2:17">
+      <c r="C129" t="s">
+        <v>7</v>
+      </c>
+      <c r="D129" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="130" spans="2:17">
+      <c r="C130" t="s">
+        <v>9</v>
+      </c>
+      <c r="D130" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="131" spans="2:17">
+      <c r="C131" t="s">
+        <v>11</v>
+      </c>
+      <c r="D131" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="132" spans="2:17">
+      <c r="B132">
+        <v>27</v>
+      </c>
+      <c r="C132" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="133" spans="2:17">
+      <c r="C133" t="s">
+        <v>5</v>
+      </c>
+      <c r="D133" t="s">
+        <v>914</v>
+      </c>
+      <c r="O133" t="s">
+        <v>54</v>
+      </c>
+      <c r="P133" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q133" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="134" spans="2:17">
+      <c r="C134" t="s">
+        <v>7</v>
+      </c>
+      <c r="D134" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="135" spans="2:17">
+      <c r="C135" t="s">
+        <v>9</v>
+      </c>
+      <c r="D135" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="136" spans="2:17">
+      <c r="C136" t="s">
+        <v>11</v>
+      </c>
+      <c r="D136" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="137" spans="2:17">
+      <c r="B137">
+        <v>28</v>
+      </c>
+      <c r="C137" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="138" spans="2:17">
+      <c r="C138" t="s">
+        <v>5</v>
+      </c>
+      <c r="D138" t="s">
+        <v>919</v>
+      </c>
+      <c r="O138" t="s">
+        <v>54</v>
+      </c>
+      <c r="P138" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q138" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="139" spans="2:17">
+      <c r="C139" t="s">
+        <v>7</v>
+      </c>
+      <c r="D139" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="140" spans="2:17">
+      <c r="C140" t="s">
+        <v>9</v>
+      </c>
+      <c r="D140" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="141" spans="2:17">
+      <c r="C141" t="s">
+        <v>11</v>
+      </c>
+      <c r="D141" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="142" spans="2:17">
+      <c r="B142">
+        <v>29</v>
+      </c>
+      <c r="C142" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="143" spans="2:17">
+      <c r="C143" t="s">
+        <v>5</v>
+      </c>
+      <c r="D143" t="s">
+        <v>924</v>
+      </c>
+      <c r="O143" t="s">
+        <v>54</v>
+      </c>
+      <c r="P143" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q143" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="144" spans="2:17">
+      <c r="C144" t="s">
+        <v>7</v>
+      </c>
+      <c r="D144" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="145" spans="2:17">
+      <c r="C145" t="s">
+        <v>9</v>
+      </c>
+      <c r="D145" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="146" spans="2:17">
+      <c r="C146" t="s">
+        <v>11</v>
+      </c>
+      <c r="D146" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="147" spans="2:17">
+      <c r="B147">
+        <v>30</v>
+      </c>
+      <c r="C147" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="148" spans="2:17">
+      <c r="C148" t="s">
+        <v>5</v>
+      </c>
+      <c r="D148" t="s">
+        <v>929</v>
+      </c>
+      <c r="O148" t="s">
+        <v>54</v>
+      </c>
+      <c r="P148" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q148" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="149" spans="2:17">
+      <c r="C149" t="s">
+        <v>7</v>
+      </c>
+      <c r="D149" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="150" spans="2:17">
+      <c r="C150" t="s">
+        <v>9</v>
+      </c>
+      <c r="D150" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="151" spans="2:17">
+      <c r="C151" t="s">
+        <v>11</v>
+      </c>
+      <c r="D151" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="152" spans="2:17">
+      <c r="B152">
+        <v>31</v>
+      </c>
+      <c r="C152" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="153" spans="2:17">
+      <c r="C153" t="s">
+        <v>5</v>
+      </c>
+      <c r="D153" t="s">
+        <v>934</v>
+      </c>
+      <c r="O153" t="s">
+        <v>54</v>
+      </c>
+      <c r="P153" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q153" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="154" spans="2:17">
+      <c r="C154" t="s">
+        <v>7</v>
+      </c>
+      <c r="D154" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="155" spans="2:17">
+      <c r="C155" t="s">
+        <v>9</v>
+      </c>
+      <c r="D155" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="156" spans="2:17">
+      <c r="C156" t="s">
+        <v>11</v>
+      </c>
+      <c r="D156" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="157" spans="2:17">
+      <c r="B157">
+        <v>32</v>
+      </c>
+      <c r="C157" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="158" spans="2:17">
+      <c r="C158" t="s">
+        <v>5</v>
+      </c>
+      <c r="D158" t="s">
+        <v>939</v>
+      </c>
+      <c r="O158" t="s">
+        <v>54</v>
+      </c>
+      <c r="P158" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q158" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="159" spans="2:17">
+      <c r="C159" t="s">
+        <v>7</v>
+      </c>
+      <c r="D159" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="160" spans="2:17">
+      <c r="C160" t="s">
+        <v>9</v>
+      </c>
+      <c r="D160" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="161" spans="2:17">
+      <c r="C161" t="s">
+        <v>11</v>
+      </c>
+      <c r="D161" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="162" spans="2:17">
+      <c r="B162">
+        <v>33</v>
+      </c>
+      <c r="C162" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="163" spans="2:17">
+      <c r="C163" t="s">
+        <v>5</v>
+      </c>
+      <c r="D163" t="s">
+        <v>944</v>
+      </c>
+      <c r="O163" t="s">
+        <v>54</v>
+      </c>
+      <c r="P163" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q163" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="164" spans="2:17">
+      <c r="C164" t="s">
+        <v>7</v>
+      </c>
+      <c r="D164" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="165" spans="2:17">
+      <c r="C165" t="s">
+        <v>9</v>
+      </c>
+      <c r="D165" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="166" spans="2:17">
+      <c r="C166" t="s">
+        <v>11</v>
+      </c>
+      <c r="D166" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="167" spans="2:17">
+      <c r="B167">
+        <v>34</v>
+      </c>
+      <c r="C167" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="168" spans="2:17">
+      <c r="C168" t="s">
+        <v>5</v>
+      </c>
+      <c r="D168" t="s">
+        <v>949</v>
+      </c>
+      <c r="O168" t="s">
+        <v>54</v>
+      </c>
+      <c r="P168" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q168" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="169" spans="2:17">
+      <c r="C169" t="s">
+        <v>7</v>
+      </c>
+      <c r="D169" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="170" spans="2:17">
+      <c r="C170" t="s">
+        <v>9</v>
+      </c>
+      <c r="D170" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="171" spans="2:17">
+      <c r="C171" t="s">
+        <v>11</v>
+      </c>
+      <c r="D171" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="172" spans="2:17">
+      <c r="B172">
+        <v>35</v>
+      </c>
+      <c r="C172" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="173" spans="2:17">
+      <c r="C173" t="s">
+        <v>5</v>
+      </c>
+      <c r="D173" t="s">
+        <v>954</v>
+      </c>
+      <c r="O173" t="s">
+        <v>54</v>
+      </c>
+      <c r="P173" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q173" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="174" spans="2:17">
+      <c r="C174" t="s">
+        <v>7</v>
+      </c>
+      <c r="D174" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="175" spans="2:17">
+      <c r="C175" t="s">
+        <v>9</v>
+      </c>
+      <c r="D175" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="176" spans="2:17">
+      <c r="C176" t="s">
+        <v>11</v>
+      </c>
+      <c r="D176" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="177" spans="2:17">
+      <c r="B177">
+        <v>36</v>
+      </c>
+      <c r="C177" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="178" spans="2:17">
+      <c r="C178" t="s">
+        <v>5</v>
+      </c>
+      <c r="D178" t="s">
+        <v>959</v>
+      </c>
+      <c r="O178" t="s">
+        <v>54</v>
+      </c>
+      <c r="P178" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q178" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="179" spans="2:17">
+      <c r="C179" t="s">
+        <v>7</v>
+      </c>
+      <c r="D179" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="180" spans="2:17">
+      <c r="C180" t="s">
+        <v>9</v>
+      </c>
+      <c r="D180" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="181" spans="2:17">
+      <c r="C181" t="s">
+        <v>11</v>
+      </c>
+      <c r="D181" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="182" spans="2:17">
+      <c r="B182">
+        <v>37</v>
+      </c>
+      <c r="C182" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="183" spans="2:17">
+      <c r="C183" t="s">
+        <v>5</v>
+      </c>
+      <c r="D183" t="s">
+        <v>964</v>
+      </c>
+      <c r="O183" t="s">
+        <v>54</v>
+      </c>
+      <c r="P183" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q183" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="184" spans="2:17">
+      <c r="C184" t="s">
+        <v>7</v>
+      </c>
+      <c r="D184" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="185" spans="2:17">
+      <c r="C185" t="s">
+        <v>9</v>
+      </c>
+      <c r="D185" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="186" spans="2:17">
+      <c r="C186" t="s">
+        <v>11</v>
+      </c>
+      <c r="D186" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="187" spans="2:17">
+      <c r="B187">
+        <v>38</v>
+      </c>
+      <c r="C187" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="188" spans="2:17">
+      <c r="C188" t="s">
+        <v>5</v>
+      </c>
+      <c r="D188" t="s">
+        <v>969</v>
+      </c>
+      <c r="O188" t="s">
+        <v>54</v>
+      </c>
+      <c r="P188" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q188" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="189" spans="2:17">
+      <c r="C189" t="s">
+        <v>7</v>
+      </c>
+      <c r="D189" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="190" spans="2:17">
+      <c r="C190" t="s">
+        <v>9</v>
+      </c>
+      <c r="D190" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="191" spans="2:17">
+      <c r="C191" t="s">
+        <v>12</v>
+      </c>
+      <c r="D191" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="192" spans="2:17">
+      <c r="B192">
+        <v>39</v>
+      </c>
+      <c r="C192" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="193" spans="2:17">
+      <c r="C193" t="s">
+        <v>5</v>
+      </c>
+      <c r="D193" t="s">
+        <v>974</v>
+      </c>
+      <c r="O193" t="s">
+        <v>54</v>
+      </c>
+      <c r="P193" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q193" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="194" spans="2:17">
+      <c r="C194" t="s">
+        <v>7</v>
+      </c>
+      <c r="D194" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="195" spans="2:17">
+      <c r="C195" t="s">
+        <v>9</v>
+      </c>
+      <c r="D195" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="196" spans="2:17">
+      <c r="C196" t="s">
+        <v>12</v>
+      </c>
+      <c r="D196" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="197" spans="2:17">
+      <c r="B197">
+        <v>40</v>
+      </c>
+      <c r="C197" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="198" spans="2:17">
+      <c r="C198" t="s">
+        <v>5</v>
+      </c>
+      <c r="D198" t="s">
+        <v>979</v>
+      </c>
+      <c r="O198" t="s">
+        <v>54</v>
+      </c>
+      <c r="P198" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q198" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="199" spans="2:17">
+      <c r="C199" t="s">
+        <v>7</v>
+      </c>
+      <c r="D199" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="200" spans="2:17">
+      <c r="C200" t="s">
+        <v>9</v>
+      </c>
+      <c r="D200" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="201" spans="2:17">
+      <c r="C201" t="s">
+        <v>12</v>
+      </c>
+      <c r="D201" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="202" spans="2:17">
+      <c r="B202">
+        <v>41</v>
+      </c>
+      <c r="C202" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="203" spans="2:17">
+      <c r="C203" t="s">
+        <v>5</v>
+      </c>
+      <c r="D203" t="s">
+        <v>984</v>
+      </c>
+      <c r="O203" t="s">
+        <v>54</v>
+      </c>
+      <c r="P203" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q203" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="204" spans="2:17">
+      <c r="C204" t="s">
+        <v>7</v>
+      </c>
+      <c r="D204" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="205" spans="2:17">
+      <c r="C205" t="s">
+        <v>9</v>
+      </c>
+      <c r="D205" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="206" spans="2:17">
+      <c r="C206" t="s">
+        <v>12</v>
+      </c>
+      <c r="D206" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="207" spans="2:17">
+      <c r="B207">
+        <v>42</v>
+      </c>
+      <c r="C207" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="208" spans="2:17">
+      <c r="C208" t="s">
+        <v>5</v>
+      </c>
+      <c r="D208" t="s">
+        <v>989</v>
+      </c>
+      <c r="O208" t="s">
+        <v>54</v>
+      </c>
+      <c r="P208" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q208" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="209" spans="2:17">
+      <c r="C209" t="s">
+        <v>7</v>
+      </c>
+      <c r="D209" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="210" spans="2:17">
+      <c r="C210" t="s">
+        <v>9</v>
+      </c>
+      <c r="D210" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="211" spans="2:17">
+      <c r="C211" t="s">
+        <v>12</v>
+      </c>
+      <c r="D211" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="212" spans="2:17">
+      <c r="B212">
+        <v>43</v>
+      </c>
+      <c r="C212" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="213" spans="2:17">
+      <c r="C213" t="s">
+        <v>5</v>
+      </c>
+      <c r="D213" t="s">
+        <v>994</v>
+      </c>
+      <c r="O213" t="s">
+        <v>54</v>
+      </c>
+      <c r="P213" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q213" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="214" spans="2:17">
+      <c r="C214" t="s">
+        <v>7</v>
+      </c>
+      <c r="D214" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="215" spans="2:17">
+      <c r="C215" t="s">
+        <v>9</v>
+      </c>
+      <c r="D215" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="216" spans="2:17">
+      <c r="C216" t="s">
+        <v>12</v>
+      </c>
+      <c r="D216" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="217" spans="2:17">
+      <c r="B217">
+        <v>44</v>
+      </c>
+      <c r="C217" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="218" spans="2:17">
+      <c r="C218" t="s">
+        <v>5</v>
+      </c>
+      <c r="D218" t="s">
+        <v>999</v>
+      </c>
+      <c r="O218" t="s">
+        <v>54</v>
+      </c>
+      <c r="P218" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q218" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="219" spans="2:17">
+      <c r="C219" t="s">
+        <v>7</v>
+      </c>
+      <c r="D219" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="220" spans="2:17">
+      <c r="C220" t="s">
+        <v>9</v>
+      </c>
+      <c r="D220" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="221" spans="2:17">
+      <c r="C221" t="s">
+        <v>12</v>
+      </c>
+      <c r="D221" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="222" spans="2:17">
+      <c r="B222">
+        <v>45</v>
+      </c>
+      <c r="C222" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="223" spans="2:17">
+      <c r="C223" t="s">
+        <v>5</v>
+      </c>
+      <c r="D223" t="s">
+        <v>1004</v>
+      </c>
+      <c r="O223" t="s">
+        <v>54</v>
+      </c>
+      <c r="P223" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q223" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="224" spans="2:17">
+      <c r="C224" t="s">
+        <v>7</v>
+      </c>
+      <c r="D224" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="225" spans="2:17">
+      <c r="C225" t="s">
+        <v>9</v>
+      </c>
+      <c r="D225" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="226" spans="2:17">
+      <c r="C226" t="s">
+        <v>12</v>
+      </c>
+      <c r="D226" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="227" spans="2:17">
+      <c r="B227">
+        <v>46</v>
+      </c>
+      <c r="C227" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="228" spans="2:17">
+      <c r="C228" t="s">
+        <v>5</v>
+      </c>
+      <c r="D228" t="s">
+        <v>1009</v>
+      </c>
+      <c r="O228" t="s">
+        <v>54</v>
+      </c>
+      <c r="P228" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q228" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="229" spans="2:17">
+      <c r="C229" t="s">
+        <v>7</v>
+      </c>
+      <c r="D229" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="230" spans="2:17">
+      <c r="C230" t="s">
+        <v>9</v>
+      </c>
+      <c r="D230" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="231" spans="2:17">
+      <c r="C231" t="s">
+        <v>12</v>
+      </c>
+      <c r="D231" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="232" spans="2:17">
+      <c r="B232">
+        <v>47</v>
+      </c>
+      <c r="C232" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="233" spans="2:17">
+      <c r="C233" t="s">
+        <v>5</v>
+      </c>
+      <c r="D233" t="s">
+        <v>1014</v>
+      </c>
+      <c r="O233" t="s">
+        <v>54</v>
+      </c>
+      <c r="P233" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q233" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="234" spans="2:17">
+      <c r="C234" t="s">
+        <v>7</v>
+      </c>
+      <c r="D234" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="235" spans="2:17">
+      <c r="C235" t="s">
+        <v>9</v>
+      </c>
+      <c r="D235" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="236" spans="2:17">
+      <c r="C236" t="s">
+        <v>12</v>
+      </c>
+      <c r="D236" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="237" spans="2:17">
+      <c r="B237">
+        <v>48</v>
+      </c>
+      <c r="C237" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="238" spans="2:17">
+      <c r="C238" t="s">
+        <v>5</v>
+      </c>
+      <c r="D238" t="s">
+        <v>1019</v>
+      </c>
+      <c r="O238" t="s">
+        <v>54</v>
+      </c>
+      <c r="P238" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q238" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="239" spans="2:17">
+      <c r="C239" t="s">
+        <v>7</v>
+      </c>
+      <c r="D239" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="240" spans="2:17">
+      <c r="C240" t="s">
+        <v>9</v>
+      </c>
+      <c r="D240" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="241" spans="2:17">
+      <c r="C241" t="s">
+        <v>12</v>
+      </c>
+      <c r="D241" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="242" spans="2:17">
+      <c r="B242">
+        <v>49</v>
+      </c>
+      <c r="C242" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="243" spans="2:17">
+      <c r="C243" t="s">
+        <v>5</v>
+      </c>
+      <c r="D243" t="s">
+        <v>1024</v>
+      </c>
+      <c r="O243" t="s">
+        <v>54</v>
+      </c>
+      <c r="P243" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q243" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="244" spans="2:17">
+      <c r="C244" t="s">
+        <v>7</v>
+      </c>
+      <c r="D244" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="245" spans="2:17">
+      <c r="C245" t="s">
+        <v>9</v>
+      </c>
+      <c r="D245" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="246" spans="2:17">
+      <c r="C246" t="s">
+        <v>12</v>
+      </c>
+      <c r="D246" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="247" spans="2:17">
+      <c r="B247">
+        <v>50</v>
+      </c>
+      <c r="C247" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="248" spans="2:17">
+      <c r="C248" t="s">
+        <v>5</v>
+      </c>
+      <c r="D248" t="s">
+        <v>1029</v>
+      </c>
+      <c r="O248" t="s">
+        <v>54</v>
+      </c>
+      <c r="P248" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q248" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="249" spans="2:17">
+      <c r="C249" t="s">
+        <v>7</v>
+      </c>
+      <c r="D249" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="250" spans="2:17">
+      <c r="C250" t="s">
+        <v>9</v>
+      </c>
+      <c r="D250" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="251" spans="2:17">
+      <c r="C251" t="s">
+        <v>12</v>
+      </c>
+      <c r="D251" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="252" spans="2:17">
+      <c r="B252">
+        <v>51</v>
+      </c>
+      <c r="C252" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="253" spans="2:17">
+      <c r="C253" t="s">
+        <v>5</v>
+      </c>
+      <c r="D253" t="s">
+        <v>1034</v>
+      </c>
+      <c r="O253" t="s">
+        <v>54</v>
+      </c>
+      <c r="P253" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q253" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="254" spans="2:17">
+      <c r="C254" t="s">
+        <v>7</v>
+      </c>
+      <c r="D254" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="255" spans="2:17">
+      <c r="C255" t="s">
+        <v>9</v>
+      </c>
+      <c r="D255" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="256" spans="2:17">
+      <c r="C256" t="s">
+        <v>12</v>
+      </c>
+      <c r="D256" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="257" spans="2:17">
+      <c r="B257">
+        <v>52</v>
+      </c>
+      <c r="C257" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="258" spans="2:17">
+      <c r="C258" t="s">
+        <v>5</v>
+      </c>
+      <c r="D258" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O258" t="s">
+        <v>54</v>
+      </c>
+      <c r="P258" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q258" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="259" spans="2:17">
+      <c r="C259" t="s">
+        <v>7</v>
+      </c>
+      <c r="D259" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="260" spans="2:17">
+      <c r="C260" t="s">
+        <v>9</v>
+      </c>
+      <c r="D260" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="261" spans="2:17">
+      <c r="C261" t="s">
+        <v>12</v>
+      </c>
+      <c r="D261" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="262" spans="2:17">
+      <c r="B262">
+        <v>53</v>
+      </c>
+      <c r="C262" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="263" spans="2:17">
+      <c r="C263" t="s">
+        <v>5</v>
+      </c>
+      <c r="D263" t="s">
+        <v>1044</v>
+      </c>
+      <c r="O263" t="s">
+        <v>54</v>
+      </c>
+      <c r="P263" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q263" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="264" spans="2:17">
+      <c r="C264" t="s">
+        <v>7</v>
+      </c>
+      <c r="D264" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="265" spans="2:17">
+      <c r="C265" t="s">
+        <v>9</v>
+      </c>
+      <c r="D265" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="266" spans="2:17">
+      <c r="C266" t="s">
+        <v>12</v>
+      </c>
+      <c r="D266" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="267" spans="2:17">
+      <c r="B267">
+        <v>54</v>
+      </c>
+      <c r="C267" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="268" spans="2:17">
+      <c r="C268" t="s">
+        <v>5</v>
+      </c>
+      <c r="D268" t="s">
+        <v>1049</v>
+      </c>
+      <c r="O268" t="s">
+        <v>54</v>
+      </c>
+      <c r="P268" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q268" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="269" spans="2:17">
+      <c r="C269" t="s">
+        <v>7</v>
+      </c>
+      <c r="D269" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="270" spans="2:17">
+      <c r="C270" t="s">
+        <v>9</v>
+      </c>
+      <c r="D270" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="271" spans="2:17">
+      <c r="C271" t="s">
+        <v>12</v>
+      </c>
+      <c r="D271" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="272" spans="2:17">
+      <c r="B272">
+        <v>55</v>
+      </c>
+      <c r="C272" t="s">
+        <v>1053</v>
+      </c>
+      <c r="O272" t="s">
+        <v>54</v>
+      </c>
+      <c r="P272" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q272" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="273" spans="2:17">
+      <c r="C273" t="s">
+        <v>5</v>
+      </c>
+      <c r="D273" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="274" spans="2:17">
+      <c r="C274" t="s">
+        <v>7</v>
+      </c>
+      <c r="D274" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="275" spans="2:17">
+      <c r="C275" t="s">
+        <v>9</v>
+      </c>
+      <c r="D275" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="276" spans="2:17">
+      <c r="C276" t="s">
+        <v>12</v>
+      </c>
+      <c r="D276" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="277" spans="2:17">
+      <c r="B277">
+        <v>56</v>
+      </c>
+      <c r="C277" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="278" spans="2:17">
+      <c r="C278" t="s">
+        <v>5</v>
+      </c>
+      <c r="D278" t="s">
+        <v>1059</v>
+      </c>
+      <c r="O278" t="s">
+        <v>54</v>
+      </c>
+      <c r="P278" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q278" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="279" spans="2:17">
+      <c r="C279" t="s">
+        <v>7</v>
+      </c>
+      <c r="D279" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="280" spans="2:17">
+      <c r="C280" t="s">
+        <v>9</v>
+      </c>
+      <c r="D280" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="281" spans="2:17">
+      <c r="C281" t="s">
+        <v>12</v>
+      </c>
+      <c r="D281" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="282" spans="2:17">
+      <c r="B282">
+        <v>57</v>
+      </c>
+      <c r="C282" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="283" spans="2:17">
+      <c r="C283" t="s">
+        <v>5</v>
+      </c>
+      <c r="D283" t="s">
+        <v>1064</v>
+      </c>
+      <c r="O283" t="s">
+        <v>54</v>
+      </c>
+      <c r="P283" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q283" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="284" spans="2:17">
+      <c r="C284" t="s">
+        <v>7</v>
+      </c>
+      <c r="D284" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="285" spans="2:17">
+      <c r="C285" t="s">
+        <v>9</v>
+      </c>
+      <c r="D285" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="286" spans="2:17">
+      <c r="C286" t="s">
+        <v>12</v>
+      </c>
+      <c r="D286" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="287" spans="2:17">
+      <c r="B287">
+        <v>58</v>
+      </c>
+      <c r="C287" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="288" spans="2:17">
+      <c r="C288" t="s">
+        <v>5</v>
+      </c>
+      <c r="D288" t="s">
+        <v>1069</v>
+      </c>
+      <c r="O288" t="s">
+        <v>54</v>
+      </c>
+      <c r="P288" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q288" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="289" spans="2:17">
+      <c r="C289" t="s">
+        <v>7</v>
+      </c>
+      <c r="D289" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="290" spans="2:17">
+      <c r="C290" t="s">
+        <v>9</v>
+      </c>
+      <c r="D290" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="291" spans="2:17">
+      <c r="C291" t="s">
+        <v>12</v>
+      </c>
+      <c r="D291" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="292" spans="2:17">
+      <c r="B292">
+        <v>59</v>
+      </c>
+      <c r="C292" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="293" spans="2:17">
+      <c r="C293" t="s">
+        <v>5</v>
+      </c>
+      <c r="D293" t="s">
+        <v>1074</v>
+      </c>
+      <c r="O293" t="s">
+        <v>54</v>
+      </c>
+      <c r="P293" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q293" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="294" spans="2:17">
+      <c r="C294" t="s">
+        <v>7</v>
+      </c>
+      <c r="D294" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="295" spans="2:17">
+      <c r="C295" t="s">
+        <v>9</v>
+      </c>
+      <c r="D295" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="296" spans="2:17">
+      <c r="C296" t="s">
+        <v>12</v>
+      </c>
+      <c r="D296" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="297" spans="2:17">
+      <c r="B297">
+        <v>60</v>
+      </c>
+      <c r="C297" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="298" spans="2:17">
+      <c r="C298" t="s">
+        <v>5</v>
+      </c>
+      <c r="D298" t="s">
+        <v>1079</v>
+      </c>
+      <c r="O298" t="s">
+        <v>54</v>
+      </c>
+      <c r="P298" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q298" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="299" spans="2:17">
+      <c r="C299" t="s">
+        <v>7</v>
+      </c>
+      <c r="D299" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="300" spans="2:17">
+      <c r="C300" t="s">
+        <v>9</v>
+      </c>
+      <c r="D300" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="301" spans="2:17">
+      <c r="C301" t="s">
+        <v>12</v>
+      </c>
+      <c r="D301" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="302" spans="2:17">
+      <c r="B302">
+        <v>61</v>
+      </c>
+      <c r="C302" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="303" spans="2:17">
+      <c r="C303" t="s">
+        <v>5</v>
+      </c>
+      <c r="D303" t="s">
+        <v>1084</v>
+      </c>
+      <c r="O303" t="s">
+        <v>54</v>
+      </c>
+      <c r="P303" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q303" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="304" spans="2:17">
+      <c r="C304" t="s">
+        <v>7</v>
+      </c>
+      <c r="D304" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="305" spans="2:17">
+      <c r="C305" t="s">
+        <v>9</v>
+      </c>
+      <c r="D305" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="306" spans="2:17">
+      <c r="C306" t="s">
+        <v>12</v>
+      </c>
+      <c r="D306" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="307" spans="2:17">
+      <c r="B307">
+        <v>62</v>
+      </c>
+      <c r="C307" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="308" spans="2:17">
+      <c r="C308" t="s">
+        <v>5</v>
+      </c>
+      <c r="D308" t="s">
+        <v>1089</v>
+      </c>
+      <c r="O308" t="s">
+        <v>54</v>
+      </c>
+      <c r="P308" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q308" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="309" spans="2:17">
+      <c r="C309" t="s">
+        <v>7</v>
+      </c>
+      <c r="D309" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="310" spans="2:17">
+      <c r="C310" t="s">
+        <v>9</v>
+      </c>
+      <c r="D310" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="311" spans="2:17">
+      <c r="C311" t="s">
+        <v>12</v>
+      </c>
+      <c r="D311" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="312" spans="2:17">
+      <c r="B312">
+        <v>63</v>
+      </c>
+      <c r="C312" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="313" spans="2:17">
+      <c r="C313" t="s">
+        <v>5</v>
+      </c>
+      <c r="D313" t="s">
+        <v>1094</v>
+      </c>
+      <c r="O313" t="s">
+        <v>54</v>
+      </c>
+      <c r="P313" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q313" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="314" spans="2:17">
+      <c r="C314" t="s">
+        <v>7</v>
+      </c>
+      <c r="D314" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="315" spans="2:17">
+      <c r="C315" t="s">
+        <v>9</v>
+      </c>
+      <c r="D315" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="316" spans="2:17">
+      <c r="C316" t="s">
+        <v>12</v>
+      </c>
+      <c r="D316" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="317" spans="2:17">
+      <c r="B317">
+        <v>64</v>
+      </c>
+      <c r="C317" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="318" spans="2:17">
+      <c r="C318" t="s">
+        <v>5</v>
+      </c>
+      <c r="D318" t="s">
+        <v>1099</v>
+      </c>
+      <c r="O318" t="s">
+        <v>54</v>
+      </c>
+      <c r="P318" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q318" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="319" spans="2:17">
+      <c r="C319" t="s">
+        <v>7</v>
+      </c>
+      <c r="D319" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="320" spans="2:17">
+      <c r="C320" t="s">
+        <v>9</v>
+      </c>
+      <c r="D320" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="321" spans="2:17">
+      <c r="C321" t="s">
+        <v>12</v>
+      </c>
+      <c r="D321" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="322" spans="2:17">
+      <c r="B322">
+        <v>65</v>
+      </c>
+      <c r="C322" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="323" spans="2:17">
+      <c r="C323" t="s">
+        <v>5</v>
+      </c>
+      <c r="D323" t="s">
+        <v>1104</v>
+      </c>
+      <c r="O323" t="s">
+        <v>54</v>
+      </c>
+      <c r="P323" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q323" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="324" spans="2:17">
+      <c r="C324" t="s">
+        <v>7</v>
+      </c>
+      <c r="D324" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="325" spans="2:17">
+      <c r="C325" t="s">
+        <v>9</v>
+      </c>
+      <c r="D325" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="326" spans="2:17">
+      <c r="C326" t="s">
+        <v>12</v>
+      </c>
+      <c r="D326" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="327" spans="2:17">
+      <c r="B327">
+        <v>66</v>
+      </c>
+      <c r="C327" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="328" spans="2:17">
+      <c r="C328" t="s">
+        <v>5</v>
+      </c>
+      <c r="D328" t="s">
+        <v>1109</v>
+      </c>
+      <c r="O328" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P328" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q328" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="329" spans="2:17">
+      <c r="C329" t="s">
+        <v>7</v>
+      </c>
+      <c r="D329" t="s">
+        <v>1110</v>
+      </c>
+      <c r="P329" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="330" spans="2:17">
+      <c r="C330" t="s">
+        <v>9</v>
+      </c>
+      <c r="D330" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="331" spans="2:17">
+      <c r="C331" t="s">
+        <v>12</v>
+      </c>
+      <c r="D331" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="332" spans="2:17">
+      <c r="B332">
+        <v>67</v>
+      </c>
+      <c r="C332" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="333" spans="2:17">
+      <c r="C333" t="s">
+        <v>5</v>
+      </c>
+      <c r="D333" t="s">
+        <v>1113</v>
+      </c>
+      <c r="O333" t="s">
+        <v>54</v>
+      </c>
+      <c r="P333" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q333" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="334" spans="2:17">
+      <c r="C334" t="s">
+        <v>7</v>
+      </c>
+      <c r="D334" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="335" spans="2:17">
+      <c r="C335" t="s">
+        <v>9</v>
+      </c>
+      <c r="D335" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="336" spans="2:17">
+      <c r="C336" t="s">
+        <v>12</v>
+      </c>
+      <c r="D336" t="s">
+        <v>1116</v>
       </c>
     </row>
   </sheetData>
@@ -19936,378 +24406,570 @@
       <c r="B5">
         <v>4</v>
       </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="6" spans="2:3">
       <c r="B6">
         <v>5</v>
       </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="7" spans="2:3">
       <c r="B7">
         <v>6</v>
       </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="8" spans="2:3">
       <c r="B8">
         <v>7</v>
       </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="9" spans="2:3">
       <c r="B9">
         <v>8</v>
       </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="10" spans="2:3">
       <c r="B10">
         <v>9</v>
       </c>
+      <c r="C10" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="11" spans="2:3">
       <c r="B11">
         <v>10</v>
       </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="12" spans="2:3">
       <c r="B12">
         <v>11</v>
       </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="13" spans="2:3">
       <c r="B13">
         <v>12</v>
       </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="14" spans="2:3">
       <c r="B14">
         <v>13</v>
       </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="15" spans="2:3">
       <c r="B15">
         <v>14</v>
       </c>
+      <c r="C15" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="16" spans="2:3">
       <c r="B16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="2:2">
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
       <c r="B17">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="2:2">
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
       <c r="B18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="2:2">
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
       <c r="B19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="2:2">
+      <c r="C19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
       <c r="B20">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="2:2">
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
       <c r="B21">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="2:2">
+      <c r="C21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
       <c r="B22">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="2:2">
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
       <c r="B23">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="2:2">
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
       <c r="B24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="2:2">
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3">
       <c r="B25">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="2:2">
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
       <c r="B26">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="2:2">
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
       <c r="B27">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="2:2">
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3">
       <c r="B28">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="2:2">
+      <c r="C28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3">
       <c r="B29">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="2:2">
+      <c r="C29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3">
       <c r="B30">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="2:2">
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3">
       <c r="B31">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="2:2">
+      <c r="C31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3">
       <c r="B32">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="2:2">
+      <c r="C32" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3">
       <c r="B33">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="2:2">
+      <c r="C33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3">
       <c r="B34">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="2:2">
+      <c r="C34" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3">
       <c r="B35">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="2:2">
+      <c r="C35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3">
       <c r="B36">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="2:2">
+      <c r="C36" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3">
       <c r="B37">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="2:2">
+      <c r="C37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3">
       <c r="B38">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="2:2">
+      <c r="C38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3">
       <c r="B39">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="2:2">
+      <c r="C39" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3">
       <c r="B40">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="2:2">
+      <c r="C40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3">
       <c r="B41">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="2:2">
+      <c r="C41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3">
       <c r="B42">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="2:2">
+      <c r="C42" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3">
       <c r="B43">
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="2:2">
+      <c r="C43" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3">
       <c r="B44">
         <v>43</v>
       </c>
-    </row>
-    <row r="45" spans="2:2">
+      <c r="C44" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3">
       <c r="B45">
         <v>44</v>
       </c>
-    </row>
-    <row r="46" spans="2:2">
+      <c r="C45" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3">
       <c r="B46">
         <v>45</v>
       </c>
-    </row>
-    <row r="47" spans="2:2">
+      <c r="C46" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3">
       <c r="B47">
         <v>46</v>
       </c>
-    </row>
-    <row r="48" spans="2:2">
+      <c r="C47" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3">
       <c r="B48">
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="2:2">
+      <c r="C48" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3">
       <c r="B49">
         <v>48</v>
       </c>
-    </row>
-    <row r="50" spans="2:2">
+      <c r="C49" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3">
       <c r="B50">
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="2:2">
+      <c r="C50" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3">
       <c r="B51">
         <v>50</v>
       </c>
-    </row>
-    <row r="52" spans="2:2">
+      <c r="C51" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3">
       <c r="B52">
         <v>51</v>
       </c>
-    </row>
-    <row r="53" spans="2:2">
+      <c r="C52" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3">
       <c r="B53">
         <v>52</v>
       </c>
-    </row>
-    <row r="54" spans="2:2">
+      <c r="C53" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3">
       <c r="B54">
         <v>53</v>
       </c>
-    </row>
-    <row r="55" spans="2:2">
+      <c r="C54" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3">
       <c r="B55">
         <v>54</v>
       </c>
-    </row>
-    <row r="56" spans="2:2">
+      <c r="C55" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3">
       <c r="B56">
         <v>55</v>
       </c>
-    </row>
-    <row r="57" spans="2:2">
+      <c r="C56" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3">
       <c r="B57">
         <v>56</v>
       </c>
-    </row>
-    <row r="58" spans="2:2">
+      <c r="C57" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3">
       <c r="B58">
         <v>57</v>
       </c>
-    </row>
-    <row r="59" spans="2:2">
+      <c r="C58" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3">
       <c r="B59">
         <v>58</v>
       </c>
-    </row>
-    <row r="60" spans="2:2">
+      <c r="C59" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3">
       <c r="B60">
         <v>59</v>
       </c>
-    </row>
-    <row r="61" spans="2:2">
+      <c r="C60" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3">
       <c r="B61">
         <v>60</v>
       </c>
-    </row>
-    <row r="62" spans="2:2">
+      <c r="C61" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3">
       <c r="B62">
         <v>61</v>
       </c>
-    </row>
-    <row r="63" spans="2:2">
+      <c r="C62" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3">
       <c r="B63">
         <v>62</v>
       </c>
-    </row>
-    <row r="64" spans="2:2">
+      <c r="C63" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3">
       <c r="B64">
         <v>63</v>
       </c>
-    </row>
-    <row r="65" spans="2:2">
+      <c r="C64" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3">
       <c r="B65">
         <v>64</v>
       </c>
-    </row>
-    <row r="66" spans="2:2">
+      <c r="C65" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3">
       <c r="B66">
         <v>65</v>
       </c>
-    </row>
-    <row r="67" spans="2:2">
+      <c r="C66" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3">
       <c r="B67">
         <v>66</v>
       </c>
-    </row>
-    <row r="68" spans="2:2">
+      <c r="C67" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3">
       <c r="B68">
         <v>67</v>
       </c>
-    </row>
-    <row r="69" spans="2:2">
+      <c r="C68" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3">
       <c r="B69">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="2:2">
+    <row r="70" spans="2:3">
       <c r="B70">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="2:2">
+    <row r="71" spans="2:3">
       <c r="B71">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="2:2">
+    <row r="72" spans="2:3">
       <c r="B72">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="2:2">
+    <row r="73" spans="2:3">
       <c r="B73">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="2:2">
+    <row r="74" spans="2:3">
       <c r="B74">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="2:2">
+    <row r="75" spans="2:3">
       <c r="B75">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="2:2">
+    <row r="76" spans="2:3">
       <c r="B76">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="2:2">
+    <row r="77" spans="2:3">
       <c r="B77">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="2:2">
+    <row r="78" spans="2:3">
       <c r="B78">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="2:2">
+    <row r="79" spans="2:3">
       <c r="B79">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="2:2">
+    <row r="80" spans="2:3">
       <c r="B80">
         <v>79</v>
       </c>
@@ -20971,4 +25633,14 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{715CA485-1F5B-4BB5-A334-8CD98D55194C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/UX検定_基礎.xlsx
+++ b/UX検定_基礎.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\勉強\資格(取得)\UX\基礎\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ドキュメント\その他\eラーニング\UX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A69786-6A51-47DE-9162-B5C8ACFB1540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0301F621-6434-445F-999A-068A00B5B331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="模擬" sheetId="1" r:id="rId1"/>
@@ -42,15 +42,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2543" uniqueCount="1117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2615" uniqueCount="1147">
   <si>
     <t>UXインテリジェンスが生み出す価値として重要視するものを、次の中から選びなさい。</t>
     <phoneticPr fontId="1"/>
@@ -12623,6 +12620,570 @@
   </si>
   <si>
     <t>成果物を一度だけリリースして評価する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXを考える上で重要な視点として最も適切なのはどれか、正しいものを次の中から選びなさい。</t>
+    <rPh sb="3" eb="4">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シテン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>モット</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業の収益性を最大化する視点</t>
+    <rPh sb="0" eb="2">
+      <t>キギョウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>シュウエキセイ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>サイダイカ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの感情や行動に焦点を当てる視点</t>
+    <rPh sb="5" eb="7">
+      <t>カンジョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ショウテン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開発コストを最小限に抑える視点</t>
+    <rPh sb="0" eb="2">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>サイショウゲン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オサ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最新技術を積極的に採用する視点</t>
+    <rPh sb="0" eb="2">
+      <t>サイシン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ギジュツ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>セッキョクテキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>サイヨウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXの捉え方として最も適切なのはどれか、次の中から選びなさい。</t>
+    <rPh sb="3" eb="4">
+      <t>トラ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>モット</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>製品発売後にユーザーがどのように評価したかを測定する活動</t>
+    <rPh sb="0" eb="2">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハツバイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ソクテイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>カツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UI改善のみを通じてユーザー満足度を高めるプロセス</t>
+    <rPh sb="2" eb="4">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ツウ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>マンゾクド</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>タカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用前・利用中・利用後を含むユーザーの体験価値を設計・評価する概念</t>
+    <rPh sb="0" eb="2">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>リヨウチュウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カチ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ガイネン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー調査を行い、ニーズを発見するための技法</t>
+    <rPh sb="4" eb="6">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハッケン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ギホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ISO 9241-210において、UXに含まれないとされる要素として最も適切なのはどれか、次の中から選びなさい。</t>
+    <rPh sb="20" eb="21">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>モット</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サービス利用中のユーザーの感情</t>
+    <rPh sb="4" eb="7">
+      <t>リヨウチュウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カンジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用前に抱く期待</t>
+    <rPh sb="0" eb="2">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>イダ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用後の満足度</t>
+    <rPh sb="0" eb="2">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>マンゾクド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが利用する前のブランドイメージそのもの</t>
+    <rPh sb="5" eb="7">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ニールセン・ノーマンが示すUXとユーザビリティの関係として最も適切なのはどれか、次の中から選びなさい。</t>
+    <rPh sb="11" eb="12">
+      <t>シメ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>モット</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXはユーザビリティの一部に含まれる</t>
+    <rPh sb="11" eb="13">
+      <t>イチブ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザビリティはUXの一部であり、UX全体を構成する要素の1つ</t>
+    <rPh sb="11" eb="13">
+      <t>イチブ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ヨウソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXとユーザビリティは同義であり、明確な区別はない</t>
+    <rPh sb="11" eb="13">
+      <t>ドウギ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>メイカク</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>クベツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXは機能品質、ユーザビリティは心理的体験を示す</t>
+    <rPh sb="3" eb="5">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒンシツ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>シンリテキ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>シメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ISO 9241-210において、UXの要素として最も正しい組み合わせはどれか、次の中から選びなさい。</t>
+    <rPh sb="20" eb="22">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>モット</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーの満足度、企業の利益、技術革新</t>
+    <rPh sb="5" eb="8">
+      <t>マンゾクド</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キギョウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>リエキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ギジュツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カクシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>使いやすさ、見やすさ、操作速度</t>
+    <rPh sb="0" eb="1">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ソクド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>期待、感情、利用後の評価</t>
+    <rPh sb="0" eb="2">
+      <t>キタイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カンジョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機能、コスト、ブランド戦略</t>
+    <rPh sb="0" eb="2">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>センリャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ニールセン・ノーマンによるUXの重要性で正しいのはどれか、次の中から選びなさい。</t>
+    <rPh sb="16" eb="19">
+      <t>ジュウヨウセイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXはユーザビリティやブランド、機能性など複数要素の統合的結果として生まれる</t>
+    <rPh sb="16" eb="19">
+      <t>キノウセイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>フクスウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>トウゴウテキ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXは画面上の操作性（UI）が全てを決める</t>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>ソウサセイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXは主に視覚的デザインと企業イメージで決まる</t>
+    <rPh sb="3" eb="4">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>シカクテキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キギョウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UXはシステムの開発効率と直接的に比例する</t>
+    <rPh sb="8" eb="10">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>コウリツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>チョクセツ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヒレイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -12971,7 +13532,7 @@
   <dimension ref="B2:P46"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="15" max="16" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
@@ -13435,9 +13996,1069 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2A52FAF-5790-423D-A8DD-955A034BED2E}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:C211"/>
   <sheetFormatPr defaultRowHeight="18"/>
-  <sheetData/>
+  <sheetData>
+    <row r="2" spans="2:3">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="B5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="B6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="B8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3">
+      <c r="B9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3">
+      <c r="B10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
+      <c r="B11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3">
+      <c r="B12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3">
+      <c r="B13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3">
+      <c r="B14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3">
+      <c r="B15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3">
+      <c r="B16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2">
+      <c r="B80">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2">
+      <c r="B88">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2">
+      <c r="B89">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2">
+      <c r="B90">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2">
+      <c r="B91">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2">
+      <c r="B92">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2">
+      <c r="B93">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2">
+      <c r="B94">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2">
+      <c r="B95">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2">
+      <c r="B96">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2">
+      <c r="B98">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2">
+      <c r="B99">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2">
+      <c r="B100">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2">
+      <c r="B101">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2">
+      <c r="B102">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2">
+      <c r="B103">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2">
+      <c r="B104">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="2:2">
+      <c r="B105">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2">
+      <c r="B106">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2">
+      <c r="B107">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2">
+      <c r="B108">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2">
+      <c r="B109">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2">
+      <c r="B110">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2">
+      <c r="B111">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2">
+      <c r="B112">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2">
+      <c r="B113">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2">
+      <c r="B114">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2">
+      <c r="B115">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2">
+      <c r="B116">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2">
+      <c r="B117">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2">
+      <c r="B118">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2">
+      <c r="B119">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2">
+      <c r="B120">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2">
+      <c r="B121">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2">
+      <c r="B122">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2">
+      <c r="B123">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2">
+      <c r="B124">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2">
+      <c r="B125">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2">
+      <c r="B126">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2">
+      <c r="B127">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="2:2">
+      <c r="B128">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2">
+      <c r="B129">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2">
+      <c r="B130">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2">
+      <c r="B131">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2">
+      <c r="B132">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2">
+      <c r="B133">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="2:2">
+      <c r="B134">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2">
+      <c r="B135">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2">
+      <c r="B136">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="2:2">
+      <c r="B137">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2">
+      <c r="B138">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2">
+      <c r="B139">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="2:2">
+      <c r="B140">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="2:2">
+      <c r="B141">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2">
+      <c r="B142">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="2:2">
+      <c r="B143">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="2:2">
+      <c r="B144">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2">
+      <c r="B145">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2">
+      <c r="B146">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2">
+      <c r="B147">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2">
+      <c r="B148">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2">
+      <c r="B149">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="2:2">
+      <c r="B150">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2">
+      <c r="B151">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2">
+      <c r="B152">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="2:2">
+      <c r="B153">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="2:2">
+      <c r="B154">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="2:2">
+      <c r="B155">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2">
+      <c r="B156">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="2:2">
+      <c r="B157">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2">
+      <c r="B158">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="2:2">
+      <c r="B159">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160" spans="2:2">
+      <c r="B160">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2">
+      <c r="B161">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2">
+      <c r="B162">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2">
+      <c r="B163">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2">
+      <c r="B164">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" spans="2:2">
+      <c r="B165">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2">
+      <c r="B166">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2">
+      <c r="B167">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2">
+      <c r="B168">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="2:2">
+      <c r="B169">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="2:2">
+      <c r="B170">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" spans="2:2">
+      <c r="B171">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2">
+      <c r="B172">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="2:2">
+      <c r="B173">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" spans="2:2">
+      <c r="B174">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" spans="2:2">
+      <c r="B175">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="2:2">
+      <c r="B176">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2">
+      <c r="B178">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2">
+      <c r="B179">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="2:2">
+      <c r="B180">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181" spans="2:2">
+      <c r="B181">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="2:2">
+      <c r="B182">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" spans="2:2">
+      <c r="B183">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" spans="2:2">
+      <c r="B184">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="2:2">
+      <c r="B185">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="2:2">
+      <c r="B186">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" spans="2:2">
+      <c r="B187">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188" spans="2:2">
+      <c r="B188">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189" spans="2:2">
+      <c r="B189">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190" spans="2:2">
+      <c r="B190">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191" spans="2:2">
+      <c r="B191">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192" spans="2:2">
+      <c r="B192">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193" spans="2:2">
+      <c r="B193">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198" spans="2:2">
+      <c r="B198">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199" spans="2:2">
+      <c r="B199">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200" spans="2:2">
+      <c r="B200">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201" spans="2:2">
+      <c r="B201">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="202" spans="2:2">
+      <c r="B202">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="203" spans="2:2">
+      <c r="B203">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="204" spans="2:2">
+      <c r="B204">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="205" spans="2:2">
+      <c r="B205">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="206" spans="2:2">
+      <c r="B206">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="207" spans="2:2">
+      <c r="B207">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="208" spans="2:2">
+      <c r="B208">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="209" spans="2:2">
+      <c r="B209">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="210" spans="2:2">
+      <c r="B210">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="211" spans="2:2">
+      <c r="B211">
+        <v>210</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13445,9 +15066,480 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17AF59C5-DF61-42ED-8998-32028D4B8AB2}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:Q332"/>
   <sheetFormatPr defaultRowHeight="18"/>
-  <sheetData/>
+  <cols>
+    <col min="17" max="17" width="9.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:17">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="O2" t="s">
+        <v>54</v>
+      </c>
+      <c r="P2" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="3" spans="2:17">
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17">
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17">
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17">
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17">
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1127</v>
+      </c>
+      <c r="O7" t="s">
+        <v>54</v>
+      </c>
+      <c r="P7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17">
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17">
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17">
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17">
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17">
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1132</v>
+      </c>
+      <c r="O12" t="s">
+        <v>54</v>
+      </c>
+      <c r="P12" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17">
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17">
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17">
+      <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="16" spans="2:17">
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2">
+      <c r="B92">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2">
+      <c r="B102">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2">
+      <c r="B107">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2">
+      <c r="B112">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2">
+      <c r="B117">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2">
+      <c r="B122">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2">
+      <c r="B127">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2">
+      <c r="B132">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="137" spans="2:2">
+      <c r="B137">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2">
+      <c r="B142">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2">
+      <c r="B147">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2">
+      <c r="B152">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="157" spans="2:2">
+      <c r="B157">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2">
+      <c r="B162">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2">
+      <c r="B167">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2">
+      <c r="B172">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="182" spans="2:2">
+      <c r="B182">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="187" spans="2:2">
+      <c r="B187">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="192" spans="2:2">
+      <c r="B192">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="202" spans="2:2">
+      <c r="B202">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="207" spans="2:2">
+      <c r="B207">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="212" spans="2:2">
+      <c r="B212">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="217" spans="2:2">
+      <c r="B217">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="222" spans="2:2">
+      <c r="B222">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="227" spans="2:2">
+      <c r="B227">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="232" spans="2:2">
+      <c r="B232">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="237" spans="2:2">
+      <c r="B237">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="242" spans="2:2">
+      <c r="B242">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="247" spans="2:2">
+      <c r="B247">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="252" spans="2:2">
+      <c r="B252">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="257" spans="2:2">
+      <c r="B257">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="262" spans="2:2">
+      <c r="B262">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="267" spans="2:2">
+      <c r="B267">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="272" spans="2:2">
+      <c r="B272">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="277" spans="2:2">
+      <c r="B277">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="282" spans="2:2">
+      <c r="B282">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="287" spans="2:2">
+      <c r="B287">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="292" spans="2:2">
+      <c r="B292">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="297" spans="2:2">
+      <c r="B297">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="302" spans="2:2">
+      <c r="B302">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="307" spans="2:2">
+      <c r="B307">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="312" spans="2:2">
+      <c r="B312">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="317" spans="2:2">
+      <c r="B317">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="322" spans="2:2">
+      <c r="B322">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="327" spans="2:2">
+      <c r="B327">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="332" spans="2:2">
+      <c r="B332">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13455,9 +15547,1069 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BCCF900-BD63-43AD-930D-63CB47F7722D}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:C211"/>
   <sheetFormatPr defaultRowHeight="18"/>
-  <sheetData/>
+  <sheetData>
+    <row r="2" spans="2:3">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3">
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="B5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="B6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="B8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3">
+      <c r="B9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3">
+      <c r="B10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
+      <c r="B11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3">
+      <c r="B12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3">
+      <c r="B13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3">
+      <c r="B14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3">
+      <c r="B15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3">
+      <c r="B16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2">
+      <c r="B80">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2">
+      <c r="B88">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2">
+      <c r="B89">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2">
+      <c r="B90">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2">
+      <c r="B91">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2">
+      <c r="B92">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2">
+      <c r="B93">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2">
+      <c r="B94">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2">
+      <c r="B95">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2">
+      <c r="B96">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2">
+      <c r="B98">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2">
+      <c r="B99">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2">
+      <c r="B100">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2">
+      <c r="B101">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2">
+      <c r="B102">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2">
+      <c r="B103">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2">
+      <c r="B104">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="2:2">
+      <c r="B105">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2">
+      <c r="B106">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2">
+      <c r="B107">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2">
+      <c r="B108">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2">
+      <c r="B109">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2">
+      <c r="B110">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2">
+      <c r="B111">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2">
+      <c r="B112">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2">
+      <c r="B113">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2">
+      <c r="B114">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2">
+      <c r="B115">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2">
+      <c r="B116">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2">
+      <c r="B117">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2">
+      <c r="B118">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2">
+      <c r="B119">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2">
+      <c r="B120">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2">
+      <c r="B121">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2">
+      <c r="B122">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2">
+      <c r="B123">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2">
+      <c r="B124">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2">
+      <c r="B125">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2">
+      <c r="B126">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2">
+      <c r="B127">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="2:2">
+      <c r="B128">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2">
+      <c r="B129">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2">
+      <c r="B130">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2">
+      <c r="B131">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2">
+      <c r="B132">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2">
+      <c r="B133">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="2:2">
+      <c r="B134">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2">
+      <c r="B135">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2">
+      <c r="B136">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="2:2">
+      <c r="B137">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2">
+      <c r="B138">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2">
+      <c r="B139">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="2:2">
+      <c r="B140">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="2:2">
+      <c r="B141">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2">
+      <c r="B142">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="2:2">
+      <c r="B143">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="2:2">
+      <c r="B144">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2">
+      <c r="B145">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2">
+      <c r="B146">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2">
+      <c r="B147">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2">
+      <c r="B148">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2">
+      <c r="B149">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="2:2">
+      <c r="B150">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2">
+      <c r="B151">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2">
+      <c r="B152">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="2:2">
+      <c r="B153">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="2:2">
+      <c r="B154">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="2:2">
+      <c r="B155">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2">
+      <c r="B156">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="2:2">
+      <c r="B157">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2">
+      <c r="B158">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="2:2">
+      <c r="B159">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160" spans="2:2">
+      <c r="B160">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2">
+      <c r="B161">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2">
+      <c r="B162">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2">
+      <c r="B163">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2">
+      <c r="B164">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" spans="2:2">
+      <c r="B165">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2">
+      <c r="B166">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2">
+      <c r="B167">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2">
+      <c r="B168">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="2:2">
+      <c r="B169">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="2:2">
+      <c r="B170">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" spans="2:2">
+      <c r="B171">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2">
+      <c r="B172">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="2:2">
+      <c r="B173">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" spans="2:2">
+      <c r="B174">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" spans="2:2">
+      <c r="B175">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="2:2">
+      <c r="B176">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2">
+      <c r="B178">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2">
+      <c r="B179">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="2:2">
+      <c r="B180">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181" spans="2:2">
+      <c r="B181">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="2:2">
+      <c r="B182">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" spans="2:2">
+      <c r="B183">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" spans="2:2">
+      <c r="B184">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="2:2">
+      <c r="B185">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="2:2">
+      <c r="B186">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" spans="2:2">
+      <c r="B187">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188" spans="2:2">
+      <c r="B188">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189" spans="2:2">
+      <c r="B189">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190" spans="2:2">
+      <c r="B190">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191" spans="2:2">
+      <c r="B191">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192" spans="2:2">
+      <c r="B192">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193" spans="2:2">
+      <c r="B193">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198" spans="2:2">
+      <c r="B198">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199" spans="2:2">
+      <c r="B199">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200" spans="2:2">
+      <c r="B200">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201" spans="2:2">
+      <c r="B201">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="202" spans="2:2">
+      <c r="B202">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="203" spans="2:2">
+      <c r="B203">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="204" spans="2:2">
+      <c r="B204">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="205" spans="2:2">
+      <c r="B205">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="206" spans="2:2">
+      <c r="B206">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="207" spans="2:2">
+      <c r="B207">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="208" spans="2:2">
+      <c r="B208">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="209" spans="2:2">
+      <c r="B209">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="210" spans="2:2">
+      <c r="B210">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="211" spans="2:2">
+      <c r="B211">
+        <v>210</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13468,7 +16620,7 @@
   <dimension ref="B2:W23"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="23" max="23" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:23">
@@ -13700,7 +16852,7 @@
   <dimension ref="B2:R27"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="18" max="18" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18">
@@ -13970,7 +17122,7 @@
   <dimension ref="B2:V23"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="22" max="22" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:22">
@@ -14196,7 +17348,7 @@
   <dimension ref="B2:Q502"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="17" max="17" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17">
@@ -21066,7 +24218,7 @@
   <dimension ref="B2:Q336"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="17" max="17" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17">
@@ -24370,6 +27522,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -25637,9 +28790,480 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{715CA485-1F5B-4BB5-A334-8CD98D55194C}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:Q332"/>
   <sheetFormatPr defaultRowHeight="18"/>
-  <sheetData/>
+  <cols>
+    <col min="17" max="17" width="9.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:17">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="O2" t="s">
+        <v>54</v>
+      </c>
+      <c r="P2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="3" spans="2:17">
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17">
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17">
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17">
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17">
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1137</v>
+      </c>
+      <c r="O7" t="s">
+        <v>54</v>
+      </c>
+      <c r="P7" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17">
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17">
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17">
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17">
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17">
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1142</v>
+      </c>
+      <c r="O12" t="s">
+        <v>54</v>
+      </c>
+      <c r="P12" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17">
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17">
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17">
+      <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="16" spans="2:17">
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2">
+      <c r="B92">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2">
+      <c r="B102">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2">
+      <c r="B107">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2">
+      <c r="B112">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2">
+      <c r="B117">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2">
+      <c r="B122">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2">
+      <c r="B127">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2">
+      <c r="B132">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="137" spans="2:2">
+      <c r="B137">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2">
+      <c r="B142">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2">
+      <c r="B147">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2">
+      <c r="B152">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="157" spans="2:2">
+      <c r="B157">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2">
+      <c r="B162">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2">
+      <c r="B167">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2">
+      <c r="B172">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="182" spans="2:2">
+      <c r="B182">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="187" spans="2:2">
+      <c r="B187">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="192" spans="2:2">
+      <c r="B192">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="202" spans="2:2">
+      <c r="B202">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="207" spans="2:2">
+      <c r="B207">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="212" spans="2:2">
+      <c r="B212">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="217" spans="2:2">
+      <c r="B217">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="222" spans="2:2">
+      <c r="B222">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="227" spans="2:2">
+      <c r="B227">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="232" spans="2:2">
+      <c r="B232">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="237" spans="2:2">
+      <c r="B237">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="242" spans="2:2">
+      <c r="B242">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="247" spans="2:2">
+      <c r="B247">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="252" spans="2:2">
+      <c r="B252">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="257" spans="2:2">
+      <c r="B257">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="262" spans="2:2">
+      <c r="B262">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="267" spans="2:2">
+      <c r="B267">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="272" spans="2:2">
+      <c r="B272">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="277" spans="2:2">
+      <c r="B277">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="282" spans="2:2">
+      <c r="B282">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="287" spans="2:2">
+      <c r="B287">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="292" spans="2:2">
+      <c r="B292">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="297" spans="2:2">
+      <c r="B297">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="302" spans="2:2">
+      <c r="B302">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="307" spans="2:2">
+      <c r="B307">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="312" spans="2:2">
+      <c r="B312">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="317" spans="2:2">
+      <c r="B317">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="322" spans="2:2">
+      <c r="B322">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="327" spans="2:2">
+      <c r="B327">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="332" spans="2:2">
+      <c r="B332">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
